--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C43BC3-4D4D-4217-BCC2-BD3D7B784A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4E3545-EB2E-422E-9431-4A46FE8A11F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Status</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>Responsável</t>
+  </si>
+  <si>
+    <t>Nota PM</t>
   </si>
 </sst>
 </file>
@@ -138,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -157,6 +160,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,96 +466,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>46027</v>
       </c>
       <c r="B2" s="4">
         <v>46125</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7">
+        <v>14178948</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="5">
+      <c r="G2" s="5">
         <v>1</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2" s="5">
         <v>2000</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4E3545-EB2E-422E-9431-4A46FE8A11F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AE8BF7-A840-4F82-BC41-232E62516C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Status</t>
   </si>
@@ -28,33 +28,12 @@
     <t>Data</t>
   </si>
   <si>
-    <t>4713400000</t>
-  </si>
-  <si>
-    <t>685531</t>
-  </si>
-  <si>
-    <t>LP-054431</t>
-  </si>
-  <si>
     <t>Objeto de Liquidação</t>
   </si>
   <si>
     <t>Part Number</t>
   </si>
   <si>
-    <t>Rodrigo Melo</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Novo - Série 0196</t>
-  </si>
-  <si>
-    <t>QMM</t>
-  </si>
-  <si>
     <t>Prazo Final</t>
   </si>
   <si>
@@ -80,6 +59,18 @@
   </si>
   <si>
     <t>Nota PM</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>bucha guia</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>LP-054888</t>
   </si>
 </sst>
 </file>
@@ -488,37 +479,37 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="H1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
@@ -526,40 +517,40 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>46027</v>
+        <v>46050</v>
       </c>
       <c r="B2" s="4">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="C2" s="7">
-        <v>14178948</v>
+        <v>14193317</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="E2" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F2" s="5">
+        <v>19</v>
       </c>
       <c r="G2" s="5">
-        <v>1</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="H2" s="5">
+        <v>4729401967</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K2" s="5">
-        <v>2000</v>
+        <v>4400</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AE8BF7-A840-4F82-BC41-232E62516C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C8A4C4-CDA5-4EAE-ADC5-687C642AD9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C8A4C4-CDA5-4EAE-ADC5-687C642AD9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BA4C43-ADEA-41BE-8DE9-33D1EBAAA7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Status</t>
   </si>
@@ -64,13 +64,37 @@
     <t>Yesica Gonzalez</t>
   </si>
   <si>
-    <t>bucha guia</t>
-  </si>
-  <si>
-    <t>DOUGLAS</t>
-  </si>
-  <si>
-    <t>LP-054888</t>
+    <t>05.01.2026</t>
+  </si>
+  <si>
+    <t>20.03.2026</t>
+  </si>
+  <si>
+    <t>IP 685487 Pino d suporte Ret.Fortuna ⌀10</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>1 200,00</t>
+  </si>
+  <si>
+    <t>LP-054499</t>
+  </si>
+  <si>
+    <t>07.01.2026</t>
+  </si>
+  <si>
+    <t>1+/11,48 -0,006</t>
+  </si>
+  <si>
+    <t>VIM6CT</t>
+  </si>
+  <si>
+    <t>2 400,00</t>
+  </si>
+  <si>
+    <t>LP-054692</t>
   </si>
 </sst>
 </file>
@@ -457,18 +481,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -516,41 +541,79 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>46050</v>
-      </c>
-      <c r="B2" s="4">
-        <v>46122</v>
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C2" s="7">
-        <v>14193317</v>
+        <v>14178673</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="5">
-        <v>685541</v>
+        <v>685487</v>
       </c>
       <c r="F2" s="5">
         <v>19</v>
       </c>
       <c r="G2" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H2" s="5">
-        <v>4729401967</v>
+        <v>4710200220</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="5">
-        <v>4400</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>16</v>
+      <c r="C3" s="7">
+        <v>14180350</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5">
+        <v>685401</v>
+      </c>
+      <c r="F3" s="5">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4711401345</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6BA4C43-ADEA-41BE-8DE9-33D1EBAAA7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B514F2BC-4B14-4658-A850-8DEA0E3048BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B514F2BC-4B14-4658-A850-8DEA0E3048BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD8F9D7-3BEB-49BB-B0A3-21154EC65A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="116">
   <si>
     <t>Status</t>
   </si>
@@ -64,37 +64,310 @@
     <t>Yesica Gonzalez</t>
   </si>
   <si>
-    <t>05.01.2026</t>
-  </si>
-  <si>
-    <t>20.03.2026</t>
-  </si>
-  <si>
-    <t>IP 685487 Pino d suporte Ret.Fortuna ⌀10</t>
-  </si>
-  <si>
     <t>DONI- 2803</t>
   </si>
   <si>
     <t>1 200,00</t>
   </si>
   <si>
-    <t>LP-054499</t>
-  </si>
-  <si>
-    <t>07.01.2026</t>
-  </si>
-  <si>
-    <t>1+/11,48 -0,006</t>
-  </si>
-  <si>
-    <t>VIM6CT</t>
-  </si>
-  <si>
-    <t>2 400,00</t>
-  </si>
-  <si>
-    <t>LP-054692</t>
+    <t>21.01.2026</t>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+  </si>
+  <si>
+    <t>FERNANDA AND</t>
+  </si>
+  <si>
+    <t>4711300472POS2</t>
+  </si>
+  <si>
+    <t>Base de apoio SCHRAUBE</t>
+  </si>
+  <si>
+    <t>1 560,00</t>
+  </si>
+  <si>
+    <t>LP-055262</t>
+  </si>
+  <si>
+    <t>Base da Solda GM</t>
+  </si>
+  <si>
+    <t>FERNANDA A</t>
+  </si>
+  <si>
+    <t>5 320,00</t>
+  </si>
+  <si>
+    <t>LP-055263</t>
+  </si>
+  <si>
+    <t>Base da Solda Gm</t>
+  </si>
+  <si>
+    <t>LP-055264</t>
+  </si>
+  <si>
+    <t>Pino do Berço GM</t>
+  </si>
+  <si>
+    <t>2 500,00</t>
+  </si>
+  <si>
+    <t>LP-055265</t>
+  </si>
+  <si>
+    <t>4722000078 POS20</t>
+  </si>
+  <si>
+    <t>Pino de desmontar Válvula</t>
+  </si>
+  <si>
+    <t>3 360,00</t>
+  </si>
+  <si>
+    <t>LP-055266</t>
+  </si>
+  <si>
+    <t>Dispositivo Superior Gm</t>
+  </si>
+  <si>
+    <t>6 600,00</t>
+  </si>
+  <si>
+    <t>LP-055267</t>
+  </si>
+  <si>
+    <t>22.01.2026</t>
+  </si>
+  <si>
+    <t>Dispo. Inferior Solda GM</t>
+  </si>
+  <si>
+    <t>8 100,00</t>
+  </si>
+  <si>
+    <t>LP-055268</t>
+  </si>
+  <si>
+    <t>4728603389 POS7</t>
+  </si>
+  <si>
+    <t>Pino de vedação superior GM</t>
+  </si>
+  <si>
+    <t>3 120,00</t>
+  </si>
+  <si>
+    <t>LP-055269</t>
+  </si>
+  <si>
+    <t>Dispo. Superior da Solda Gm</t>
+  </si>
+  <si>
+    <t>5 130,00</t>
+  </si>
+  <si>
+    <t>LP-055270</t>
+  </si>
+  <si>
+    <t>Sacador de anéis GM</t>
+  </si>
+  <si>
+    <t>2 200,00</t>
+  </si>
+  <si>
+    <t>LP-055271</t>
+  </si>
+  <si>
+    <t>Parafuso Excêntrico GM - Fabricação</t>
+  </si>
+  <si>
+    <t>7 300,00</t>
+  </si>
+  <si>
+    <t>LP-055272</t>
+  </si>
+  <si>
+    <t>4728603390POS13</t>
+  </si>
+  <si>
+    <t>Fixação Pino de Cobre GM</t>
+  </si>
+  <si>
+    <t>2 760,00</t>
+  </si>
+  <si>
+    <t>LP-055273</t>
+  </si>
+  <si>
+    <t>4729111119 POS 3</t>
+  </si>
+  <si>
+    <t>DU 685421 POS 3 do Bico direcionador</t>
+  </si>
+  <si>
+    <t>1 700,00</t>
+  </si>
+  <si>
+    <t>LP-054966</t>
+  </si>
+  <si>
+    <t>4728603390POS16</t>
+  </si>
+  <si>
+    <t>Encosto de Medição Resis. Plástico GM</t>
+  </si>
+  <si>
+    <t>LP-055274</t>
+  </si>
+  <si>
+    <t>4729108072POS13</t>
+  </si>
+  <si>
+    <t>Borracha de vedação GM</t>
+  </si>
+  <si>
+    <t>LP-055275</t>
+  </si>
+  <si>
+    <t>4712001662POS14</t>
+  </si>
+  <si>
+    <t>LP-055276</t>
+  </si>
+  <si>
+    <t>4729108073POS7</t>
+  </si>
+  <si>
+    <t>LP-055277</t>
+  </si>
+  <si>
+    <t>4712001661POS5</t>
+  </si>
+  <si>
+    <t>LP-055278</t>
+  </si>
+  <si>
+    <t>4729108072POS17</t>
+  </si>
+  <si>
+    <t>Apoio de Vedação Inferior GM</t>
+  </si>
+  <si>
+    <t>3 000,00</t>
+  </si>
+  <si>
+    <t>LP-055279</t>
+  </si>
+  <si>
+    <t>24.01.2026</t>
+  </si>
+  <si>
+    <t>Dispositivo Blaichach</t>
+  </si>
+  <si>
+    <t>REGIMARA</t>
+  </si>
+  <si>
+    <t>LP-054901</t>
+  </si>
+  <si>
+    <t>26.01.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+  </si>
+  <si>
+    <t>4728603390POS19</t>
+  </si>
+  <si>
+    <t>Dispo. Medição GM</t>
+  </si>
+  <si>
+    <t>8 750,00</t>
+  </si>
+  <si>
+    <t>LP-055287</t>
+  </si>
+  <si>
+    <t>4728603390POS20</t>
+  </si>
+  <si>
+    <t>LP-055288</t>
+  </si>
+  <si>
+    <t>Ponteira Parafusamento Est 50 - MTG UP</t>
+  </si>
+  <si>
+    <t>JHEYMIS</t>
+  </si>
+  <si>
+    <t>LP-055180</t>
+  </si>
+  <si>
+    <t>Disp. Nagel</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>1 000,00</t>
+  </si>
+  <si>
+    <t>LP-054890</t>
+  </si>
+  <si>
+    <t>LP-054892</t>
+  </si>
+  <si>
+    <t>LP-054896</t>
+  </si>
+  <si>
+    <t>LP-054891</t>
+  </si>
+  <si>
+    <t>30.01.2026</t>
+  </si>
+  <si>
+    <t>LP-055173</t>
+  </si>
+  <si>
+    <t>LP-055174</t>
+  </si>
+  <si>
+    <t>Braço Alimentador 8,38</t>
+  </si>
+  <si>
+    <t>3 300,00</t>
+  </si>
+  <si>
+    <t>LP-055289</t>
+  </si>
+  <si>
+    <t>Castanhas  Ø8,25</t>
+  </si>
+  <si>
+    <t>4 740,00</t>
+  </si>
+  <si>
+    <t>LP-055290</t>
+  </si>
+  <si>
+    <t>Castanhas Crin</t>
+  </si>
+  <si>
+    <t>2 490,00</t>
+  </si>
+  <si>
+    <t>LP-055291</t>
+  </si>
+  <si>
+    <t>DU 685434 Vareta retífica curso (acabame</t>
+  </si>
+  <si>
+    <t>LP-054955</t>
   </si>
 </sst>
 </file>
@@ -481,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="4" bestFit="1" customWidth="1"/>
@@ -542,78 +815,1256 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="7">
-        <v>14178673</v>
+        <v>14188001</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="5">
-        <v>685487</v>
+        <v>685605</v>
       </c>
       <c r="F2" s="5">
         <v>19</v>
       </c>
       <c r="G2" s="5">
-        <v>2</v>
-      </c>
-      <c r="H2" s="5">
-        <v>4710200220</v>
+        <v>12</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="7">
+        <v>14188039</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F3" s="5">
+        <v>19</v>
+      </c>
+      <c r="G3" s="5">
+        <v>4</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4712001682</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="7">
+        <v>14188046</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F4" s="5">
+        <v>19</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4728602195</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7">
+        <v>14188051</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F5" s="5">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5">
         <v>20</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="H5" s="5">
+        <v>4730500266</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="7">
+        <v>14188356</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F6" s="5">
+        <v>19</v>
+      </c>
+      <c r="G6" s="5">
+        <v>12</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="7">
+        <v>14188366</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F7" s="5">
+        <v>19</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>4712001661</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="7">
+        <v>14188774</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F8" s="5">
+        <v>19</v>
+      </c>
+      <c r="G8" s="5">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5">
+        <v>4711300472</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7">
+        <v>14188777</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F9" s="5">
+        <v>19</v>
+      </c>
+      <c r="G9" s="5">
+        <v>4</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="7">
+        <v>14188784</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F10" s="5">
+        <v>19</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5">
+        <v>4728602373</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="7">
+        <v>14188800</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F11" s="5">
+        <v>19</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4728602423</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="7">
+        <v>14188802</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F12" s="5">
+        <v>19</v>
+      </c>
+      <c r="G12" s="5">
+        <v>10</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4712004495</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="7">
+        <v>14188828</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F13" s="5">
+        <v>19</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="7">
+        <v>14189088</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="5">
+        <v>685421</v>
+      </c>
+      <c r="F14" s="5">
+        <v>19</v>
+      </c>
+      <c r="G14" s="5">
+        <v>10</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="7">
+        <v>14189105</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F15" s="5">
+        <v>19</v>
+      </c>
+      <c r="G15" s="5">
+        <v>4</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="7">
+        <v>14189107</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F16" s="5">
+        <v>19</v>
+      </c>
+      <c r="G16" s="5">
+        <v>4</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="5">
+        <v>400</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="7">
+        <v>14189109</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F17" s="5">
+        <v>19</v>
+      </c>
+      <c r="G17" s="5">
+        <v>10</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="7">
-        <v>14180350</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5">
-        <v>685401</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="L17" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="7">
+        <v>14189111</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F18" s="5">
+        <v>19</v>
+      </c>
+      <c r="G18" s="5">
+        <v>10</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="5">
+        <v>900</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="7">
+        <v>14189113</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F19" s="5">
+        <v>19</v>
+      </c>
+      <c r="G19" s="5">
+        <v>10</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="5">
+        <v>900</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="7">
+        <v>14189117</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F20" s="5">
+        <v>19</v>
+      </c>
+      <c r="G20" s="5">
+        <v>15</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="7">
+        <v>14190286</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="5">
+        <v>685554</v>
+      </c>
+      <c r="F21" s="5">
+        <v>19</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5">
+        <v>4712003439</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K21" s="5">
+        <v>330</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="7">
+        <v>14191160</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F22" s="5">
+        <v>19</v>
+      </c>
+      <c r="G22" s="5">
+        <v>10</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="7">
+        <v>14191160</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F23" s="5">
+        <v>19</v>
+      </c>
+      <c r="G23" s="5">
+        <v>10</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="7">
+        <v>14191164</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="5">
+        <v>685553</v>
+      </c>
+      <c r="F24" s="5">
         <v>5</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G24" s="5">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5">
+        <v>4728602128</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="7">
+        <v>14191179</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F25" s="5">
+        <v>19</v>
+      </c>
+      <c r="G25" s="5">
+        <v>5</v>
+      </c>
+      <c r="H25" s="5">
+        <v>4727501155</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="7">
+        <v>14191189</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F26" s="5">
+        <v>19</v>
+      </c>
+      <c r="G26" s="5">
+        <v>3</v>
+      </c>
+      <c r="H26" s="5">
+        <v>4729104510</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K26" s="5">
+        <v>450</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="7">
+        <v>14191213</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F27" s="5">
+        <v>19</v>
+      </c>
+      <c r="G27" s="5">
+        <v>4</v>
+      </c>
+      <c r="H27" s="5">
+        <v>4729401707</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K27" s="5">
+        <v>800</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="7">
+        <v>14191219</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F28" s="5">
+        <v>19</v>
+      </c>
+      <c r="G28" s="5">
+        <v>4</v>
+      </c>
+      <c r="H28" s="5">
+        <v>4727501151</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" s="5">
+        <v>800</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="7">
+        <v>14196078</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F29" s="5">
+        <v>19</v>
+      </c>
+      <c r="G29" s="5">
+        <v>4</v>
+      </c>
+      <c r="H29" s="5">
+        <v>4727501150</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K29" s="5">
+        <v>800</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="7">
+        <v>14196087</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F30" s="5">
+        <v>19</v>
+      </c>
+      <c r="G30" s="5">
+        <v>5</v>
+      </c>
+      <c r="H30" s="5">
+        <v>4729401707</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="7">
+        <v>14196118</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="5">
+        <v>685615</v>
+      </c>
+      <c r="F31" s="5">
+        <v>19</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2</v>
+      </c>
+      <c r="H31" s="5">
+        <v>4728701255</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="7">
+        <v>14196129</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="5">
+        <v>685615</v>
+      </c>
+      <c r="F32" s="5">
+        <v>19</v>
+      </c>
+      <c r="G32" s="5">
         <v>6</v>
       </c>
-      <c r="H3" s="5">
-        <v>4711401345</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>24</v>
+      <c r="H32" s="5">
+        <v>4711400979</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="7">
+        <v>14196132</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="5">
+        <v>685615</v>
+      </c>
+      <c r="F33" s="5">
+        <v>19</v>
+      </c>
+      <c r="G33" s="5">
+        <v>3</v>
+      </c>
+      <c r="H33" s="5">
+        <v>4711400737</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="7">
+        <v>14196239</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="5">
+        <v>685434</v>
+      </c>
+      <c r="F34" s="5">
+        <v>20</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5">
+        <v>4728701030</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K34" s="5">
+        <v>880</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA881D8C-06BD-48CF-B7A7-90B24657086D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E899617-D690-4520-971B-A1BC008354B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,22 +20,94 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>PM</t>
-  </si>
-  <si>
-    <t>000014153774</t>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Prazo Final</t>
+  </si>
+  <si>
+    <t>Nota PM</t>
+  </si>
+  <si>
+    <t>Responsável</t>
+  </si>
+  <si>
+    <t>Objeto de Liquidação</t>
+  </si>
+  <si>
+    <t>Esquema de Alocação</t>
+  </si>
+  <si>
+    <t>Quantidade</t>
+  </si>
+  <si>
+    <t>Part Number</t>
+  </si>
+  <si>
+    <t>Denominação</t>
+  </si>
+  <si>
+    <t>Entregar para</t>
+  </si>
+  <si>
+    <t>Custo estimado</t>
+  </si>
+  <si>
+    <t>Elemento PEP</t>
+  </si>
+  <si>
+    <t>21.01.2026</t>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+  </si>
+  <si>
+    <t>Yesica Gonzalez</t>
+  </si>
+  <si>
+    <t>4711300472POS2</t>
+  </si>
+  <si>
+    <t>Base de apoio SCHRAUBE</t>
+  </si>
+  <si>
+    <t>FERNANDA AND</t>
+  </si>
+  <si>
+    <t>1 560,00</t>
+  </si>
+  <si>
+    <t>LP-055262</t>
+  </si>
+  <si>
+    <t>Base da Solda GM</t>
+  </si>
+  <si>
+    <t>FERNANDA A</t>
+  </si>
+  <si>
+    <t>5 320,00</t>
+  </si>
+  <si>
+    <t>LP-055263</t>
+  </si>
+  <si>
+    <t>Base da Solda Gm</t>
+  </si>
+  <si>
+    <t>LP-055264</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -48,6 +120,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -57,7 +135,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -80,21 +158,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -107,11 +170,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -415,25 +478,177 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="4">
+        <v>14188001</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4">
+        <v>685605</v>
+      </c>
+      <c r="F2" s="4">
+        <v>19</v>
+      </c>
+      <c r="G2" s="4">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4">
+        <v>14188039</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4">
+        <v>685605</v>
+      </c>
+      <c r="F3" s="4">
+        <v>19</v>
+      </c>
+      <c r="G3" s="4">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4">
+        <v>4712001682</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4">
+        <v>14188046</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4">
+        <v>685605</v>
+      </c>
+      <c r="F4" s="4">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4">
+        <v>4</v>
+      </c>
+      <c r="H4" s="4">
+        <v>4728602195</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E899617-D690-4520-971B-A1BC008354B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C430B5B3-EB8C-4327-8774-D68B05978296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="297">
   <si>
     <t>Status</t>
   </si>
@@ -101,6 +101,816 @@
   </si>
   <si>
     <t>LP-055264</t>
+  </si>
+  <si>
+    <t>Pino do Berço GM</t>
+  </si>
+  <si>
+    <t>2 500,00</t>
+  </si>
+  <si>
+    <t>LP-055265</t>
+  </si>
+  <si>
+    <t>4722000078 POS20</t>
+  </si>
+  <si>
+    <t>Pino de desmontar Válvula</t>
+  </si>
+  <si>
+    <t>3 360,00</t>
+  </si>
+  <si>
+    <t>LP-055266</t>
+  </si>
+  <si>
+    <t>Dispositivo Superior Gm</t>
+  </si>
+  <si>
+    <t>6 600,00</t>
+  </si>
+  <si>
+    <t>LP-055267</t>
+  </si>
+  <si>
+    <t>22.01.2026</t>
+  </si>
+  <si>
+    <t>Dispo. Inferior Solda GM</t>
+  </si>
+  <si>
+    <t>8 100,00</t>
+  </si>
+  <si>
+    <t>LP-055268</t>
+  </si>
+  <si>
+    <t>4728603389 POS7</t>
+  </si>
+  <si>
+    <t>Pino de vedação superior GM</t>
+  </si>
+  <si>
+    <t>3 120,00</t>
+  </si>
+  <si>
+    <t>LP-055269</t>
+  </si>
+  <si>
+    <t>Dispo. Superior da Solda Gm</t>
+  </si>
+  <si>
+    <t>5 130,00</t>
+  </si>
+  <si>
+    <t>LP-055270</t>
+  </si>
+  <si>
+    <t>Sacador de anéis GM</t>
+  </si>
+  <si>
+    <t>2 200,00</t>
+  </si>
+  <si>
+    <t>LP-055271</t>
+  </si>
+  <si>
+    <t>Parafuso Excêntrico GM - Fabricação</t>
+  </si>
+  <si>
+    <t>7 300,00</t>
+  </si>
+  <si>
+    <t>LP-055272</t>
+  </si>
+  <si>
+    <t>4728603390POS13</t>
+  </si>
+  <si>
+    <t>Fixação Pino de Cobre GM</t>
+  </si>
+  <si>
+    <t>2 760,00</t>
+  </si>
+  <si>
+    <t>LP-055273</t>
+  </si>
+  <si>
+    <t>4729111119 POS 3</t>
+  </si>
+  <si>
+    <t>DU 685421 POS 3 do Bico direcionador</t>
+  </si>
+  <si>
+    <t>DONI- 2803</t>
+  </si>
+  <si>
+    <t>1 700,00</t>
+  </si>
+  <si>
+    <t>LP-054966</t>
+  </si>
+  <si>
+    <t>4728603390POS16</t>
+  </si>
+  <si>
+    <t>Encosto de Medição Resis. Plástico GM</t>
+  </si>
+  <si>
+    <t>LP-055274</t>
+  </si>
+  <si>
+    <t>4729108072POS13</t>
+  </si>
+  <si>
+    <t>Borracha de vedação GM</t>
+  </si>
+  <si>
+    <t>LP-055275</t>
+  </si>
+  <si>
+    <t>4712001662POS14</t>
+  </si>
+  <si>
+    <t>1 200,00</t>
+  </si>
+  <si>
+    <t>LP-055276</t>
+  </si>
+  <si>
+    <t>4729108073POS7</t>
+  </si>
+  <si>
+    <t>LP-055277</t>
+  </si>
+  <si>
+    <t>4712001661POS5</t>
+  </si>
+  <si>
+    <t>LP-055278</t>
+  </si>
+  <si>
+    <t>4729108072POS17</t>
+  </si>
+  <si>
+    <t>Apoio de Vedação Inferior GM</t>
+  </si>
+  <si>
+    <t>3 000,00</t>
+  </si>
+  <si>
+    <t>LP-055279</t>
+  </si>
+  <si>
+    <t>24.01.2026</t>
+  </si>
+  <si>
+    <t>Dispositivo Blaichach</t>
+  </si>
+  <si>
+    <t>REGIMARA</t>
+  </si>
+  <si>
+    <t>LP-054901</t>
+  </si>
+  <si>
+    <t>26.01.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026</t>
+  </si>
+  <si>
+    <t>4728603390POS19</t>
+  </si>
+  <si>
+    <t>Dispo. Medição GM</t>
+  </si>
+  <si>
+    <t>8 750,00</t>
+  </si>
+  <si>
+    <t>LP-055287</t>
+  </si>
+  <si>
+    <t>4728603390POS20</t>
+  </si>
+  <si>
+    <t>LP-055288</t>
+  </si>
+  <si>
+    <t>Ponteira Parafusamento Est 50 - MTG UP</t>
+  </si>
+  <si>
+    <t>JHEYMIS</t>
+  </si>
+  <si>
+    <t>LP-055180</t>
+  </si>
+  <si>
+    <t>Disp. Nagel</t>
+  </si>
+  <si>
+    <t>DOUGLAS</t>
+  </si>
+  <si>
+    <t>1 000,00</t>
+  </si>
+  <si>
+    <t>LP-054890</t>
+  </si>
+  <si>
+    <t>LP-054892</t>
+  </si>
+  <si>
+    <t>LP-054896</t>
+  </si>
+  <si>
+    <t>LP-054891</t>
+  </si>
+  <si>
+    <t>30.01.2026</t>
+  </si>
+  <si>
+    <t>LP-055173</t>
+  </si>
+  <si>
+    <t>LP-055174</t>
+  </si>
+  <si>
+    <t>Braço Alimentador 8,38</t>
+  </si>
+  <si>
+    <t>3 300,00</t>
+  </si>
+  <si>
+    <t>LP-055289</t>
+  </si>
+  <si>
+    <t>Castanhas  Ø8,25</t>
+  </si>
+  <si>
+    <t>4 740,00</t>
+  </si>
+  <si>
+    <t>LP-055290</t>
+  </si>
+  <si>
+    <t>Castanhas Crin</t>
+  </si>
+  <si>
+    <t>2 490,00</t>
+  </si>
+  <si>
+    <t>LP-055291</t>
+  </si>
+  <si>
+    <t>DU 685434 Vareta retífica curso (acabame</t>
+  </si>
+  <si>
+    <t>LP-054955</t>
+  </si>
+  <si>
+    <t>02.02.2026</t>
+  </si>
+  <si>
+    <t>17.04.2026</t>
+  </si>
+  <si>
+    <t>4729401760 POS 3</t>
+  </si>
+  <si>
+    <t>DU 685421 POSIÇÃO 3 d corpo distribuidor</t>
+  </si>
+  <si>
+    <t>7 000,00</t>
+  </si>
+  <si>
+    <t>LP-055085</t>
+  </si>
+  <si>
+    <t>DU 685421 Pino de gravadora AGIEs</t>
+  </si>
+  <si>
+    <t>2 250,00</t>
+  </si>
+  <si>
+    <t>LP-055087</t>
+  </si>
+  <si>
+    <t>IP 685485 Braço de tranporte de pallet</t>
+  </si>
+  <si>
+    <t>3 520,00</t>
+  </si>
+  <si>
+    <t>LP-055097</t>
+  </si>
+  <si>
+    <t>DU 685434 Garra da linha autom.Acabamen.</t>
+  </si>
+  <si>
+    <t>2 920,00</t>
+  </si>
+  <si>
+    <t>LP-055086</t>
+  </si>
+  <si>
+    <t>03.02.2026</t>
+  </si>
+  <si>
+    <t>IP 685484 Espera prismatica pistão A</t>
+  </si>
+  <si>
+    <t>3 020,00</t>
+  </si>
+  <si>
+    <t>LP-055047</t>
+  </si>
+  <si>
+    <t>DU 685421 POSIÇÃO 1 Dispositivo AGIE Q1</t>
+  </si>
+  <si>
+    <t>4 280,00</t>
+  </si>
+  <si>
+    <t>LP-055092</t>
+  </si>
+  <si>
+    <t>DU 685434 Pino fixação de pano Ø3mm</t>
+  </si>
+  <si>
+    <t>LP-055091</t>
+  </si>
+  <si>
+    <t>DU 685421 Pino de fixação Q1</t>
+  </si>
+  <si>
+    <t>3 500,00</t>
+  </si>
+  <si>
+    <t>LP-055089</t>
+  </si>
+  <si>
+    <t>DU 685421 Bucha pino guia ∅3,5mm</t>
+  </si>
+  <si>
+    <t>4 900,00</t>
+  </si>
+  <si>
+    <t>LP-055090</t>
+  </si>
+  <si>
+    <t>DU 685421 Ponteira de medição da gravad.</t>
+  </si>
+  <si>
+    <t>4 500,00</t>
+  </si>
+  <si>
+    <t>LP-055088</t>
+  </si>
+  <si>
+    <t>04.02.2026</t>
+  </si>
+  <si>
+    <t>Encosto da placa</t>
+  </si>
+  <si>
+    <t>2 000,00</t>
+  </si>
+  <si>
+    <t>LP-055193</t>
+  </si>
+  <si>
+    <t>Dispositivo suporte prego</t>
+  </si>
+  <si>
+    <t>2 740,00</t>
+  </si>
+  <si>
+    <t>LP-055061</t>
+  </si>
+  <si>
+    <t>Contra ponto</t>
+  </si>
+  <si>
+    <t>LP-055160</t>
+  </si>
+  <si>
+    <t>Carimbo da montadora Tucho</t>
+  </si>
+  <si>
+    <t>11 880,00</t>
+  </si>
+  <si>
+    <t>LP-055239</t>
+  </si>
+  <si>
+    <t>Suporte de fixação</t>
+  </si>
+  <si>
+    <t>LP-055207</t>
+  </si>
+  <si>
+    <t>Pino 7mm</t>
+  </si>
+  <si>
+    <t>LP-055157</t>
+  </si>
+  <si>
+    <t>bucha guia</t>
+  </si>
+  <si>
+    <t>10 000,00</t>
+  </si>
+  <si>
+    <t>LP-055206</t>
+  </si>
+  <si>
+    <t>Pino</t>
+  </si>
+  <si>
+    <t>4 000,00</t>
+  </si>
+  <si>
+    <t>LP-055204</t>
+  </si>
+  <si>
+    <t>Garra</t>
+  </si>
+  <si>
+    <t>2 400,00</t>
+  </si>
+  <si>
+    <t>LP-055163</t>
+  </si>
+  <si>
+    <t>Disp. Rebarbação</t>
+  </si>
+  <si>
+    <t>LP-055156</t>
+  </si>
+  <si>
+    <t>LP-055158</t>
+  </si>
+  <si>
+    <t>LP-055164</t>
+  </si>
+  <si>
+    <t>POSIÇÃO 25 do robo da embalagem</t>
+  </si>
+  <si>
+    <t>2 560,00</t>
+  </si>
+  <si>
+    <t>LP-055063</t>
+  </si>
+  <si>
+    <t>POSIÇÃO 44 do robo da embalagem</t>
+  </si>
+  <si>
+    <t>3 160,00</t>
+  </si>
+  <si>
+    <t>LP-055064</t>
+  </si>
+  <si>
+    <t>IP 685484 Contra ponto emparelhamento A</t>
+  </si>
+  <si>
+    <t>LP-055100</t>
+  </si>
+  <si>
+    <t>DU 685411 Contra ponto Haste Cheia U.D</t>
+  </si>
+  <si>
+    <t>LP-055060</t>
+  </si>
+  <si>
+    <t>IP 685487 Contra ponto emparelhament A/K</t>
+  </si>
+  <si>
+    <t>LP-055095</t>
+  </si>
+  <si>
+    <t>Pino ECM</t>
+  </si>
+  <si>
+    <t>LP-055208</t>
+  </si>
+  <si>
+    <t>Carrinho</t>
+  </si>
+  <si>
+    <t>LP-055162</t>
+  </si>
+  <si>
+    <t>Flange TBT</t>
+  </si>
+  <si>
+    <t>LP-055161</t>
+  </si>
+  <si>
+    <t>05.02.2026</t>
+  </si>
+  <si>
+    <t>Posição 3</t>
+  </si>
+  <si>
+    <t>4 800,00</t>
+  </si>
+  <si>
+    <t>LP-055155</t>
+  </si>
+  <si>
+    <t>IP 685485 Flange de fixação de Rebolo.</t>
+  </si>
+  <si>
+    <t>1 100,00</t>
+  </si>
+  <si>
+    <t>LP-055099</t>
+  </si>
+  <si>
+    <t>LP-055154</t>
+  </si>
+  <si>
+    <t>09.02.2026</t>
+  </si>
+  <si>
+    <t>Dispositivo completo</t>
+  </si>
+  <si>
+    <t>LAL9CT</t>
+  </si>
+  <si>
+    <t>LP-055411</t>
+  </si>
+  <si>
+    <t>10.02.2026</t>
+  </si>
+  <si>
+    <t>18.03.2026</t>
+  </si>
+  <si>
+    <t>4710900878-2</t>
+  </si>
+  <si>
+    <t>PUNÇÃO DE PRENSAGEM</t>
+  </si>
+  <si>
+    <t>6 000,00</t>
+  </si>
+  <si>
+    <t>LP-055237</t>
+  </si>
+  <si>
+    <t>11.02.2026</t>
+  </si>
+  <si>
+    <t>Rebolo</t>
+  </si>
+  <si>
+    <t>1 760,00</t>
+  </si>
+  <si>
+    <t>LP-055393</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>685556 - Batente carrinho de transporte</t>
+  </si>
+  <si>
+    <t>VLU9CT</t>
+  </si>
+  <si>
+    <t>LP-055461</t>
+  </si>
+  <si>
+    <t>12.02.2026</t>
+  </si>
+  <si>
+    <t>Tampão VDI/EMAG</t>
+  </si>
+  <si>
+    <t>2 640,00</t>
+  </si>
+  <si>
+    <t>LP-055437</t>
+  </si>
+  <si>
+    <t>HASTE DE MEDIÇÃO S/NORMA</t>
+  </si>
+  <si>
+    <t>LP-055392</t>
+  </si>
+  <si>
+    <t>13.02.2026</t>
+  </si>
+  <si>
+    <t>DU 685434 Encosto THIELENHAUSS</t>
+  </si>
+  <si>
+    <t>10 860,00</t>
+  </si>
+  <si>
+    <t>LP-055420</t>
+  </si>
+  <si>
+    <t>DU 685434 POSIÇÃO 1 Pressionador  mola</t>
+  </si>
+  <si>
+    <t>LP-055415</t>
+  </si>
+  <si>
+    <t>DU 685412 Guia da vareta injetora (agulh</t>
+  </si>
+  <si>
+    <t>LP-055419</t>
+  </si>
+  <si>
+    <t>DU 685412 Vareta recolhedora d alimentaç</t>
+  </si>
+  <si>
+    <t>LP-055416</t>
+  </si>
+  <si>
+    <t>4728701270 POS 1</t>
+  </si>
+  <si>
+    <t>DU 685412 Disp. "jacaré" Bahmuller POS 1</t>
+  </si>
+  <si>
+    <t>LP-055417</t>
+  </si>
+  <si>
+    <t>4728701270 POS 2</t>
+  </si>
+  <si>
+    <t>DU 685412 Disp. "jacaré" Bahmuller POS 2</t>
+  </si>
+  <si>
+    <t>LP-055418</t>
+  </si>
+  <si>
+    <t>16.02.2026</t>
+  </si>
+  <si>
+    <t>Dispositivo STH</t>
+  </si>
+  <si>
+    <t>1 650,00</t>
+  </si>
+  <si>
+    <t>LP-055430</t>
+  </si>
+  <si>
+    <t>posição 2</t>
+  </si>
+  <si>
+    <t>LP-055424</t>
+  </si>
+  <si>
+    <t>Anel da placa MIKRON</t>
+  </si>
+  <si>
+    <t>2 310,00</t>
+  </si>
+  <si>
+    <t>LP-055434</t>
+  </si>
+  <si>
+    <t>Contraponto</t>
+  </si>
+  <si>
+    <t>LP-055394</t>
+  </si>
+  <si>
+    <t>GARRA UVA</t>
+  </si>
+  <si>
+    <t>2 750,00</t>
+  </si>
+  <si>
+    <t>LP-055432</t>
+  </si>
+  <si>
+    <t>LP-055431</t>
+  </si>
+  <si>
+    <t>17.02.2026</t>
+  </si>
+  <si>
+    <t>RÉGUA</t>
+  </si>
+  <si>
+    <t>4 400,00</t>
+  </si>
+  <si>
+    <t>LP-055428</t>
+  </si>
+  <si>
+    <t>4710900876_3</t>
+  </si>
+  <si>
+    <t>PUNÇÃO DE PRENSAGEM - UIN2</t>
+  </si>
+  <si>
+    <t>LP-055236</t>
+  </si>
+  <si>
+    <t>18.02.2026</t>
+  </si>
+  <si>
+    <t>IP 685485 Bucha de guia inferior  Ø11</t>
+  </si>
+  <si>
+    <t>LP-055433</t>
+  </si>
+  <si>
+    <t>IP 685486 Pinça CIL H ⌀11 Zema 4593</t>
+  </si>
+  <si>
+    <t>5 500,00</t>
+  </si>
+  <si>
+    <t>LP-055435</t>
+  </si>
+  <si>
+    <t>IP 685487 Buchas ZL CIL A 7498 (Lino/Fe)</t>
+  </si>
+  <si>
+    <t>11 730,00</t>
+  </si>
+  <si>
+    <t>LP-055429</t>
+  </si>
+  <si>
+    <t>LP-055395</t>
+  </si>
+  <si>
+    <t>1 800,00</t>
+  </si>
+  <si>
+    <t>LP-055396</t>
+  </si>
+  <si>
+    <t>IP-685485 POSIÇÃO 20 da garra d Manipul.</t>
+  </si>
+  <si>
+    <t>3 100,00</t>
+  </si>
+  <si>
+    <t>LP-055427</t>
+  </si>
+  <si>
+    <t>19.02.2026</t>
+  </si>
+  <si>
+    <t>RÉGUA DE APOIO BONELI</t>
+  </si>
+  <si>
+    <t>LP-055462</t>
+  </si>
+  <si>
+    <t>LP-055463</t>
+  </si>
+  <si>
+    <t>LP-055436</t>
+  </si>
+  <si>
+    <t>BUCHA GUIA</t>
+  </si>
+  <si>
+    <t>LP-055464</t>
+  </si>
+  <si>
+    <t>carimbos hpc</t>
+  </si>
+  <si>
+    <t>BOB2CT</t>
+  </si>
+  <si>
+    <t>10 600,00</t>
+  </si>
+  <si>
+    <t>LP-055457</t>
+  </si>
+  <si>
+    <t>20.02.2026</t>
+  </si>
+  <si>
+    <t>IP 685484 Contra ponto emparelhamento P</t>
+  </si>
+  <si>
+    <t>LP-055460</t>
+  </si>
+  <si>
+    <t>DU 685411 Pino Ø 5mm retificas U.V.A</t>
+  </si>
+  <si>
+    <t>LP-055450</t>
   </si>
 </sst>
 </file>
@@ -135,7 +945,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -158,11 +968,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -173,14 +998,229 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FFEDD8FC"/>
+          <bgColor rgb="FFCCCCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FFEDD8FC"/>
+          <bgColor rgb="FFCCCCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FFEDD8FC"/>
+          <bgColor rgb="FFCCCCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFCC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FFEDD8FC"/>
+          <bgColor rgb="FFCCCCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -478,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
@@ -488,8 +1528,8 @@
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -544,34 +1584,34 @@
       <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>14188001</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="5">
         <v>685605</v>
       </c>
-      <c r="F2" s="4">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="F2" s="5">
+        <v>19</v>
+      </c>
+      <c r="G2" s="5">
         <v>12</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -582,34 +1622,34 @@
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>14188039</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="5">
         <v>685605</v>
       </c>
-      <c r="F3" s="4">
-        <v>19</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="F3" s="5">
+        <v>19</v>
+      </c>
+      <c r="G3" s="5">
         <v>4</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
         <v>4712001682</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>24</v>
       </c>
     </row>
@@ -620,35 +1660,3681 @@
       <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>14188046</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5">
         <v>685605</v>
       </c>
-      <c r="F4" s="4">
-        <v>19</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="F4" s="5">
+        <v>19</v>
+      </c>
+      <c r="G4" s="5">
         <v>4</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>4728602195</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="5" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="5">
+        <v>14188051</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F5" s="5">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5">
+        <v>4730500266</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5">
+        <v>14188356</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F6" s="5">
+        <v>19</v>
+      </c>
+      <c r="G6" s="5">
+        <v>12</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5">
+        <v>14188366</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F7" s="5">
+        <v>19</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>4712001661</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5">
+        <v>14188774</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F8" s="5">
+        <v>19</v>
+      </c>
+      <c r="G8" s="5">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5">
+        <v>4711300472</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="5">
+        <v>14188777</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F9" s="5">
+        <v>19</v>
+      </c>
+      <c r="G9" s="5">
+        <v>4</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="5">
+        <v>14188784</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F10" s="5">
+        <v>19</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5">
+        <v>4728602373</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5">
+        <v>14188800</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F11" s="5">
+        <v>19</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4728602423</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="5">
+        <v>14188802</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F12" s="5">
+        <v>19</v>
+      </c>
+      <c r="G12" s="5">
+        <v>10</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4712004495</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5">
+        <v>14188828</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F13" s="5">
+        <v>19</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="5">
+        <v>14189088</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5">
+        <v>685421</v>
+      </c>
+      <c r="F14" s="5">
+        <v>19</v>
+      </c>
+      <c r="G14" s="5">
+        <v>10</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="5">
+        <v>14189105</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F15" s="5">
+        <v>19</v>
+      </c>
+      <c r="G15" s="5">
+        <v>4</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="5">
+        <v>14189107</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F16" s="5">
+        <v>19</v>
+      </c>
+      <c r="G16" s="5">
+        <v>4</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="5">
+        <v>400</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="5">
+        <v>14189109</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F17" s="5">
+        <v>19</v>
+      </c>
+      <c r="G17" s="5">
+        <v>10</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="5">
+        <v>14189111</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F18" s="5">
+        <v>19</v>
+      </c>
+      <c r="G18" s="5">
+        <v>10</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="5">
+        <v>900</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="5">
+        <v>14189113</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F19" s="5">
+        <v>19</v>
+      </c>
+      <c r="G19" s="5">
+        <v>10</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="5">
+        <v>900</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="5">
+        <v>14189117</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F20" s="5">
+        <v>19</v>
+      </c>
+      <c r="G20" s="5">
+        <v>15</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="5">
+        <v>14190286</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="5">
+        <v>685554</v>
+      </c>
+      <c r="F21" s="5">
+        <v>19</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5">
+        <v>4712003439</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K21" s="5">
+        <v>330</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="5">
+        <v>14191160</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F22" s="5">
+        <v>19</v>
+      </c>
+      <c r="G22" s="5">
+        <v>10</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="5">
+        <v>14191160</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="5">
+        <v>685605</v>
+      </c>
+      <c r="F23" s="5">
+        <v>19</v>
+      </c>
+      <c r="G23" s="5">
+        <v>10</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="5">
+        <v>14191164</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5">
+        <v>685553</v>
+      </c>
+      <c r="F24" s="5">
+        <v>5</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5">
+        <v>4728602128</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="5">
+        <v>14191179</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F25" s="5">
+        <v>19</v>
+      </c>
+      <c r="G25" s="5">
+        <v>5</v>
+      </c>
+      <c r="H25" s="5">
+        <v>4727501155</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="5">
+        <v>14191189</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F26" s="5">
+        <v>19</v>
+      </c>
+      <c r="G26" s="5">
+        <v>3</v>
+      </c>
+      <c r="H26" s="5">
+        <v>4729104510</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K26" s="5">
+        <v>450</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="5">
+        <v>14191213</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F27" s="5">
+        <v>19</v>
+      </c>
+      <c r="G27" s="5">
+        <v>4</v>
+      </c>
+      <c r="H27" s="5">
+        <v>4729401707</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K27" s="5">
+        <v>800</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="5">
+        <v>14191219</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F28" s="5">
+        <v>19</v>
+      </c>
+      <c r="G28" s="5">
+        <v>4</v>
+      </c>
+      <c r="H28" s="5">
+        <v>4727501151</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" s="5">
+        <v>800</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="5">
+        <v>14196078</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F29" s="5">
+        <v>19</v>
+      </c>
+      <c r="G29" s="5">
+        <v>4</v>
+      </c>
+      <c r="H29" s="5">
+        <v>4727501150</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K29" s="5">
+        <v>800</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="5">
+        <v>14196087</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F30" s="5">
+        <v>19</v>
+      </c>
+      <c r="G30" s="5">
+        <v>5</v>
+      </c>
+      <c r="H30" s="5">
+        <v>4729401707</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="5">
+        <v>14196118</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="5">
+        <v>685615</v>
+      </c>
+      <c r="F31" s="5">
+        <v>19</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2</v>
+      </c>
+      <c r="H31" s="5">
+        <v>4728701255</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="5">
+        <v>14196129</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="5">
+        <v>685615</v>
+      </c>
+      <c r="F32" s="5">
+        <v>19</v>
+      </c>
+      <c r="G32" s="5">
+        <v>6</v>
+      </c>
+      <c r="H32" s="5">
+        <v>4711400979</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="5">
+        <v>14196132</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="5">
+        <v>685615</v>
+      </c>
+      <c r="F33" s="5">
+        <v>19</v>
+      </c>
+      <c r="G33" s="5">
+        <v>3</v>
+      </c>
+      <c r="H33" s="5">
+        <v>4711400737</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="5">
+        <v>14196239</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5">
+        <v>685434</v>
+      </c>
+      <c r="F34" s="5">
+        <v>20</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5">
+        <v>4728701030</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K34" s="5">
+        <v>880</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="5">
+        <v>14197099</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="5">
+        <v>685421</v>
+      </c>
+      <c r="F35" s="5">
+        <v>19</v>
+      </c>
+      <c r="G35" s="5">
+        <v>5</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="5">
+        <v>14197157</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="5">
+        <v>685421</v>
+      </c>
+      <c r="F36" s="5">
+        <v>19</v>
+      </c>
+      <c r="G36" s="5">
+        <v>5</v>
+      </c>
+      <c r="H36" s="5">
+        <v>4712000859</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="5">
+        <v>14197356</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="5">
+        <v>685487</v>
+      </c>
+      <c r="F37" s="5">
+        <v>19</v>
+      </c>
+      <c r="G37" s="5">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5">
+        <v>4729110942</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="5">
+        <v>14197401</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="5">
+        <v>685434</v>
+      </c>
+      <c r="F38" s="5">
+        <v>19</v>
+      </c>
+      <c r="G38" s="5">
+        <v>4</v>
+      </c>
+      <c r="H38" s="5">
+        <v>4729110767</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="5">
+        <v>14197866</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="5">
+        <v>685484</v>
+      </c>
+      <c r="F39" s="5">
+        <v>19</v>
+      </c>
+      <c r="G39" s="5">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5">
+        <v>4711200746</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="5">
+        <v>14198026</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="5">
+        <v>685421</v>
+      </c>
+      <c r="F40" s="5">
+        <v>19</v>
+      </c>
+      <c r="G40" s="5">
+        <v>4</v>
+      </c>
+      <c r="H40" s="5">
+        <v>4729110067</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="5">
+        <v>14198033</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="5">
+        <v>685434</v>
+      </c>
+      <c r="F41" s="5">
+        <v>19</v>
+      </c>
+      <c r="G41" s="5">
+        <v>5</v>
+      </c>
+      <c r="H41" s="5">
+        <v>4721900207</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="5">
+        <v>14198045</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5">
+        <v>685421</v>
+      </c>
+      <c r="F42" s="5">
+        <v>19</v>
+      </c>
+      <c r="G42" s="5">
+        <v>10</v>
+      </c>
+      <c r="H42" s="5">
+        <v>4730502592</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="5">
+        <v>14198173</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="5">
+        <v>685421</v>
+      </c>
+      <c r="F43" s="5">
+        <v>19</v>
+      </c>
+      <c r="G43" s="5">
+        <v>10</v>
+      </c>
+      <c r="H43" s="5">
+        <v>4729107872</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="5">
+        <v>14198232</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="5">
+        <v>685421</v>
+      </c>
+      <c r="F44" s="5">
+        <v>19</v>
+      </c>
+      <c r="G44" s="5">
+        <v>10</v>
+      </c>
+      <c r="H44" s="5">
+        <v>4741420126</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" s="5">
+        <v>14198613</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="5">
+        <v>685556</v>
+      </c>
+      <c r="F45" s="5">
+        <v>19</v>
+      </c>
+      <c r="G45" s="5">
+        <v>2</v>
+      </c>
+      <c r="H45" s="5">
+        <v>4729106992</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="5">
+        <v>14198617</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="5">
+        <v>685401</v>
+      </c>
+      <c r="F46" s="5">
+        <v>19</v>
+      </c>
+      <c r="G46" s="5">
+        <v>87</v>
+      </c>
+      <c r="H46" s="5">
+        <v>4729105794</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="5">
+        <v>14198791</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="5">
+        <v>685703</v>
+      </c>
+      <c r="F47" s="5">
+        <v>19</v>
+      </c>
+      <c r="G47" s="5">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5">
+        <v>4710800349</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K47" s="5">
+        <v>600</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="5">
+        <v>14198799</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="5">
+        <v>685557</v>
+      </c>
+      <c r="F48" s="5">
+        <v>19</v>
+      </c>
+      <c r="G48" s="5">
+        <v>24</v>
+      </c>
+      <c r="H48" s="5">
+        <v>4722804942</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="5">
+        <v>14198807</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="5">
+        <v>685401</v>
+      </c>
+      <c r="F49" s="5">
+        <v>19</v>
+      </c>
+      <c r="G49" s="5">
+        <v>5</v>
+      </c>
+      <c r="H49" s="5">
+        <v>4712001569</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="5">
+        <v>14198812</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="5">
+        <v>685551</v>
+      </c>
+      <c r="F50" s="5">
+        <v>19</v>
+      </c>
+      <c r="G50" s="5">
+        <v>10</v>
+      </c>
+      <c r="H50" s="5">
+        <v>4730502260</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="5">
+        <v>14198825</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="5">
+        <v>685401</v>
+      </c>
+      <c r="F51" s="5">
+        <v>19</v>
+      </c>
+      <c r="G51" s="5">
+        <v>10</v>
+      </c>
+      <c r="H51" s="5">
+        <v>4729401660</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52" s="5">
+        <v>14198910</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="5">
+        <v>685401</v>
+      </c>
+      <c r="F52" s="5">
+        <v>19</v>
+      </c>
+      <c r="G52" s="5">
+        <v>10</v>
+      </c>
+      <c r="H52" s="5">
+        <v>4729111969</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="5">
+        <v>14198918</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="5">
+        <v>685556</v>
+      </c>
+      <c r="F53" s="5">
+        <v>19</v>
+      </c>
+      <c r="G53" s="5">
+        <v>2</v>
+      </c>
+      <c r="H53" s="5">
+        <v>4729108289</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="5">
+        <v>14198923</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="5">
+        <v>685551</v>
+      </c>
+      <c r="F54" s="5">
+        <v>19</v>
+      </c>
+      <c r="G54" s="5">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5">
+        <v>4729108428</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="L54" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C55" s="5">
+        <v>14198956</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="5">
+        <v>685552</v>
+      </c>
+      <c r="F55" s="5">
+        <v>19</v>
+      </c>
+      <c r="G55" s="5">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5">
+        <v>4710800277</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" s="5">
+        <v>14198969</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="5">
+        <v>685703</v>
+      </c>
+      <c r="F56" s="5">
+        <v>19</v>
+      </c>
+      <c r="G56" s="5">
+        <v>1</v>
+      </c>
+      <c r="H56" s="5">
+        <v>4710800349</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="5">
+        <v>14198973</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="5">
+        <v>685432</v>
+      </c>
+      <c r="F57" s="5">
+        <v>19</v>
+      </c>
+      <c r="G57" s="5">
+        <v>4</v>
+      </c>
+      <c r="H57" s="5">
+        <v>4728603152</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="5">
+        <v>14198973</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="5">
+        <v>685432</v>
+      </c>
+      <c r="F58" s="5">
+        <v>19</v>
+      </c>
+      <c r="G58" s="5">
+        <v>4</v>
+      </c>
+      <c r="H58" s="5">
+        <v>4728603152</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="L58" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="5">
+        <v>14198977</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" s="5">
+        <v>685487</v>
+      </c>
+      <c r="F59" s="5">
+        <v>20</v>
+      </c>
+      <c r="G59" s="5">
+        <v>5</v>
+      </c>
+      <c r="H59" s="5">
+        <v>4310800263</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="5">
+        <v>14198980</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="5">
+        <v>685411</v>
+      </c>
+      <c r="F60" s="5">
+        <v>20</v>
+      </c>
+      <c r="G60" s="5">
+        <v>5</v>
+      </c>
+      <c r="H60" s="5">
+        <v>4710800193</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="L60" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="5">
+        <v>14198981</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="5">
+        <v>685487</v>
+      </c>
+      <c r="F61" s="5">
+        <v>19</v>
+      </c>
+      <c r="G61" s="5">
+        <v>3</v>
+      </c>
+      <c r="H61" s="5">
+        <v>4710800032</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="5">
+        <v>14199104</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="5">
+        <v>685401</v>
+      </c>
+      <c r="F62" s="5">
+        <v>19</v>
+      </c>
+      <c r="G62" s="5">
+        <v>33</v>
+      </c>
+      <c r="H62" s="5">
+        <v>4712001852</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K62" s="5">
+        <v>660</v>
+      </c>
+      <c r="L62" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" s="5">
+        <v>14199124</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="5">
+        <v>685554</v>
+      </c>
+      <c r="F63" s="5">
+        <v>19</v>
+      </c>
+      <c r="G63" s="5">
+        <v>1</v>
+      </c>
+      <c r="H63" s="5">
+        <v>4729108746</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K63" s="5">
+        <v>400</v>
+      </c>
+      <c r="L63" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C64" s="5">
+        <v>14199170</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="5">
+        <v>685701</v>
+      </c>
+      <c r="F64" s="5">
+        <v>19</v>
+      </c>
+      <c r="G64" s="5">
+        <v>1</v>
+      </c>
+      <c r="H64" s="5">
+        <v>4729401944</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K64" s="5">
+        <v>300</v>
+      </c>
+      <c r="L64" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C65" s="5">
+        <v>14199721</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F65" s="5">
+        <v>19</v>
+      </c>
+      <c r="G65" s="5">
+        <v>4</v>
+      </c>
+      <c r="H65" s="5">
+        <v>4727501447</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="L65" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C66" s="5">
+        <v>14199736</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="5">
+        <v>685485</v>
+      </c>
+      <c r="F66" s="5">
+        <v>20</v>
+      </c>
+      <c r="G66" s="5">
+        <v>1</v>
+      </c>
+      <c r="H66" s="5">
+        <v>4712004463</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C67" s="5">
+        <v>14199789</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" s="5">
+        <v>685552</v>
+      </c>
+      <c r="F67" s="5">
+        <v>19</v>
+      </c>
+      <c r="G67" s="5">
+        <v>1</v>
+      </c>
+      <c r="H67" s="5">
+        <v>4710800212</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K67" s="5">
+        <v>600</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68" s="5">
+        <v>14201711</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" s="5">
+        <v>685608</v>
+      </c>
+      <c r="F68" s="5">
+        <v>19</v>
+      </c>
+      <c r="G68" s="5">
+        <v>2</v>
+      </c>
+      <c r="H68" s="5">
+        <v>4728602405</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L68" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C69" s="5">
+        <v>14202161</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" s="5">
+        <v>685705</v>
+      </c>
+      <c r="F69" s="5">
+        <v>5</v>
+      </c>
+      <c r="G69" s="5">
+        <v>10</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C70" s="5">
+        <v>14203084</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" s="5">
+        <v>685703</v>
+      </c>
+      <c r="F70" s="5">
+        <v>19</v>
+      </c>
+      <c r="G70" s="5">
+        <v>200</v>
+      </c>
+      <c r="H70" s="5">
+        <v>4719241071</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K70" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="L70" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C71" s="5">
+        <v>14203153</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" s="5">
+        <v>685556</v>
+      </c>
+      <c r="F71" s="5">
+        <v>5</v>
+      </c>
+      <c r="G71" s="5">
+        <v>3</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C72" s="5">
+        <v>14203508</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" s="5">
+        <v>685551</v>
+      </c>
+      <c r="F72" s="5">
+        <v>19</v>
+      </c>
+      <c r="G72" s="5">
+        <v>4</v>
+      </c>
+      <c r="H72" s="5">
+        <v>4712002045</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K72" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C73" s="5">
+        <v>14203511</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" s="5">
+        <v>685702</v>
+      </c>
+      <c r="F73" s="5">
+        <v>19</v>
+      </c>
+      <c r="G73" s="5">
+        <v>1</v>
+      </c>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K73" s="5">
+        <v>330</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C74" s="5">
+        <v>14204334</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" s="5">
+        <v>685434</v>
+      </c>
+      <c r="F74" s="5">
+        <v>19</v>
+      </c>
+      <c r="G74" s="5">
+        <v>6</v>
+      </c>
+      <c r="H74" s="5">
+        <v>4711201805</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K74" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="L74" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C75" s="5">
+        <v>14204368</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" s="5">
+        <v>685434</v>
+      </c>
+      <c r="F75" s="5">
+        <v>19</v>
+      </c>
+      <c r="G75" s="5">
+        <v>2</v>
+      </c>
+      <c r="H75" s="5">
+        <v>4729111359</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L75" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76" s="5">
+        <v>14205007</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" s="5">
+        <v>685412</v>
+      </c>
+      <c r="F76" s="5">
+        <v>19</v>
+      </c>
+      <c r="G76" s="5">
+        <v>10</v>
+      </c>
+      <c r="H76" s="5">
+        <v>4712001343</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="L76" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C77" s="5">
+        <v>14205014</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" s="5">
+        <v>685412</v>
+      </c>
+      <c r="F77" s="5">
+        <v>19</v>
+      </c>
+      <c r="G77" s="5">
+        <v>30</v>
+      </c>
+      <c r="H77" s="5">
+        <v>4728701264</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L77" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" s="5">
+        <v>14205067</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" s="5">
+        <v>685412</v>
+      </c>
+      <c r="F78" s="5">
+        <v>19</v>
+      </c>
+      <c r="G78" s="5">
+        <v>10</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K78" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L78" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C79" s="5">
+        <v>14205067</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" s="5">
+        <v>685412</v>
+      </c>
+      <c r="F79" s="5">
+        <v>19</v>
+      </c>
+      <c r="G79" s="5">
+        <v>10</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L79" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C80" s="5">
+        <v>14205640</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" s="5">
+        <v>685546</v>
+      </c>
+      <c r="F80" s="5">
+        <v>19</v>
+      </c>
+      <c r="G80" s="5">
+        <v>5</v>
+      </c>
+      <c r="H80" s="5">
+        <v>4710200987</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K80" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="L80" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81" s="5">
+        <v>14205643</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" s="5">
+        <v>685401</v>
+      </c>
+      <c r="F81" s="5">
+        <v>19</v>
+      </c>
+      <c r="G81" s="5">
+        <v>50</v>
+      </c>
+      <c r="H81" s="5">
+        <v>4711401012</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K81" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L81" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C82" s="5">
+        <v>14205644</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" s="5">
+        <v>685622</v>
+      </c>
+      <c r="F82" s="5">
+        <v>19</v>
+      </c>
+      <c r="G82" s="5">
+        <v>6</v>
+      </c>
+      <c r="H82" s="5">
+        <v>4729109351</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K82" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="L82" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83" s="5">
+        <v>14205646</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="5">
+        <v>685552</v>
+      </c>
+      <c r="F83" s="5">
+        <v>19</v>
+      </c>
+      <c r="G83" s="5">
+        <v>2</v>
+      </c>
+      <c r="H83" s="5">
+        <v>4710800277</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K83" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L83" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C84" s="5">
+        <v>14205648</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" s="5">
+        <v>685702</v>
+      </c>
+      <c r="F84" s="5">
+        <v>19</v>
+      </c>
+      <c r="G84" s="5">
+        <v>5</v>
+      </c>
+      <c r="H84" s="5">
+        <v>4711400977</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K84" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L84" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C85" s="5">
+        <v>14205649</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E85" s="5">
+        <v>685702</v>
+      </c>
+      <c r="F85" s="5">
+        <v>19</v>
+      </c>
+      <c r="G85" s="5">
+        <v>1</v>
+      </c>
+      <c r="H85" s="5">
+        <v>4711400977</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K85" s="5">
+        <v>550</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C86" s="5">
+        <v>14205779</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" s="5">
+        <v>685552</v>
+      </c>
+      <c r="F86" s="5">
+        <v>19</v>
+      </c>
+      <c r="G86" s="5">
+        <v>2</v>
+      </c>
+      <c r="H86" s="5">
+        <v>4718301625</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K86" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="L86" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C87" s="5">
+        <v>14205881</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" s="5">
+        <v>685704</v>
+      </c>
+      <c r="F87" s="5">
+        <v>5</v>
+      </c>
+      <c r="G87" s="5">
+        <v>10</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="L87" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C88" s="5">
+        <v>14206161</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" s="5">
+        <v>685485</v>
+      </c>
+      <c r="F88" s="5">
+        <v>19</v>
+      </c>
+      <c r="G88" s="5">
+        <v>2</v>
+      </c>
+      <c r="H88" s="5">
+        <v>4729401814</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K88" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L88" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C89" s="5">
+        <v>14206439</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" s="5">
+        <v>685486</v>
+      </c>
+      <c r="F89" s="5">
+        <v>19</v>
+      </c>
+      <c r="G89" s="5">
+        <v>2</v>
+      </c>
+      <c r="H89" s="5">
+        <v>4710101504</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K89" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="L89" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90" s="5">
+        <v>14206462</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" s="5">
+        <v>685487</v>
+      </c>
+      <c r="F90" s="5">
+        <v>19</v>
+      </c>
+      <c r="G90" s="5">
+        <v>23</v>
+      </c>
+      <c r="H90" s="5">
+        <v>4729400390</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K90" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="L90" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C91" s="5">
+        <v>14206475</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" s="5">
+        <v>685487</v>
+      </c>
+      <c r="F91" s="5">
+        <v>20</v>
+      </c>
+      <c r="G91" s="5">
+        <v>2</v>
+      </c>
+      <c r="H91" s="5">
+        <v>4710800032</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K91" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L91" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C92" s="5">
+        <v>14206475</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" s="5">
+        <v>685487</v>
+      </c>
+      <c r="F92" s="5">
+        <v>20</v>
+      </c>
+      <c r="G92" s="5">
+        <v>3</v>
+      </c>
+      <c r="H92" s="5">
+        <v>4710800002</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K92" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="L92" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C93" s="5">
+        <v>14206487</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E93" s="5">
+        <v>685485</v>
+      </c>
+      <c r="F93" s="5">
+        <v>19</v>
+      </c>
+      <c r="G93" s="5">
+        <v>10</v>
+      </c>
+      <c r="H93" s="5">
+        <v>4679720013</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K93" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="L93" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C94" s="5">
+        <v>14208021</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" s="5">
+        <v>685622</v>
+      </c>
+      <c r="F94" s="5">
+        <v>19</v>
+      </c>
+      <c r="G94" s="5">
+        <v>1</v>
+      </c>
+      <c r="H94" s="5">
+        <v>4718301751</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K94" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L94" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C95" s="5">
+        <v>14208029</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" s="5">
+        <v>685552</v>
+      </c>
+      <c r="F95" s="5">
+        <v>19</v>
+      </c>
+      <c r="G95" s="5">
+        <v>1</v>
+      </c>
+      <c r="H95" s="5">
+        <v>4728701085</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K95" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="L95" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C96" s="5">
+        <v>14208031</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E96" s="5">
+        <v>685552</v>
+      </c>
+      <c r="F96" s="5">
+        <v>19</v>
+      </c>
+      <c r="G96" s="5">
+        <v>2</v>
+      </c>
+      <c r="H96" s="5">
+        <v>4710800212</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K96" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L96" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C97" s="5">
+        <v>14208044</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" s="5">
+        <v>685541</v>
+      </c>
+      <c r="F97" s="5">
+        <v>19</v>
+      </c>
+      <c r="G97" s="5">
+        <v>4</v>
+      </c>
+      <c r="H97" s="5">
+        <v>4729401715</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K97" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="L97" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C98" s="5">
+        <v>14208384</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" s="5">
+        <v>685547</v>
+      </c>
+      <c r="F98" s="5">
+        <v>5</v>
+      </c>
+      <c r="G98" s="5">
+        <v>20</v>
+      </c>
+      <c r="H98" s="5">
+        <v>4722804907</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="K98" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="L98" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C99" s="5">
+        <v>14208738</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" s="5">
+        <v>685484</v>
+      </c>
+      <c r="F99" s="5">
+        <v>20</v>
+      </c>
+      <c r="G99" s="5">
+        <v>5</v>
+      </c>
+      <c r="H99" s="6">
+        <v>4310800263</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K99" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L99" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C100" s="5">
+        <v>14208911</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E100" s="5">
+        <v>685411</v>
+      </c>
+      <c r="F100" s="5">
+        <v>19</v>
+      </c>
+      <c r="G100" s="5">
+        <v>2</v>
+      </c>
+      <c r="H100" s="5">
+        <v>4710201043</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K100" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="L100" s="5" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A3FA9B-AC25-4989-8315-407E784FD4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8815FF70-AF72-41BC-9A0F-A03E1030CF00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -595,15 +595,6 @@
     <t>Status CN21</t>
   </si>
   <si>
-    <t>LP055085</t>
-  </si>
-  <si>
-    <t>LP055087</t>
-  </si>
-  <si>
-    <t>LP055097</t>
-  </si>
-  <si>
     <t>CAPA DE EXPULSOR</t>
   </si>
   <si>
@@ -616,147 +607,27 @@
     <t>6 060,00</t>
   </si>
   <si>
-    <t>LP055859</t>
-  </si>
-  <si>
-    <t>LP055086</t>
-  </si>
-  <si>
-    <t>LP055047</t>
-  </si>
-  <si>
-    <t>LP055092</t>
-  </si>
-  <si>
-    <t>LP055091</t>
-  </si>
-  <si>
-    <t>LP055089</t>
-  </si>
-  <si>
-    <t>LP055090</t>
-  </si>
-  <si>
-    <t>LP055088</t>
-  </si>
-  <si>
-    <t>LP055193</t>
-  </si>
-  <si>
-    <t>LP055061</t>
-  </si>
-  <si>
-    <t>LP055160</t>
-  </si>
-  <si>
-    <t>LP055239</t>
-  </si>
-  <si>
-    <t>LP055206</t>
-  </si>
-  <si>
-    <t>LP055204</t>
-  </si>
-  <si>
-    <t>LP055163</t>
-  </si>
-  <si>
-    <t>LP055156</t>
-  </si>
-  <si>
-    <t>LP055158</t>
-  </si>
-  <si>
-    <t>LP055164</t>
-  </si>
-  <si>
-    <t>LP055100</t>
-  </si>
-  <si>
-    <t>LP055060</t>
-  </si>
-  <si>
-    <t>LP055095</t>
-  </si>
-  <si>
-    <t>LP055208</t>
-  </si>
-  <si>
-    <t>LP055162</t>
-  </si>
-  <si>
-    <t>LP055161</t>
-  </si>
-  <si>
-    <t>LP055155</t>
-  </si>
-  <si>
-    <t>LP055099</t>
-  </si>
-  <si>
-    <t>LP055154</t>
-  </si>
-  <si>
     <t>CtP/MFE31</t>
   </si>
   <si>
-    <t>LP055411</t>
-  </si>
-  <si>
-    <t>LP055237</t>
-  </si>
-  <si>
-    <t>LP055614</t>
-  </si>
-  <si>
-    <t>LP055616</t>
-  </si>
-  <si>
-    <t>LP055393</t>
-  </si>
-  <si>
     <t>Dispositivo bloco de pressão</t>
   </si>
   <si>
-    <t>LP055613</t>
-  </si>
-  <si>
     <t>CtP/MFW11-B</t>
   </si>
   <si>
-    <t>LP055461</t>
-  </si>
-  <si>
-    <t>LP055437</t>
-  </si>
-  <si>
-    <t>LP055392</t>
-  </si>
-  <si>
-    <t>LP055612</t>
-  </si>
-  <si>
-    <t>LP055609</t>
-  </si>
-  <si>
     <t>Ponteira Blaichach</t>
   </si>
   <si>
     <t>1 050,00</t>
   </si>
   <si>
-    <t>LP055611</t>
-  </si>
-  <si>
     <t>Posição 4</t>
   </si>
   <si>
     <t>1 920,00</t>
   </si>
   <si>
-    <t>LP055610</t>
-  </si>
-  <si>
     <t>4781700221/31</t>
   </si>
   <si>
@@ -766,36 +637,12 @@
     <t>9 200,00</t>
   </si>
   <si>
-    <t>LP055637</t>
-  </si>
-  <si>
     <t>Disp. Robodril</t>
   </si>
   <si>
     <t>11 700,00</t>
   </si>
   <si>
-    <t>LP055631</t>
-  </si>
-  <si>
-    <t>LP055420</t>
-  </si>
-  <si>
-    <t>LP055415</t>
-  </si>
-  <si>
-    <t>LP055419</t>
-  </si>
-  <si>
-    <t>LP055416</t>
-  </si>
-  <si>
-    <t>LP055417</t>
-  </si>
-  <si>
-    <t>LP055418</t>
-  </si>
-  <si>
     <t>Pino UVA</t>
   </si>
   <si>
@@ -805,126 +652,42 @@
     <t>2 800,00</t>
   </si>
   <si>
-    <t>LP055898</t>
-  </si>
-  <si>
-    <t>LP055899</t>
-  </si>
-  <si>
-    <t>LP055430</t>
-  </si>
-  <si>
-    <t>LP055424</t>
-  </si>
-  <si>
-    <t>LP055434</t>
-  </si>
-  <si>
-    <t>LP055394</t>
-  </si>
-  <si>
-    <t>LP055432</t>
-  </si>
-  <si>
-    <t>LP055431</t>
-  </si>
-  <si>
-    <t>LP055428</t>
-  </si>
-  <si>
-    <t>LP055433</t>
-  </si>
-  <si>
-    <t>LP055429</t>
-  </si>
-  <si>
-    <t>LP055395</t>
-  </si>
-  <si>
-    <t>LP055396</t>
-  </si>
-  <si>
-    <t>LP055427</t>
-  </si>
-  <si>
     <t>DU 685421 Conexão de usinagem HE</t>
   </si>
   <si>
-    <t>LP055522</t>
-  </si>
-  <si>
-    <t>LP055462</t>
-  </si>
-  <si>
-    <t>LP055463</t>
-  </si>
-  <si>
-    <t>LP055436</t>
-  </si>
-  <si>
-    <t>LP055464</t>
-  </si>
-  <si>
     <t>DU 685434 Chapa d alimentação acabamen.</t>
   </si>
   <si>
     <t>1 320,00</t>
   </si>
   <si>
-    <t>LP055523</t>
-  </si>
-  <si>
     <t>DU 685434 Bico de refrigeração POSIÇÃO 1</t>
   </si>
   <si>
     <t>3 280,00</t>
   </si>
   <si>
-    <t>LP055524</t>
-  </si>
-  <si>
     <t>CtP/TEF1</t>
   </si>
   <si>
-    <t>LP055457</t>
-  </si>
-  <si>
     <t>encosto da thielenhaus</t>
   </si>
   <si>
-    <t>LP055934</t>
-  </si>
-  <si>
-    <t>LP055460</t>
-  </si>
-  <si>
-    <t>LP055450</t>
-  </si>
-  <si>
     <t>DU 685411 POS 1 Sistema d Alimen.Supfina</t>
   </si>
   <si>
     <t>3 560,00</t>
   </si>
   <si>
-    <t>LP055595</t>
-  </si>
-  <si>
     <t>DU 685411 POS 3 Sistema d Alimen.Supfina</t>
   </si>
   <si>
-    <t>LP055596</t>
-  </si>
-  <si>
     <t>DU 685411 POS23 Sistema d Alimen.Supfina</t>
   </si>
   <si>
     <t>10 360,00</t>
   </si>
   <si>
-    <t>LP055597</t>
-  </si>
-  <si>
     <t>23.02.2026</t>
   </si>
   <si>
@@ -934,48 +697,30 @@
     <t>Mandril rebolo Supfina - Fabricação</t>
   </si>
   <si>
-    <t>LP055636</t>
-  </si>
-  <si>
     <t>24.02.2026</t>
   </si>
   <si>
     <t>IP 685491 POSIÇÃO 8 bancada escovação.</t>
   </si>
   <si>
-    <t>LP055507</t>
-  </si>
-  <si>
     <t>DU 685412 POSIÇÃO 1 do pino Guiringuelli</t>
   </si>
   <si>
     <t>3 840,00</t>
   </si>
   <si>
-    <t>LP055519</t>
-  </si>
-  <si>
-    <t>LP007619-04-22</t>
-  </si>
-  <si>
     <t>Retrabalho da altura do magazine agulha</t>
   </si>
   <si>
     <t>JOSIANE OLIV</t>
   </si>
   <si>
-    <t>LP055513</t>
-  </si>
-  <si>
     <t>4729108882 POS1</t>
   </si>
   <si>
     <t>DU 685421 POSIÇÃO 1  do cabeçote AGIE</t>
   </si>
   <si>
-    <t>LP055517</t>
-  </si>
-  <si>
     <t>4729108882 POS7</t>
   </si>
   <si>
@@ -985,15 +730,9 @@
     <t>1 150,00</t>
   </si>
   <si>
-    <t>LP055518</t>
-  </si>
-  <si>
     <t>DU 685421 Conector ∅4/6</t>
   </si>
   <si>
-    <t>LP055521</t>
-  </si>
-  <si>
     <t>25.02.2026</t>
   </si>
   <si>
@@ -1003,45 +742,24 @@
     <t>DU 685421 Pino fixação bico S-POSIÇÃO 2</t>
   </si>
   <si>
-    <t>LP055536</t>
-  </si>
-  <si>
     <t>IP 685481 Castanha studer Válvula</t>
   </si>
   <si>
-    <t>LP055540</t>
-  </si>
-  <si>
     <t>Castanha da placa</t>
   </si>
   <si>
     <t>4 560,00</t>
   </si>
   <si>
-    <t>LP055556</t>
-  </si>
-  <si>
     <t>GARRA POSIÇÃO 13</t>
   </si>
   <si>
     <t>2 440,00</t>
   </si>
   <si>
-    <t>LP055554</t>
-  </si>
-  <si>
     <t>Dispositivo DHK</t>
   </si>
   <si>
-    <t>LP055553</t>
-  </si>
-  <si>
-    <t>LP055555</t>
-  </si>
-  <si>
-    <t>LP055552</t>
-  </si>
-  <si>
     <t>4710900878 P01 F2</t>
   </si>
   <si>
@@ -1054,63 +772,24 @@
     <t>CtP/MFW13-A</t>
   </si>
   <si>
-    <t>LP055537</t>
-  </si>
-  <si>
-    <t>LP055546</t>
-  </si>
-  <si>
-    <t>LP055551</t>
-  </si>
-  <si>
-    <t>LP055550</t>
-  </si>
-  <si>
     <t>Cone da montagem</t>
   </si>
   <si>
-    <t>LP055549</t>
-  </si>
-  <si>
     <t>DU 685411 Pinça d Alimentação Haste Chei</t>
   </si>
   <si>
     <t>2 720,00</t>
   </si>
   <si>
-    <t>LP055526</t>
-  </si>
-  <si>
     <t>IP 685484 Rebolo borazon Pistão A/P</t>
   </si>
   <si>
-    <t>LP055541</t>
-  </si>
-  <si>
-    <t>LP055542</t>
-  </si>
-  <si>
-    <t>LP055544</t>
-  </si>
-  <si>
-    <t>LP055545</t>
-  </si>
-  <si>
-    <t>LP055547</t>
-  </si>
-  <si>
-    <t>LP055548</t>
-  </si>
-  <si>
     <t>4728700097 POS 5</t>
   </si>
   <si>
     <t>IP 685484 Prisma de apoio pistão P</t>
   </si>
   <si>
-    <t>LP055543</t>
-  </si>
-  <si>
     <t>26.02.2026</t>
   </si>
   <si>
@@ -1120,15 +799,9 @@
     <t>1 500,00</t>
   </si>
   <si>
-    <t>LP055534</t>
-  </si>
-  <si>
     <t>DU 685421 Guia de eletrodo AGIEs</t>
   </si>
   <si>
-    <t>LP055535</t>
-  </si>
-  <si>
     <t>Base completa - Todas posições</t>
   </si>
   <si>
@@ -1141,27 +814,15 @@
     <t>8 300,00</t>
   </si>
   <si>
-    <t>LP055575</t>
-  </si>
-  <si>
     <t>9 960,00</t>
   </si>
   <si>
-    <t>LP055576</t>
-  </si>
-  <si>
     <t>DU 685411 Garra de alimentação HTT 3362</t>
   </si>
   <si>
-    <t>LP055530</t>
-  </si>
-  <si>
     <t>DU 685411 Garra de alimentação HTT 3352</t>
   </si>
   <si>
-    <t>LP055531</t>
-  </si>
-  <si>
     <t>4729107609 POS 9</t>
   </si>
   <si>
@@ -1171,18 +832,12 @@
     <t>1 780,00</t>
   </si>
   <si>
-    <t>LP055629</t>
-  </si>
-  <si>
     <t>4729107609 POS 12</t>
   </si>
   <si>
     <t>IP 685485 POSIÇÃO 12 Sistema de aliment.</t>
   </si>
   <si>
-    <t>LP055630</t>
-  </si>
-  <si>
     <t>27.02.2026</t>
   </si>
   <si>
@@ -1192,108 +847,54 @@
     <t>IP 685010 Borracha de vedação ATEQ POS11</t>
   </si>
   <si>
-    <t>LP055625</t>
-  </si>
-  <si>
     <t>IP 685482 Eletrodo ecm corpo CRIN/LE</t>
   </si>
   <si>
-    <t>LP055626</t>
-  </si>
-  <si>
     <t>IP 685482 Eletrodo POS 1 ecm corpo CRIN</t>
   </si>
   <si>
-    <t>LP055627</t>
-  </si>
-  <si>
     <t>DU 685434 Garra supfina Turquia acabamen</t>
   </si>
   <si>
     <t>4 080,00</t>
   </si>
   <si>
-    <t>LP055570</t>
-  </si>
-  <si>
     <t>Parafuso Robodril posição 03</t>
   </si>
   <si>
-    <t>LP055622</t>
-  </si>
-  <si>
     <t>Suporte do alimentador</t>
   </si>
   <si>
     <t>3 690,00</t>
   </si>
   <si>
-    <t>LP055638</t>
-  </si>
-  <si>
     <t>DU 685434 Pino Centralizador Lavador.Glu</t>
   </si>
   <si>
-    <t>LP055571</t>
-  </si>
-  <si>
     <t>DU 685434 Pino posicionador lavadora Glu</t>
   </si>
   <si>
     <t>3 200,00</t>
   </si>
   <si>
-    <t>LP055572</t>
-  </si>
-  <si>
     <t>DU 685433 Arruela bancada de montag Bico</t>
   </si>
   <si>
-    <t>LP055569</t>
-  </si>
-  <si>
     <t>Porta bucha</t>
   </si>
   <si>
-    <t>LP055620</t>
-  </si>
-  <si>
     <t>DU 685411 Pino de aliment. Nomyline 4mm</t>
   </si>
   <si>
-    <t>LP055581</t>
-  </si>
-  <si>
-    <t>LP055619</t>
-  </si>
-  <si>
-    <t>LP055621</t>
-  </si>
-  <si>
     <t>IP 685072 Pinça CIL P7/P8/R/TICs  ⌀12</t>
   </si>
   <si>
-    <t>LP055623</t>
-  </si>
-  <si>
     <t>IP 685485 Arrastador de pallet Brunidora</t>
   </si>
   <si>
-    <t>LP055624</t>
-  </si>
-  <si>
     <t>IP 685485 Vareta de presença Brunidoras.</t>
   </si>
   <si>
-    <t>LP055580</t>
-  </si>
-  <si>
-    <t>LP055618</t>
-  </si>
-  <si>
-    <t>LP055617</t>
-  </si>
-  <si>
     <t>ANEXO</t>
   </si>
   <si>
@@ -1303,9 +904,6 @@
     <t>DONI/VELLUD</t>
   </si>
   <si>
-    <t>LP055589</t>
-  </si>
-  <si>
     <t>28.02.2026</t>
   </si>
   <si>
@@ -1315,39 +913,21 @@
     <t>1 600,00</t>
   </si>
   <si>
-    <t>LP055600</t>
-  </si>
-  <si>
-    <t>LP055628</t>
-  </si>
-  <si>
     <t>12 850,00</t>
   </si>
   <si>
-    <t>LP055687</t>
-  </si>
-  <si>
     <t>Dispositivo posição 01</t>
   </si>
   <si>
     <t>3 720,00</t>
   </si>
   <si>
-    <t>LP055742</t>
-  </si>
-  <si>
     <t>TAGS POSIÇÃO 02</t>
   </si>
   <si>
-    <t>LP055598</t>
-  </si>
-  <si>
     <t>TAGS POSIÇÃO 01</t>
   </si>
   <si>
-    <t>LP055599</t>
-  </si>
-  <si>
     <t>02.03.2026</t>
   </si>
   <si>
@@ -1631,6 +1211,426 @@
   </si>
   <si>
     <t>LP-055910</t>
+  </si>
+  <si>
+    <t>LP-055085</t>
+  </si>
+  <si>
+    <t>LP-055087</t>
+  </si>
+  <si>
+    <t>LP-055097</t>
+  </si>
+  <si>
+    <t>LP-055859</t>
+  </si>
+  <si>
+    <t>LP-055086</t>
+  </si>
+  <si>
+    <t>LP-055047</t>
+  </si>
+  <si>
+    <t>LP-055092</t>
+  </si>
+  <si>
+    <t>LP-055091</t>
+  </si>
+  <si>
+    <t>LP-055089</t>
+  </si>
+  <si>
+    <t>LP-055090</t>
+  </si>
+  <si>
+    <t>LP-055088</t>
+  </si>
+  <si>
+    <t>LP-055193</t>
+  </si>
+  <si>
+    <t>LP-055061</t>
+  </si>
+  <si>
+    <t>LP-055160</t>
+  </si>
+  <si>
+    <t>LP-055239</t>
+  </si>
+  <si>
+    <t>LP-055206</t>
+  </si>
+  <si>
+    <t>LP-055204</t>
+  </si>
+  <si>
+    <t>LP-055163</t>
+  </si>
+  <si>
+    <t>LP-055156</t>
+  </si>
+  <si>
+    <t>LP-055158</t>
+  </si>
+  <si>
+    <t>LP-055164</t>
+  </si>
+  <si>
+    <t>LP-055100</t>
+  </si>
+  <si>
+    <t>LP-055060</t>
+  </si>
+  <si>
+    <t>LP-055095</t>
+  </si>
+  <si>
+    <t>LP-055208</t>
+  </si>
+  <si>
+    <t>LP-055162</t>
+  </si>
+  <si>
+    <t>LP-055161</t>
+  </si>
+  <si>
+    <t>LP-055155</t>
+  </si>
+  <si>
+    <t>LP-055099</t>
+  </si>
+  <si>
+    <t>LP-055154</t>
+  </si>
+  <si>
+    <t>LP-055411</t>
+  </si>
+  <si>
+    <t>LP-055237</t>
+  </si>
+  <si>
+    <t>LP-055614</t>
+  </si>
+  <si>
+    <t>LP-055616</t>
+  </si>
+  <si>
+    <t>LP-055393</t>
+  </si>
+  <si>
+    <t>LP-055613</t>
+  </si>
+  <si>
+    <t>LP-055461</t>
+  </si>
+  <si>
+    <t>LP-055437</t>
+  </si>
+  <si>
+    <t>LP-055392</t>
+  </si>
+  <si>
+    <t>LP-055612</t>
+  </si>
+  <si>
+    <t>LP-055609</t>
+  </si>
+  <si>
+    <t>LP-055611</t>
+  </si>
+  <si>
+    <t>LP-055610</t>
+  </si>
+  <si>
+    <t>LP-055637</t>
+  </si>
+  <si>
+    <t>LP-055631</t>
+  </si>
+  <si>
+    <t>LP-055420</t>
+  </si>
+  <si>
+    <t>LP-055415</t>
+  </si>
+  <si>
+    <t>LP-055419</t>
+  </si>
+  <si>
+    <t>LP-055416</t>
+  </si>
+  <si>
+    <t>LP-055417</t>
+  </si>
+  <si>
+    <t>LP-055418</t>
+  </si>
+  <si>
+    <t>LP-055898</t>
+  </si>
+  <si>
+    <t>LP-055899</t>
+  </si>
+  <si>
+    <t>LP-055430</t>
+  </si>
+  <si>
+    <t>LP-055424</t>
+  </si>
+  <si>
+    <t>LP-055434</t>
+  </si>
+  <si>
+    <t>LP-055394</t>
+  </si>
+  <si>
+    <t>LP-055432</t>
+  </si>
+  <si>
+    <t>LP-055431</t>
+  </si>
+  <si>
+    <t>LP-055428</t>
+  </si>
+  <si>
+    <t>LP-055433</t>
+  </si>
+  <si>
+    <t>LP-055429</t>
+  </si>
+  <si>
+    <t>LP-055395</t>
+  </si>
+  <si>
+    <t>LP-055396</t>
+  </si>
+  <si>
+    <t>LP-055427</t>
+  </si>
+  <si>
+    <t>LP-055522</t>
+  </si>
+  <si>
+    <t>LP-055462</t>
+  </si>
+  <si>
+    <t>LP-055463</t>
+  </si>
+  <si>
+    <t>LP-055436</t>
+  </si>
+  <si>
+    <t>LP-055464</t>
+  </si>
+  <si>
+    <t>LP-055523</t>
+  </si>
+  <si>
+    <t>LP-055524</t>
+  </si>
+  <si>
+    <t>LP-055457</t>
+  </si>
+  <si>
+    <t>LP-055934</t>
+  </si>
+  <si>
+    <t>LP-055460</t>
+  </si>
+  <si>
+    <t>LP-055450</t>
+  </si>
+  <si>
+    <t>LP-055595</t>
+  </si>
+  <si>
+    <t>LP-055596</t>
+  </si>
+  <si>
+    <t>LP-055597</t>
+  </si>
+  <si>
+    <t>LP-055636</t>
+  </si>
+  <si>
+    <t>LP-055507</t>
+  </si>
+  <si>
+    <t>LP-055519</t>
+  </si>
+  <si>
+    <t>LP-007619-04-22</t>
+  </si>
+  <si>
+    <t>LP-055513</t>
+  </si>
+  <si>
+    <t>LP-055517</t>
+  </si>
+  <si>
+    <t>LP-055518</t>
+  </si>
+  <si>
+    <t>LP-055521</t>
+  </si>
+  <si>
+    <t>LP-055536</t>
+  </si>
+  <si>
+    <t>LP-055540</t>
+  </si>
+  <si>
+    <t>LP-055556</t>
+  </si>
+  <si>
+    <t>LP-055554</t>
+  </si>
+  <si>
+    <t>LP-055553</t>
+  </si>
+  <si>
+    <t>LP-055555</t>
+  </si>
+  <si>
+    <t>LP-055552</t>
+  </si>
+  <si>
+    <t>LP-055537</t>
+  </si>
+  <si>
+    <t>LP-055546</t>
+  </si>
+  <si>
+    <t>LP-055551</t>
+  </si>
+  <si>
+    <t>LP-055550</t>
+  </si>
+  <si>
+    <t>LP-055549</t>
+  </si>
+  <si>
+    <t>LP-055526</t>
+  </si>
+  <si>
+    <t>LP-055541</t>
+  </si>
+  <si>
+    <t>LP-055542</t>
+  </si>
+  <si>
+    <t>LP-055544</t>
+  </si>
+  <si>
+    <t>LP-055545</t>
+  </si>
+  <si>
+    <t>LP-055547</t>
+  </si>
+  <si>
+    <t>LP-055548</t>
+  </si>
+  <si>
+    <t>LP-055543</t>
+  </si>
+  <si>
+    <t>LP-055534</t>
+  </si>
+  <si>
+    <t>LP-055535</t>
+  </si>
+  <si>
+    <t>LP-055575</t>
+  </si>
+  <si>
+    <t>LP-055576</t>
+  </si>
+  <si>
+    <t>LP-055530</t>
+  </si>
+  <si>
+    <t>LP-055531</t>
+  </si>
+  <si>
+    <t>LP-055629</t>
+  </si>
+  <si>
+    <t>LP-055630</t>
+  </si>
+  <si>
+    <t>LP-055625</t>
+  </si>
+  <si>
+    <t>LP-055626</t>
+  </si>
+  <si>
+    <t>LP-055627</t>
+  </si>
+  <si>
+    <t>LP-055570</t>
+  </si>
+  <si>
+    <t>LP-055622</t>
+  </si>
+  <si>
+    <t>LP-055638</t>
+  </si>
+  <si>
+    <t>LP-055571</t>
+  </si>
+  <si>
+    <t>LP-055572</t>
+  </si>
+  <si>
+    <t>LP-055569</t>
+  </si>
+  <si>
+    <t>LP-055620</t>
+  </si>
+  <si>
+    <t>LP-055581</t>
+  </si>
+  <si>
+    <t>LP-055619</t>
+  </si>
+  <si>
+    <t>LP-055621</t>
+  </si>
+  <si>
+    <t>LP-055623</t>
+  </si>
+  <si>
+    <t>LP-055624</t>
+  </si>
+  <si>
+    <t>LP-055580</t>
+  </si>
+  <si>
+    <t>LP-055618</t>
+  </si>
+  <si>
+    <t>LP-055617</t>
+  </si>
+  <si>
+    <t>LP-055589</t>
+  </si>
+  <si>
+    <t>LP-055600</t>
+  </si>
+  <si>
+    <t>LP-055628</t>
+  </si>
+  <si>
+    <t>LP-055687</t>
+  </si>
+  <si>
+    <t>LP-055742</t>
+  </si>
+  <si>
+    <t>LP-055598</t>
+  </si>
+  <si>
+    <t>LP-055599</t>
   </si>
 </sst>
 </file>
@@ -3025,7 +3025,7 @@
         <v>82</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>191</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -3066,7 +3066,7 @@
         <v>84</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>192</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -3107,7 +3107,7 @@
         <v>86</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>193</v>
+        <v>399</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -3136,19 +3136,19 @@
         <v>4712001238</v>
       </c>
       <c r="I26" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="L26" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="J26" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>197</v>
-      </c>
       <c r="M26" s="5" t="s">
-        <v>198</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -3189,7 +3189,7 @@
         <v>88</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>199</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -3230,7 +3230,7 @@
         <v>91</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>200</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -3271,7 +3271,7 @@
         <v>93</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>201</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -3312,7 +3312,7 @@
         <v>33</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>202</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -3353,7 +3353,7 @@
         <v>96</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>203</v>
+        <v>405</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -3394,7 +3394,7 @@
         <v>98</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>204</v>
+        <v>406</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -3435,7 +3435,7 @@
         <v>100</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>205</v>
+        <v>407</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
@@ -3476,7 +3476,7 @@
         <v>103</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>206</v>
+        <v>408</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -3517,7 +3517,7 @@
         <v>105</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>207</v>
+        <v>409</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -3558,7 +3558,7 @@
         <v>600</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>208</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -3599,7 +3599,7 @@
         <v>108</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>209</v>
+        <v>411</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -3640,7 +3640,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>210</v>
+        <v>412</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -3681,7 +3681,7 @@
         <v>112</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>211</v>
+        <v>413</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -3722,7 +3722,7 @@
         <v>114</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>212</v>
+        <v>414</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -3763,7 +3763,7 @@
         <v>112</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>213</v>
+        <v>415</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -3804,7 +3804,7 @@
         <v>41</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>214</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
@@ -3845,7 +3845,7 @@
         <v>103</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>215</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
@@ -3886,7 +3886,7 @@
         <v>68</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>216</v>
+        <v>418</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
@@ -3927,7 +3927,7 @@
         <v>112</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>217</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
@@ -3968,7 +3968,7 @@
         <v>103</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>218</v>
+        <v>420</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
@@ -4009,7 +4009,7 @@
         <v>660</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>219</v>
+        <v>421</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
@@ -4050,7 +4050,7 @@
         <v>400</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>220</v>
+        <v>422</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
@@ -4091,7 +4091,7 @@
         <v>300</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>221</v>
+        <v>423</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
@@ -4132,7 +4132,7 @@
         <v>124</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>222</v>
+        <v>424</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -4173,7 +4173,7 @@
         <v>126</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>223</v>
+        <v>425</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -4214,7 +4214,7 @@
         <v>600</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>224</v>
+        <v>426</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -4249,13 +4249,13 @@
         <v>129</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>82</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>226</v>
+        <v>427</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -4296,7 +4296,7 @@
         <v>134</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>227</v>
+        <v>428</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -4337,7 +4337,7 @@
         <v>600</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>228</v>
+        <v>429</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
@@ -4378,7 +4378,7 @@
         <v>600</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>229</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
@@ -4419,7 +4419,7 @@
         <v>137</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>230</v>
+        <v>431</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -4448,7 +4448,7 @@
         <v>4723000024</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>58</v>
@@ -4460,7 +4460,7 @@
         <v>33</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>232</v>
+        <v>432</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -4495,13 +4495,13 @@
         <v>140</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>16</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>234</v>
+        <v>433</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -4542,7 +4542,7 @@
         <v>143</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>235</v>
+        <v>434</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -4581,7 +4581,7 @@
         <v>330</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>236</v>
+        <v>435</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -4622,7 +4622,7 @@
         <v>600</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>237</v>
+        <v>436</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -4663,7 +4663,7 @@
         <v>600</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>238</v>
+        <v>437</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
         <v>4729107684</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>239</v>
+        <v>198</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>58</v>
@@ -4701,10 +4701,10 @@
         <v>185</v>
       </c>
       <c r="L64" s="5" t="s">
-        <v>240</v>
+        <v>199</v>
       </c>
       <c r="M64" s="5" t="s">
-        <v>241</v>
+        <v>438</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -4733,7 +4733,7 @@
         <v>4728800293</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>58</v>
@@ -4742,10 +4742,10 @@
         <v>185</v>
       </c>
       <c r="L65" s="5" t="s">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="M65" s="5" t="s">
-        <v>244</v>
+        <v>439</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
@@ -4771,10 +4771,10 @@
         <v>10</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>58</v>
@@ -4783,10 +4783,10 @@
         <v>185</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>248</v>
+        <v>440</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -4815,7 +4815,7 @@
         <v>4727501921</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>58</v>
@@ -4824,10 +4824,10 @@
         <v>185</v>
       </c>
       <c r="L67" s="5" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="M67" s="5" t="s">
-        <v>251</v>
+        <v>441</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -4868,7 +4868,7 @@
         <v>147</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>252</v>
+        <v>442</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -4909,7 +4909,7 @@
         <v>103</v>
       </c>
       <c r="M69" s="5" t="s">
-        <v>253</v>
+        <v>443</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>137</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>254</v>
+        <v>444</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
@@ -4991,7 +4991,7 @@
         <v>68</v>
       </c>
       <c r="M71" s="5" t="s">
-        <v>255</v>
+        <v>445</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -5032,7 +5032,7 @@
         <v>68</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>256</v>
+        <v>446</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -5073,7 +5073,7 @@
         <v>68</v>
       </c>
       <c r="M73" s="5" t="s">
-        <v>257</v>
+        <v>447</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -5102,19 +5102,19 @@
         <v>4710201197</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="K74" s="5" t="s">
         <v>186</v>
       </c>
       <c r="L74" s="5" t="s">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="M74" s="5" t="s">
-        <v>261</v>
+        <v>448</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -5143,19 +5143,19 @@
         <v>4710201155</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="K75" s="5" t="s">
         <v>186</v>
       </c>
       <c r="L75" s="5" t="s">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="M75" s="5" t="s">
-        <v>262</v>
+        <v>449</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -5196,7 +5196,7 @@
         <v>157</v>
       </c>
       <c r="M76" s="5" t="s">
-        <v>263</v>
+        <v>450</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -5237,7 +5237,7 @@
         <v>33</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>264</v>
+        <v>451</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -5278,7 +5278,7 @@
         <v>160</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>265</v>
+        <v>452</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -5319,7 +5319,7 @@
         <v>41</v>
       </c>
       <c r="M79" s="5" t="s">
-        <v>266</v>
+        <v>453</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -5360,7 +5360,7 @@
         <v>163</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>267</v>
+        <v>454</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -5401,7 +5401,7 @@
         <v>550</v>
       </c>
       <c r="M81" s="5" t="s">
-        <v>268</v>
+        <v>455</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
@@ -5442,7 +5442,7 @@
         <v>166</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>269</v>
+        <v>456</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -5483,7 +5483,7 @@
         <v>33</v>
       </c>
       <c r="M83" s="5" t="s">
-        <v>270</v>
+        <v>457</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -5524,7 +5524,7 @@
         <v>172</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>271</v>
+        <v>458</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -5565,7 +5565,7 @@
         <v>41</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>272</v>
+        <v>459</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -5606,7 +5606,7 @@
         <v>173</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>273</v>
+        <v>460</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -5647,7 +5647,7 @@
         <v>175</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>274</v>
+        <v>461</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -5676,7 +5676,7 @@
         <v>4712001379</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>37</v>
@@ -5688,7 +5688,7 @@
         <v>600</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>276</v>
+        <v>462</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
@@ -5729,7 +5729,7 @@
         <v>163</v>
       </c>
       <c r="M89" s="5" t="s">
-        <v>277</v>
+        <v>463</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>126</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>278</v>
+        <v>464</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -5811,7 +5811,7 @@
         <v>41</v>
       </c>
       <c r="M91" s="5" t="s">
-        <v>279</v>
+        <v>465</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -5852,7 +5852,7 @@
         <v>170</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>280</v>
+        <v>466</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -5881,7 +5881,7 @@
         <v>4711200727</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>281</v>
+        <v>211</v>
       </c>
       <c r="J93" s="5" t="s">
         <v>37</v>
@@ -5890,10 +5890,10 @@
         <v>185</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="M93" s="5" t="s">
-        <v>283</v>
+        <v>467</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -5922,7 +5922,7 @@
         <v>4712002037</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>284</v>
+        <v>213</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>37</v>
@@ -5931,10 +5931,10 @@
         <v>185</v>
       </c>
       <c r="L94" s="5" t="s">
-        <v>285</v>
+        <v>214</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>286</v>
+        <v>468</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -5969,13 +5969,13 @@
         <v>180</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="L95" s="5" t="s">
         <v>181</v>
       </c>
       <c r="M95" s="5" t="s">
-        <v>288</v>
+        <v>469</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -6004,10 +6004,10 @@
         <v>4711201805</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>289</v>
+        <v>216</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K96" s="5" t="s">
         <v>186</v>
@@ -6016,7 +6016,7 @@
         <v>147</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>290</v>
+        <v>470</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -6057,7 +6057,7 @@
         <v>68</v>
       </c>
       <c r="M97" s="5" t="s">
-        <v>291</v>
+        <v>471</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
@@ -6098,7 +6098,7 @@
         <v>143</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>292</v>
+        <v>472</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -6127,7 +6127,7 @@
         <v>4729105131</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>37</v>
@@ -6136,10 +6136,10 @@
         <v>185</v>
       </c>
       <c r="L99" s="5" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="M99" s="5" t="s">
-        <v>295</v>
+        <v>473</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
@@ -6168,7 +6168,7 @@
         <v>4729105131</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>296</v>
+        <v>219</v>
       </c>
       <c r="J100" s="5" t="s">
         <v>37</v>
@@ -6180,7 +6180,7 @@
         <v>150</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>297</v>
+        <v>474</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
@@ -6209,7 +6209,7 @@
         <v>4729105131</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>298</v>
+        <v>220</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>37</v>
@@ -6218,18 +6218,18 @@
         <v>185</v>
       </c>
       <c r="L101" s="5" t="s">
-        <v>299</v>
+        <v>221</v>
       </c>
       <c r="M101" s="5" t="s">
-        <v>300</v>
+        <v>475</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>301</v>
+        <v>222</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C102" s="5">
         <v>14209967</v>
@@ -6250,7 +6250,7 @@
         <v>4710201184</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>303</v>
+        <v>224</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>15</v>
@@ -6262,15 +6262,15 @@
         <v>160</v>
       </c>
       <c r="M102" s="5" t="s">
-        <v>304</v>
+        <v>476</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>305</v>
+        <v>225</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C103" s="5">
         <v>14210518</v>
@@ -6291,7 +6291,7 @@
         <v>4711202059</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c r="J103" s="5" t="s">
         <v>37</v>
@@ -6303,15 +6303,15 @@
         <v>360</v>
       </c>
       <c r="M103" s="5" t="s">
-        <v>307</v>
+        <v>477</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>305</v>
+        <v>225</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C104" s="5">
         <v>14210621</v>
@@ -6332,7 +6332,7 @@
         <v>4718301283</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>308</v>
+        <v>227</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>37</v>
@@ -6341,18 +6341,18 @@
         <v>185</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>309</v>
+        <v>228</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>310</v>
+        <v>478</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>305</v>
+        <v>225</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C105" s="5">
         <v>14210653</v>
@@ -6361,7 +6361,7 @@
         <v>14</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>311</v>
+        <v>479</v>
       </c>
       <c r="F105" s="5">
         <v>5</v>
@@ -6373,10 +6373,10 @@
         <v>4718300337</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>312</v>
+        <v>229</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>313</v>
+        <v>230</v>
       </c>
       <c r="K105" s="5" t="s">
         <v>186</v>
@@ -6385,15 +6385,15 @@
         <v>166</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>314</v>
+        <v>480</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>305</v>
+        <v>225</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C106" s="5">
         <v>14210666</v>
@@ -6411,10 +6411,10 @@
         <v>2</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>315</v>
+        <v>231</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>316</v>
+        <v>232</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>37</v>
@@ -6426,15 +6426,15 @@
         <v>143</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>317</v>
+        <v>481</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>305</v>
+        <v>225</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C107" s="5">
         <v>14210666</v>
@@ -6452,10 +6452,10 @@
         <v>5</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>318</v>
+        <v>233</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>37</v>
@@ -6464,18 +6464,18 @@
         <v>185</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>320</v>
+        <v>235</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>321</v>
+        <v>482</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>305</v>
+        <v>225</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C108" s="5">
         <v>14210794</v>
@@ -6496,7 +6496,7 @@
         <v>4729110120</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>322</v>
+        <v>236</v>
       </c>
       <c r="J108" s="5" t="s">
         <v>37</v>
@@ -6508,15 +6508,15 @@
         <v>820</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>323</v>
+        <v>483</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C109" s="5">
         <v>14211272</v>
@@ -6534,10 +6534,10 @@
         <v>10</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>325</v>
+        <v>238</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>326</v>
+        <v>239</v>
       </c>
       <c r="J109" s="5" t="s">
         <v>37</v>
@@ -6549,15 +6549,15 @@
         <v>126</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>327</v>
+        <v>484</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C110" s="5">
         <v>14211388</v>
@@ -6578,7 +6578,7 @@
         <v>4711400231</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>328</v>
+        <v>240</v>
       </c>
       <c r="J110" s="5" t="s">
         <v>37</v>
@@ -6587,18 +6587,18 @@
         <v>185</v>
       </c>
       <c r="L110" s="5" t="s">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>329</v>
+        <v>485</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C111" s="5">
         <v>14211404</v>
@@ -6619,7 +6619,7 @@
         <v>4711400931</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>50</v>
@@ -6628,18 +6628,18 @@
         <v>185</v>
       </c>
       <c r="L111" s="5" t="s">
-        <v>331</v>
+        <v>242</v>
       </c>
       <c r="M111" s="5" t="s">
-        <v>332</v>
+        <v>486</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C112" s="5">
         <v>14211411</v>
@@ -6660,7 +6660,7 @@
         <v>4729109063</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>333</v>
+        <v>243</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>50</v>
@@ -6669,18 +6669,18 @@
         <v>185</v>
       </c>
       <c r="L112" s="5" t="s">
-        <v>334</v>
+        <v>244</v>
       </c>
       <c r="M112" s="5" t="s">
-        <v>335</v>
+        <v>487</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C113" s="5">
         <v>14211435</v>
@@ -6701,7 +6701,7 @@
         <v>4729401707</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>336</v>
+        <v>245</v>
       </c>
       <c r="J113" s="5" t="s">
         <v>50</v>
@@ -6713,15 +6713,15 @@
         <v>800</v>
       </c>
       <c r="M113" s="5" t="s">
-        <v>337</v>
+        <v>488</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C114" s="5">
         <v>14211440</v>
@@ -6754,15 +6754,15 @@
         <v>41</v>
       </c>
       <c r="M114" s="5" t="s">
-        <v>338</v>
+        <v>489</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C115" s="5">
         <v>14211447</v>
@@ -6795,15 +6795,15 @@
         <v>600</v>
       </c>
       <c r="M115" s="5" t="s">
-        <v>339</v>
+        <v>490</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C116" s="5">
         <v>14211453</v>
@@ -6821,30 +6821,30 @@
         <v>10</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>340</v>
+        <v>246</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>341</v>
+        <v>247</v>
       </c>
       <c r="J116" s="5" t="s">
-        <v>342</v>
+        <v>248</v>
       </c>
       <c r="K116" s="5" t="s">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="L116" s="5" t="s">
         <v>47</v>
       </c>
       <c r="M116" s="5" t="s">
-        <v>344</v>
+        <v>491</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C117" s="5">
         <v>14211457</v>
@@ -6877,15 +6877,15 @@
         <v>600</v>
       </c>
       <c r="M117" s="5" t="s">
-        <v>345</v>
+        <v>492</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C118" s="5">
         <v>14211459</v>
@@ -6918,15 +6918,15 @@
         <v>600</v>
       </c>
       <c r="M118" s="5" t="s">
-        <v>346</v>
+        <v>493</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C119" s="5">
         <v>14211464</v>
@@ -6959,15 +6959,15 @@
         <v>59</v>
       </c>
       <c r="M119" s="5" t="s">
-        <v>347</v>
+        <v>494</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C120" s="5">
         <v>14211477</v>
@@ -6988,7 +6988,7 @@
         <v>4729105685</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>348</v>
+        <v>250</v>
       </c>
       <c r="J120" s="5" t="s">
         <v>50</v>
@@ -7000,15 +7000,15 @@
         <v>430</v>
       </c>
       <c r="M120" s="5" t="s">
-        <v>349</v>
+        <v>495</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C121" s="5">
         <v>14211509</v>
@@ -7029,7 +7029,7 @@
         <v>4710101503</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>350</v>
+        <v>251</v>
       </c>
       <c r="J121" s="5" t="s">
         <v>37</v>
@@ -7038,18 +7038,18 @@
         <v>185</v>
       </c>
       <c r="L121" s="5" t="s">
-        <v>351</v>
+        <v>252</v>
       </c>
       <c r="M121" s="5" t="s">
-        <v>352</v>
+        <v>496</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C122" s="5">
         <v>14211553</v>
@@ -7070,7 +7070,7 @@
         <v>4304800227</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>353</v>
+        <v>253</v>
       </c>
       <c r="J122" s="5" t="s">
         <v>37</v>
@@ -7082,15 +7082,15 @@
         <v>110</v>
       </c>
       <c r="M122" s="5" t="s">
-        <v>354</v>
+        <v>497</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C123" s="5">
         <v>14211553</v>
@@ -7111,7 +7111,7 @@
         <v>4304800253</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>353</v>
+        <v>253</v>
       </c>
       <c r="J123" s="5" t="s">
         <v>37</v>
@@ -7123,15 +7123,15 @@
         <v>220</v>
       </c>
       <c r="M123" s="5" t="s">
-        <v>355</v>
+        <v>498</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C124" s="5">
         <v>14211553</v>
@@ -7152,7 +7152,7 @@
         <v>4304800229</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>353</v>
+        <v>253</v>
       </c>
       <c r="J124" s="5" t="s">
         <v>37</v>
@@ -7164,15 +7164,15 @@
         <v>550</v>
       </c>
       <c r="M124" s="5" t="s">
-        <v>356</v>
+        <v>499</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C125" s="5">
         <v>14211553</v>
@@ -7193,7 +7193,7 @@
         <v>4304800230</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>353</v>
+        <v>253</v>
       </c>
       <c r="J125" s="5" t="s">
         <v>37</v>
@@ -7205,15 +7205,15 @@
         <v>550</v>
       </c>
       <c r="M125" s="5" t="s">
-        <v>357</v>
+        <v>500</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C126" s="5">
         <v>14211553</v>
@@ -7234,7 +7234,7 @@
         <v>4719266003</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>353</v>
+        <v>253</v>
       </c>
       <c r="J126" s="5" t="s">
         <v>37</v>
@@ -7246,15 +7246,15 @@
         <v>110</v>
       </c>
       <c r="M126" s="5" t="s">
-        <v>358</v>
+        <v>501</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C127" s="5">
         <v>14211553</v>
@@ -7275,7 +7275,7 @@
         <v>4719266046</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>353</v>
+        <v>253</v>
       </c>
       <c r="J127" s="5" t="s">
         <v>37</v>
@@ -7287,15 +7287,15 @@
         <v>110</v>
       </c>
       <c r="M127" s="5" t="s">
-        <v>359</v>
+        <v>502</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>324</v>
+        <v>237</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C128" s="5">
         <v>14211575</v>
@@ -7313,10 +7313,10 @@
         <v>2</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>360</v>
+        <v>254</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>361</v>
+        <v>255</v>
       </c>
       <c r="J128" s="5" t="s">
         <v>37</v>
@@ -7328,15 +7328,15 @@
         <v>680</v>
       </c>
       <c r="M128" s="5" t="s">
-        <v>362</v>
+        <v>503</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C129" s="5">
         <v>14212112</v>
@@ -7357,7 +7357,7 @@
         <v>4712003208</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>364</v>
+        <v>257</v>
       </c>
       <c r="J129" s="5" t="s">
         <v>37</v>
@@ -7366,18 +7366,18 @@
         <v>185</v>
       </c>
       <c r="L129" s="5" t="s">
-        <v>365</v>
+        <v>258</v>
       </c>
       <c r="M129" s="5" t="s">
-        <v>366</v>
+        <v>504</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C130" s="5">
         <v>14212120</v>
@@ -7398,7 +7398,7 @@
         <v>4712004263</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>367</v>
+        <v>259</v>
       </c>
       <c r="J130" s="5" t="s">
         <v>37</v>
@@ -7410,15 +7410,15 @@
         <v>173</v>
       </c>
       <c r="M130" s="5" t="s">
-        <v>368</v>
+        <v>505</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C131" s="5">
         <v>14212124</v>
@@ -7439,27 +7439,27 @@
         <v>4711300621</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>369</v>
+        <v>260</v>
       </c>
       <c r="J131" s="5" t="s">
-        <v>370</v>
+        <v>261</v>
       </c>
       <c r="K131" s="5" t="s">
-        <v>371</v>
+        <v>262</v>
       </c>
       <c r="L131" s="5" t="s">
-        <v>372</v>
+        <v>263</v>
       </c>
       <c r="M131" s="5" t="s">
-        <v>373</v>
+        <v>506</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C132" s="5">
         <v>14212124</v>
@@ -7480,27 +7480,27 @@
         <v>4711300387</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>369</v>
+        <v>260</v>
       </c>
       <c r="J132" s="5" t="s">
-        <v>370</v>
+        <v>261</v>
       </c>
       <c r="K132" s="5" t="s">
-        <v>371</v>
+        <v>262</v>
       </c>
       <c r="L132" s="5" t="s">
-        <v>374</v>
+        <v>264</v>
       </c>
       <c r="M132" s="5" t="s">
-        <v>375</v>
+        <v>507</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C133" s="5">
         <v>14212245</v>
@@ -7521,7 +7521,7 @@
         <v>4712004409</v>
       </c>
       <c r="I133" s="5" t="s">
-        <v>376</v>
+        <v>265</v>
       </c>
       <c r="J133" s="5" t="s">
         <v>37</v>
@@ -7530,18 +7530,18 @@
         <v>185</v>
       </c>
       <c r="L133" s="5" t="s">
-        <v>365</v>
+        <v>258</v>
       </c>
       <c r="M133" s="5" t="s">
-        <v>377</v>
+        <v>508</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C134" s="5">
         <v>14212245</v>
@@ -7562,7 +7562,7 @@
         <v>4712004594</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>378</v>
+        <v>266</v>
       </c>
       <c r="J134" s="5" t="s">
         <v>37</v>
@@ -7571,18 +7571,18 @@
         <v>185</v>
       </c>
       <c r="L134" s="5" t="s">
-        <v>365</v>
+        <v>258</v>
       </c>
       <c r="M134" s="5" t="s">
-        <v>379</v>
+        <v>509</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C135" s="5">
         <v>14212254</v>
@@ -7600,10 +7600,10 @@
         <v>1</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>380</v>
+        <v>267</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>381</v>
+        <v>268</v>
       </c>
       <c r="J135" s="5" t="s">
         <v>37</v>
@@ -7612,18 +7612,18 @@
         <v>185</v>
       </c>
       <c r="L135" s="5" t="s">
-        <v>382</v>
+        <v>269</v>
       </c>
       <c r="M135" s="5" t="s">
-        <v>383</v>
+        <v>510</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>363</v>
+        <v>256</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C136" s="5">
         <v>14212254</v>
@@ -7641,10 +7641,10 @@
         <v>1</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>384</v>
+        <v>270</v>
       </c>
       <c r="I136" s="5" t="s">
-        <v>385</v>
+        <v>271</v>
       </c>
       <c r="J136" s="5" t="s">
         <v>37</v>
@@ -7656,15 +7656,15 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="s">
-        <v>386</v>
+        <v>511</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C137" s="5">
         <v>14212686</v>
@@ -7682,10 +7682,10 @@
         <v>10</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>388</v>
+        <v>273</v>
       </c>
       <c r="I137" s="5" t="s">
-        <v>389</v>
+        <v>274</v>
       </c>
       <c r="J137" s="5" t="s">
         <v>37</v>
@@ -7697,15 +7697,15 @@
         <v>157</v>
       </c>
       <c r="M137" s="5" t="s">
-        <v>390</v>
+        <v>512</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C138" s="5">
         <v>14212761</v>
@@ -7726,7 +7726,7 @@
         <v>4702500847</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>391</v>
+        <v>275</v>
       </c>
       <c r="J138" s="5" t="s">
         <v>37</v>
@@ -7738,15 +7738,15 @@
         <v>110</v>
       </c>
       <c r="M138" s="5" t="s">
-        <v>392</v>
+        <v>513</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C139" s="5">
         <v>14212761</v>
@@ -7767,7 +7767,7 @@
         <v>4702500848</v>
       </c>
       <c r="I139" s="5" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="J139" s="5" t="s">
         <v>37</v>
@@ -7779,15 +7779,15 @@
         <v>19</v>
       </c>
       <c r="M139" s="5" t="s">
-        <v>394</v>
+        <v>514</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C140" s="5">
         <v>14212803</v>
@@ -7808,7 +7808,7 @@
         <v>4711401085</v>
       </c>
       <c r="I140" s="5" t="s">
-        <v>395</v>
+        <v>277</v>
       </c>
       <c r="J140" s="5" t="s">
         <v>37</v>
@@ -7817,18 +7817,18 @@
         <v>185</v>
       </c>
       <c r="L140" s="5" t="s">
-        <v>396</v>
+        <v>278</v>
       </c>
       <c r="M140" s="5" t="s">
-        <v>397</v>
+        <v>515</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C141" s="5">
         <v>14212853</v>
@@ -7849,7 +7849,7 @@
         <v>4727501921</v>
       </c>
       <c r="I141" s="5" t="s">
-        <v>398</v>
+        <v>279</v>
       </c>
       <c r="J141" s="5" t="s">
         <v>50</v>
@@ -7861,15 +7861,15 @@
         <v>19</v>
       </c>
       <c r="M141" s="5" t="s">
-        <v>399</v>
+        <v>516</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C142" s="5">
         <v>14212865</v>
@@ -7890,7 +7890,7 @@
         <v>4712004670</v>
       </c>
       <c r="I142" s="5" t="s">
-        <v>400</v>
+        <v>280</v>
       </c>
       <c r="J142" s="5" t="s">
         <v>50</v>
@@ -7899,18 +7899,18 @@
         <v>185</v>
       </c>
       <c r="L142" s="5" t="s">
-        <v>401</v>
+        <v>281</v>
       </c>
       <c r="M142" s="5" t="s">
-        <v>402</v>
+        <v>517</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C143" s="5">
         <v>14212876</v>
@@ -7931,7 +7931,7 @@
         <v>4730502874</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>403</v>
+        <v>282</v>
       </c>
       <c r="J143" s="5" t="s">
         <v>37</v>
@@ -7943,15 +7943,15 @@
         <v>880</v>
       </c>
       <c r="M143" s="5" t="s">
-        <v>404</v>
+        <v>518</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C144" s="5">
         <v>14212949</v>
@@ -7972,7 +7972,7 @@
         <v>4729109250</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>405</v>
+        <v>283</v>
       </c>
       <c r="J144" s="5" t="s">
         <v>37</v>
@@ -7981,18 +7981,18 @@
         <v>185</v>
       </c>
       <c r="L144" s="5" t="s">
-        <v>406</v>
+        <v>284</v>
       </c>
       <c r="M144" s="5" t="s">
-        <v>407</v>
+        <v>519</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C145" s="5">
         <v>14212952</v>
@@ -8013,7 +8013,7 @@
         <v>4730502878</v>
       </c>
       <c r="I145" s="5" t="s">
-        <v>408</v>
+        <v>285</v>
       </c>
       <c r="J145" s="5" t="s">
         <v>37</v>
@@ -8025,15 +8025,15 @@
         <v>650</v>
       </c>
       <c r="M145" s="5" t="s">
-        <v>409</v>
+        <v>520</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C146" s="5">
         <v>14212953</v>
@@ -8054,7 +8054,7 @@
         <v>4727501154</v>
       </c>
       <c r="I146" s="5" t="s">
-        <v>410</v>
+        <v>286</v>
       </c>
       <c r="J146" s="5" t="s">
         <v>50</v>
@@ -8066,15 +8066,15 @@
         <v>800</v>
       </c>
       <c r="M146" s="5" t="s">
-        <v>411</v>
+        <v>521</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C147" s="5">
         <v>14212955</v>
@@ -8095,7 +8095,7 @@
         <v>4711201791</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>412</v>
+        <v>287</v>
       </c>
       <c r="J147" s="5" t="s">
         <v>37</v>
@@ -8107,15 +8107,15 @@
         <v>173</v>
       </c>
       <c r="M147" s="5" t="s">
-        <v>413</v>
+        <v>522</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C148" s="5">
         <v>14212957</v>
@@ -8136,7 +8136,7 @@
         <v>4727501155</v>
       </c>
       <c r="I148" s="5" t="s">
-        <v>410</v>
+        <v>286</v>
       </c>
       <c r="J148" s="5" t="s">
         <v>50</v>
@@ -8148,15 +8148,15 @@
         <v>400</v>
       </c>
       <c r="M148" s="5" t="s">
-        <v>414</v>
+        <v>523</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C149" s="5">
         <v>14212962</v>
@@ -8189,15 +8189,15 @@
         <v>166</v>
       </c>
       <c r="M149" s="5" t="s">
-        <v>415</v>
+        <v>524</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C150" s="5">
         <v>14212967</v>
@@ -8218,7 +8218,7 @@
         <v>4710101560</v>
       </c>
       <c r="I150" s="5" t="s">
-        <v>416</v>
+        <v>288</v>
       </c>
       <c r="J150" s="5" t="s">
         <v>37</v>
@@ -8230,15 +8230,15 @@
         <v>166</v>
       </c>
       <c r="M150" s="5" t="s">
-        <v>417</v>
+        <v>525</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C151" s="5">
         <v>14212971</v>
@@ -8259,7 +8259,7 @@
         <v>4729108732</v>
       </c>
       <c r="I151" s="5" t="s">
-        <v>418</v>
+        <v>289</v>
       </c>
       <c r="J151" s="5" t="s">
         <v>37</v>
@@ -8271,15 +8271,15 @@
         <v>700</v>
       </c>
       <c r="M151" s="5" t="s">
-        <v>419</v>
+        <v>526</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C152" s="5">
         <v>14213020</v>
@@ -8300,7 +8300,7 @@
         <v>4729110620</v>
       </c>
       <c r="I152" s="5" t="s">
-        <v>420</v>
+        <v>290</v>
       </c>
       <c r="J152" s="5" t="s">
         <v>37</v>
@@ -8312,15 +8312,15 @@
         <v>163</v>
       </c>
       <c r="M152" s="5" t="s">
-        <v>421</v>
+        <v>527</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C153" s="5">
         <v>14213030</v>
@@ -8353,15 +8353,15 @@
         <v>166</v>
       </c>
       <c r="M153" s="5" t="s">
-        <v>422</v>
+        <v>528</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C154" s="5">
         <v>14213034</v>
@@ -8394,15 +8394,15 @@
         <v>166</v>
       </c>
       <c r="M154" s="5" t="s">
-        <v>423</v>
+        <v>529</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>387</v>
+        <v>272</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C155" s="5">
         <v>14213104</v>
@@ -8420,30 +8420,30 @@
         <v>2</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>424</v>
+        <v>291</v>
       </c>
       <c r="I155" s="5" t="s">
-        <v>425</v>
+        <v>292</v>
       </c>
       <c r="J155" s="5" t="s">
-        <v>426</v>
+        <v>293</v>
       </c>
       <c r="K155" s="5" t="s">
-        <v>371</v>
+        <v>262</v>
       </c>
       <c r="L155" s="5" t="s">
         <v>103</v>
       </c>
       <c r="M155" s="5" t="s">
-        <v>427</v>
+        <v>530</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>428</v>
+        <v>294</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C156" s="5">
         <v>14213297</v>
@@ -8464,7 +8464,7 @@
         <v>4727501151</v>
       </c>
       <c r="I156" s="5" t="s">
-        <v>429</v>
+        <v>295</v>
       </c>
       <c r="J156" s="5" t="s">
         <v>50</v>
@@ -8473,18 +8473,18 @@
         <v>185</v>
       </c>
       <c r="L156" s="5" t="s">
-        <v>430</v>
+        <v>296</v>
       </c>
       <c r="M156" s="5" t="s">
-        <v>431</v>
+        <v>531</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>428</v>
+        <v>294</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C157" s="5">
         <v>14213301</v>
@@ -8505,7 +8505,7 @@
         <v>4729104510</v>
       </c>
       <c r="I157" s="5" t="s">
-        <v>410</v>
+        <v>286</v>
       </c>
       <c r="J157" s="5" t="s">
         <v>50</v>
@@ -8514,18 +8514,18 @@
         <v>185</v>
       </c>
       <c r="L157" s="5" t="s">
-        <v>240</v>
+        <v>199</v>
       </c>
       <c r="M157" s="5" t="s">
-        <v>432</v>
+        <v>532</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>428</v>
+        <v>294</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C158" s="5">
         <v>14213305</v>
@@ -8555,18 +8555,18 @@
         <v>185</v>
       </c>
       <c r="L158" s="5" t="s">
-        <v>433</v>
+        <v>297</v>
       </c>
       <c r="M158" s="5" t="s">
-        <v>434</v>
+        <v>533</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>428</v>
+        <v>294</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C159" s="5">
         <v>14213308</v>
@@ -8587,7 +8587,7 @@
         <v>4711201528</v>
       </c>
       <c r="I159" s="5" t="s">
-        <v>435</v>
+        <v>298</v>
       </c>
       <c r="J159" s="5" t="s">
         <v>50</v>
@@ -8596,18 +8596,18 @@
         <v>185</v>
       </c>
       <c r="L159" s="5" t="s">
-        <v>436</v>
+        <v>299</v>
       </c>
       <c r="M159" s="5" t="s">
-        <v>437</v>
+        <v>534</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>428</v>
+        <v>294</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C160" s="5">
         <v>14213310</v>
@@ -8628,7 +8628,7 @@
         <v>4712004047</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>438</v>
+        <v>300</v>
       </c>
       <c r="J160" s="5" t="s">
         <v>50</v>
@@ -8640,15 +8640,15 @@
         <v>68</v>
       </c>
       <c r="M160" s="5" t="s">
-        <v>439</v>
+        <v>535</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>428</v>
+        <v>294</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C161" s="5">
         <v>14213311</v>
@@ -8669,7 +8669,7 @@
         <v>4712004047</v>
       </c>
       <c r="I161" s="5" t="s">
-        <v>440</v>
+        <v>301</v>
       </c>
       <c r="J161" s="5" t="s">
         <v>50</v>
@@ -8681,15 +8681,15 @@
         <v>33</v>
       </c>
       <c r="M161" s="5" t="s">
-        <v>441</v>
+        <v>536</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>442</v>
+        <v>302</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C162" s="5">
         <v>14213659</v>
@@ -8710,7 +8710,7 @@
         <v>4710800192</v>
       </c>
       <c r="I162" s="5" t="s">
-        <v>444</v>
+        <v>304</v>
       </c>
       <c r="J162" s="5" t="s">
         <v>37</v>
@@ -8722,15 +8722,15 @@
         <v>112</v>
       </c>
       <c r="M162" s="5" t="s">
-        <v>445</v>
+        <v>305</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>442</v>
+        <v>302</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C163" s="5">
         <v>14213659</v>
@@ -8763,15 +8763,15 @@
         <v>112</v>
       </c>
       <c r="M163" s="5" t="s">
-        <v>446</v>
+        <v>306</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>442</v>
+        <v>302</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C164" s="5">
         <v>14213693</v>
@@ -8792,7 +8792,7 @@
         <v>4729111555</v>
       </c>
       <c r="I164" s="5" t="s">
-        <v>447</v>
+        <v>307</v>
       </c>
       <c r="J164" s="5" t="s">
         <v>50</v>
@@ -8804,15 +8804,15 @@
         <v>38</v>
       </c>
       <c r="M164" s="5" t="s">
-        <v>448</v>
+        <v>308</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>442</v>
+        <v>302</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C165" s="5">
         <v>14213876</v>
@@ -8833,7 +8833,7 @@
         <v>4728701223</v>
       </c>
       <c r="I165" s="5" t="s">
-        <v>449</v>
+        <v>309</v>
       </c>
       <c r="J165" s="5" t="s">
         <v>37</v>
@@ -8845,15 +8845,15 @@
         <v>880</v>
       </c>
       <c r="M165" s="5" t="s">
-        <v>450</v>
+        <v>310</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>442</v>
+        <v>302</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C166" s="5">
         <v>14213913</v>
@@ -8874,7 +8874,7 @@
         <v>4710201151</v>
       </c>
       <c r="I166" s="5" t="s">
-        <v>451</v>
+        <v>311</v>
       </c>
       <c r="J166" s="5" t="s">
         <v>37</v>
@@ -8883,18 +8883,18 @@
         <v>185</v>
       </c>
       <c r="L166" s="5" t="s">
-        <v>452</v>
+        <v>312</v>
       </c>
       <c r="M166" s="5" t="s">
-        <v>453</v>
+        <v>313</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>442</v>
+        <v>302</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C167" s="5">
         <v>14213936</v>
@@ -8915,7 +8915,7 @@
         <v>4729109958</v>
       </c>
       <c r="I167" s="5" t="s">
-        <v>454</v>
+        <v>314</v>
       </c>
       <c r="J167" s="5" t="s">
         <v>37</v>
@@ -8927,15 +8927,15 @@
         <v>59</v>
       </c>
       <c r="M167" s="5" t="s">
-        <v>455</v>
+        <v>315</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>442</v>
+        <v>302</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C168" s="5">
         <v>14213992</v>
@@ -8953,10 +8953,10 @@
         <v>4</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>456</v>
+        <v>316</v>
       </c>
       <c r="I168" s="5" t="s">
-        <v>457</v>
+        <v>317</v>
       </c>
       <c r="J168" s="5" t="s">
         <v>58</v>
@@ -8968,15 +8968,15 @@
         <v>800</v>
       </c>
       <c r="M168" s="5" t="s">
-        <v>458</v>
+        <v>318</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>459</v>
+        <v>319</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C169" s="5">
         <v>14214523</v>
@@ -8997,7 +8997,7 @@
         <v>4711202048</v>
       </c>
       <c r="I169" s="5" t="s">
-        <v>460</v>
+        <v>320</v>
       </c>
       <c r="J169" s="5" t="s">
         <v>37</v>
@@ -9009,15 +9009,15 @@
         <v>157</v>
       </c>
       <c r="M169" s="5" t="s">
-        <v>461</v>
+        <v>321</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>459</v>
+        <v>319</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C170" s="5">
         <v>14214728</v>
@@ -9038,7 +9038,7 @@
         <v>4728700283</v>
       </c>
       <c r="I170" s="5" t="s">
-        <v>462</v>
+        <v>322</v>
       </c>
       <c r="J170" s="5" t="s">
         <v>37</v>
@@ -9047,18 +9047,18 @@
         <v>185</v>
       </c>
       <c r="L170" s="5" t="s">
-        <v>463</v>
+        <v>323</v>
       </c>
       <c r="M170" s="5" t="s">
-        <v>464</v>
+        <v>324</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>459</v>
+        <v>319</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C171" s="5">
         <v>14214738</v>
@@ -9088,18 +9088,18 @@
         <v>185</v>
       </c>
       <c r="L171" s="5" t="s">
-        <v>465</v>
+        <v>325</v>
       </c>
       <c r="M171" s="5" t="s">
-        <v>466</v>
+        <v>326</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>459</v>
+        <v>319</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C172" s="5">
         <v>14214744</v>
@@ -9120,7 +9120,7 @@
         <v>4710101560</v>
       </c>
       <c r="I172" s="5" t="s">
-        <v>467</v>
+        <v>327</v>
       </c>
       <c r="J172" s="5" t="s">
         <v>37</v>
@@ -9132,15 +9132,15 @@
         <v>166</v>
       </c>
       <c r="M172" s="5" t="s">
-        <v>468</v>
+        <v>328</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>459</v>
+        <v>319</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C173" s="5">
         <v>14214825</v>
@@ -9161,7 +9161,7 @@
         <v>4727500865</v>
       </c>
       <c r="I173" s="5" t="s">
-        <v>469</v>
+        <v>329</v>
       </c>
       <c r="J173" s="5" t="s">
         <v>37</v>
@@ -9173,15 +9173,15 @@
         <v>114</v>
       </c>
       <c r="M173" s="5" t="s">
-        <v>470</v>
+        <v>330</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>471</v>
+        <v>331</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C174" s="5">
         <v>14215400</v>
@@ -9202,7 +9202,7 @@
         <v>4710101475</v>
       </c>
       <c r="I174" s="5" t="s">
-        <v>472</v>
+        <v>332</v>
       </c>
       <c r="J174" s="5" t="s">
         <v>37</v>
@@ -9211,18 +9211,18 @@
         <v>185</v>
       </c>
       <c r="L174" s="5" t="s">
-        <v>473</v>
+        <v>333</v>
       </c>
       <c r="M174" s="5" t="s">
-        <v>474</v>
+        <v>334</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>471</v>
+        <v>331</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C175" s="5">
         <v>14215433</v>
@@ -9240,30 +9240,30 @@
         <v>28</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>475</v>
+        <v>335</v>
       </c>
       <c r="I175" s="5" t="s">
-        <v>476</v>
+        <v>336</v>
       </c>
       <c r="J175" s="5" t="s">
-        <v>477</v>
+        <v>337</v>
       </c>
       <c r="K175" s="5" t="s">
-        <v>478</v>
+        <v>338</v>
       </c>
       <c r="L175" s="5" t="s">
-        <v>479</v>
+        <v>339</v>
       </c>
       <c r="M175" s="5" t="s">
-        <v>480</v>
+        <v>340</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>471</v>
+        <v>331</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C176" s="5">
         <v>14215504</v>
@@ -9296,15 +9296,15 @@
         <v>450</v>
       </c>
       <c r="M176" s="5" t="s">
-        <v>481</v>
+        <v>341</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>471</v>
+        <v>331</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C177" s="5">
         <v>14215675</v>
@@ -9325,27 +9325,27 @@
         <v>4711201529</v>
       </c>
       <c r="I177" s="5" t="s">
-        <v>482</v>
+        <v>342</v>
       </c>
       <c r="J177" s="5" t="s">
-        <v>483</v>
+        <v>343</v>
       </c>
       <c r="K177" s="5" t="s">
-        <v>484</v>
+        <v>344</v>
       </c>
       <c r="L177" s="5" t="s">
-        <v>485</v>
+        <v>345</v>
       </c>
       <c r="M177" s="5" t="s">
-        <v>486</v>
+        <v>346</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>487</v>
+        <v>347</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C178" s="5">
         <v>14216106</v>
@@ -9366,7 +9366,7 @@
         <v>4305400225</v>
       </c>
       <c r="I178" s="5" t="s">
-        <v>488</v>
+        <v>348</v>
       </c>
       <c r="J178" s="5" t="s">
         <v>37</v>
@@ -9378,15 +9378,15 @@
         <v>160</v>
       </c>
       <c r="M178" s="5" t="s">
-        <v>489</v>
+        <v>349</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>487</v>
+        <v>347</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C179" s="5">
         <v>14216222</v>
@@ -9407,7 +9407,7 @@
         <v>4729105785</v>
       </c>
       <c r="I179" s="5" t="s">
-        <v>490</v>
+        <v>350</v>
       </c>
       <c r="J179" s="5" t="s">
         <v>50</v>
@@ -9419,15 +9419,15 @@
         <v>68</v>
       </c>
       <c r="M179" s="5" t="s">
-        <v>491</v>
+        <v>351</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>487</v>
+        <v>347</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C180" s="5">
         <v>14216272</v>
@@ -9448,7 +9448,7 @@
         <v>4710800032</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>492</v>
+        <v>352</v>
       </c>
       <c r="J180" s="5" t="s">
         <v>37</v>
@@ -9460,15 +9460,15 @@
         <v>41</v>
       </c>
       <c r="M180" s="5" t="s">
-        <v>493</v>
+        <v>353</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>487</v>
+        <v>347</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C181" s="5">
         <v>14216272</v>
@@ -9489,7 +9489,7 @@
         <v>4710800002</v>
       </c>
       <c r="I181" s="5" t="s">
-        <v>492</v>
+        <v>352</v>
       </c>
       <c r="J181" s="5" t="s">
         <v>37</v>
@@ -9501,15 +9501,15 @@
         <v>173</v>
       </c>
       <c r="M181" s="5" t="s">
-        <v>494</v>
+        <v>354</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>487</v>
+        <v>347</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C182" s="5">
         <v>14216272</v>
@@ -9530,7 +9530,7 @@
         <v>4710800100</v>
       </c>
       <c r="I182" s="5" t="s">
-        <v>492</v>
+        <v>352</v>
       </c>
       <c r="J182" s="5" t="s">
         <v>37</v>
@@ -9542,15 +9542,15 @@
         <v>47</v>
       </c>
       <c r="M182" s="5" t="s">
-        <v>495</v>
+        <v>355</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C183" s="5">
         <v>14216678</v>
@@ -9571,7 +9571,7 @@
         <v>4729111741</v>
       </c>
       <c r="I183" s="5" t="s">
-        <v>497</v>
+        <v>357</v>
       </c>
       <c r="J183" s="5" t="s">
         <v>37</v>
@@ -9583,15 +9583,15 @@
         <v>143</v>
       </c>
       <c r="M183" s="5" t="s">
-        <v>498</v>
+        <v>358</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C184" s="5">
         <v>14216857</v>
@@ -9609,10 +9609,10 @@
         <v>2</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>499</v>
+        <v>359</v>
       </c>
       <c r="I184" s="5" t="s">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="J184" s="5" t="s">
         <v>37</v>
@@ -9621,18 +9621,18 @@
         <v>185</v>
       </c>
       <c r="L184" s="5" t="s">
-        <v>501</v>
+        <v>361</v>
       </c>
       <c r="M184" s="5" t="s">
-        <v>502</v>
+        <v>362</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C185" s="5">
         <v>14216857</v>
@@ -9650,10 +9650,10 @@
         <v>2</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>503</v>
+        <v>363</v>
       </c>
       <c r="I185" s="5" t="s">
-        <v>504</v>
+        <v>364</v>
       </c>
       <c r="J185" s="5" t="s">
         <v>37</v>
@@ -9662,18 +9662,18 @@
         <v>185</v>
       </c>
       <c r="L185" s="5" t="s">
-        <v>501</v>
+        <v>361</v>
       </c>
       <c r="M185" s="5" t="s">
-        <v>505</v>
+        <v>365</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C186" s="5">
         <v>14216857</v>
@@ -9691,10 +9691,10 @@
         <v>2</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>506</v>
+        <v>366</v>
       </c>
       <c r="I186" s="5" t="s">
-        <v>507</v>
+        <v>367</v>
       </c>
       <c r="J186" s="5" t="s">
         <v>37</v>
@@ -9703,18 +9703,18 @@
         <v>185</v>
       </c>
       <c r="L186" s="5" t="s">
-        <v>501</v>
+        <v>361</v>
       </c>
       <c r="M186" s="5" t="s">
-        <v>508</v>
+        <v>368</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C187" s="5">
         <v>14216857</v>
@@ -9732,10 +9732,10 @@
         <v>2</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>509</v>
+        <v>369</v>
       </c>
       <c r="I187" s="5" t="s">
-        <v>510</v>
+        <v>370</v>
       </c>
       <c r="J187" s="5" t="s">
         <v>37</v>
@@ -9744,18 +9744,18 @@
         <v>185</v>
       </c>
       <c r="L187" s="5" t="s">
-        <v>511</v>
+        <v>371</v>
       </c>
       <c r="M187" s="5" t="s">
-        <v>512</v>
+        <v>372</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C188" s="5">
         <v>14216857</v>
@@ -9773,10 +9773,10 @@
         <v>2</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>513</v>
+        <v>373</v>
       </c>
       <c r="I188" s="5" t="s">
-        <v>514</v>
+        <v>374</v>
       </c>
       <c r="J188" s="5" t="s">
         <v>37</v>
@@ -9785,18 +9785,18 @@
         <v>185</v>
       </c>
       <c r="L188" s="5" t="s">
-        <v>511</v>
+        <v>371</v>
       </c>
       <c r="M188" s="5" t="s">
-        <v>515</v>
+        <v>375</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C189" s="5">
         <v>14216925</v>
@@ -9817,7 +9817,7 @@
         <v>4730502923</v>
       </c>
       <c r="I189" s="5" t="s">
-        <v>516</v>
+        <v>376</v>
       </c>
       <c r="J189" s="5" t="s">
         <v>50</v>
@@ -9829,15 +9829,15 @@
         <v>800</v>
       </c>
       <c r="M189" s="5" t="s">
-        <v>517</v>
+        <v>377</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C190" s="5">
         <v>14216965</v>
@@ -9858,7 +9858,7 @@
         <v>4729106006</v>
       </c>
       <c r="I190" s="5" t="s">
-        <v>518</v>
+        <v>378</v>
       </c>
       <c r="J190" s="5" t="s">
         <v>58</v>
@@ -9870,15 +9870,15 @@
         <v>157</v>
       </c>
       <c r="M190" s="5" t="s">
-        <v>519</v>
+        <v>379</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C191" s="5">
         <v>14216976</v>
@@ -9899,7 +9899,7 @@
         <v>4320600139</v>
       </c>
       <c r="I191" s="5" t="s">
-        <v>520</v>
+        <v>380</v>
       </c>
       <c r="J191" s="5" t="s">
         <v>37</v>
@@ -9908,18 +9908,18 @@
         <v>185</v>
       </c>
       <c r="L191" s="5" t="s">
-        <v>521</v>
+        <v>381</v>
       </c>
       <c r="M191" s="5" t="s">
-        <v>522</v>
+        <v>382</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>496</v>
+        <v>356</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="C192" s="5">
         <v>14217041</v>
@@ -9940,7 +9940,7 @@
         <v>4729112103</v>
       </c>
       <c r="I192" s="5" t="s">
-        <v>523</v>
+        <v>383</v>
       </c>
       <c r="J192" s="5" t="s">
         <v>58</v>
@@ -9949,18 +9949,18 @@
         <v>185</v>
       </c>
       <c r="L192" s="5" t="s">
-        <v>524</v>
+        <v>384</v>
       </c>
       <c r="M192" s="5" t="s">
-        <v>525</v>
+        <v>385</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>526</v>
+        <v>386</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>527</v>
+        <v>387</v>
       </c>
       <c r="C193" s="5">
         <v>14217734</v>
@@ -9981,7 +9981,7 @@
         <v>4711401061</v>
       </c>
       <c r="I193" s="5" t="s">
-        <v>528</v>
+        <v>388</v>
       </c>
       <c r="J193" s="5" t="s">
         <v>58</v>
@@ -9990,18 +9990,18 @@
         <v>185</v>
       </c>
       <c r="L193" s="5" t="s">
-        <v>529</v>
+        <v>389</v>
       </c>
       <c r="M193" s="5" t="s">
-        <v>530</v>
+        <v>390</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>526</v>
+        <v>386</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>527</v>
+        <v>387</v>
       </c>
       <c r="C194" s="5">
         <v>14218303</v>
@@ -10022,7 +10022,7 @@
         <v>4712002707</v>
       </c>
       <c r="I194" s="5" t="s">
-        <v>523</v>
+        <v>383</v>
       </c>
       <c r="J194" s="5" t="s">
         <v>58</v>
@@ -10031,18 +10031,18 @@
         <v>185</v>
       </c>
       <c r="L194" s="5" t="s">
-        <v>531</v>
+        <v>391</v>
       </c>
       <c r="M194" s="5" t="s">
-        <v>532</v>
+        <v>392</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>526</v>
+        <v>386</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>527</v>
+        <v>387</v>
       </c>
       <c r="C195" s="5">
         <v>14218494</v>
@@ -10075,15 +10075,15 @@
         <v>600</v>
       </c>
       <c r="M195" s="5" t="s">
-        <v>533</v>
+        <v>393</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>526</v>
+        <v>386</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>527</v>
+        <v>387</v>
       </c>
       <c r="C196" s="5">
         <v>14218497</v>
@@ -10116,15 +10116,15 @@
         <v>600</v>
       </c>
       <c r="M196" s="5" t="s">
-        <v>534</v>
+        <v>394</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>526</v>
+        <v>386</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>527</v>
+        <v>387</v>
       </c>
       <c r="C197" s="5">
         <v>14218498</v>
@@ -10145,7 +10145,7 @@
         <v>4712003439</v>
       </c>
       <c r="I197" s="5" t="s">
-        <v>535</v>
+        <v>395</v>
       </c>
       <c r="J197" s="5" t="s">
         <v>58</v>
@@ -10157,7 +10157,7 @@
         <v>660</v>
       </c>
       <c r="M197" s="5" t="s">
-        <v>536</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AE0472-A711-4BE0-8D09-62826A1578FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD9FBC2-E6A0-4E0F-9C87-C56D625C6829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="644">
   <si>
     <t>Data</t>
   </si>
@@ -1949,6 +1949,9 @@
   </si>
   <si>
     <t>LP-055834</t>
+  </si>
+  <si>
+    <t>CADASTRADA</t>
   </si>
 </sst>
 </file>
@@ -2456,7 +2459,9 @@
       <c r="M2" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="N2" s="5"/>
+      <c r="N2" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O2" s="5"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -2499,7 +2504,9 @@
       <c r="M3" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="N3" s="5"/>
+      <c r="N3" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -2542,7 +2549,9 @@
       <c r="M4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="5"/>
+      <c r="N4" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -2585,7 +2594,9 @@
       <c r="M5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="N5" s="5"/>
+      <c r="N5" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O5" s="5"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -2628,7 +2639,9 @@
       <c r="M6" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N6" s="5"/>
+      <c r="N6" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -2671,7 +2684,9 @@
       <c r="M7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="N7" s="5"/>
+      <c r="N7" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -2714,7 +2729,9 @@
       <c r="M8" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N8" s="5"/>
+      <c r="N8" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -2757,7 +2774,9 @@
       <c r="M9" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N9" s="5"/>
+      <c r="N9" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -2800,7 +2819,9 @@
       <c r="M10" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="N10" s="5"/>
+      <c r="N10" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O10" s="5"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -2843,7 +2864,9 @@
       <c r="M11" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N11" s="5"/>
+      <c r="N11" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O11" s="5"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2886,7 +2909,9 @@
       <c r="M12" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="N12" s="5"/>
+      <c r="N12" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O12" s="5"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2929,7 +2954,9 @@
       <c r="M13" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="N13" s="5"/>
+      <c r="N13" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O13" s="5"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -2972,7 +2999,9 @@
       <c r="M14" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="N14" s="5"/>
+      <c r="N14" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -3015,7 +3044,9 @@
       <c r="M15" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="N15" s="5"/>
+      <c r="N15" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O15" s="5"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -3058,7 +3089,9 @@
       <c r="M16" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="N16" s="5"/>
+      <c r="N16" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O16" s="5"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -3101,7 +3134,9 @@
       <c r="M17" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="N17" s="5"/>
+      <c r="N17" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O17" s="5"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -3144,7 +3179,9 @@
       <c r="M18" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="N18" s="5"/>
+      <c r="N18" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O18" s="5"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -3187,7 +3224,9 @@
       <c r="M19" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="N19" s="5"/>
+      <c r="N19" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O19" s="5"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -3230,7 +3269,9 @@
       <c r="M20" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="N20" s="5"/>
+      <c r="N20" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O20" s="5"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -3273,7 +3314,9 @@
       <c r="M21" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="N21" s="5"/>
+      <c r="N21" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O21" s="5"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -3316,7 +3359,9 @@
       <c r="M22" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="N22" s="5"/>
+      <c r="N22" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O22" s="5"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -3359,7 +3404,9 @@
       <c r="M23" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="N23" s="5"/>
+      <c r="N23" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3402,7 +3449,9 @@
       <c r="M24" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="N24" s="5"/>
+      <c r="N24" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -3445,7 +3494,9 @@
       <c r="M25" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="N25" s="5"/>
+      <c r="N25" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O25" s="5"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3488,7 +3539,9 @@
       <c r="M26" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="N26" s="5"/>
+      <c r="N26" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O26" s="5"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -3531,7 +3584,9 @@
       <c r="M27" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="N27" s="5"/>
+      <c r="N27" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O27" s="5"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -3574,7 +3629,9 @@
       <c r="M28" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="N28" s="5"/>
+      <c r="N28" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O28" s="5"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3617,7 +3674,9 @@
       <c r="M29" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N29" s="5"/>
+      <c r="N29" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3660,7 +3719,9 @@
       <c r="M30" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="N30" s="5"/>
+      <c r="N30" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O30" s="5"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -3703,7 +3764,9 @@
       <c r="M31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="N31" s="5"/>
+      <c r="N31" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O31" s="5"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -3746,7 +3809,9 @@
       <c r="M32" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="N32" s="5"/>
+      <c r="N32" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O32" s="5"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -3789,7 +3854,9 @@
       <c r="M33" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="N33" s="5"/>
+      <c r="N33" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O33" s="5"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -3832,7 +3899,9 @@
       <c r="M34" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="N34" s="5"/>
+      <c r="N34" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O34" s="5"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -3875,7 +3944,9 @@
       <c r="M35" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="N35" s="5"/>
+      <c r="N35" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O35" s="5"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3918,7 +3989,9 @@
       <c r="M36" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="N36" s="5"/>
+      <c r="N36" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O36" s="5"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -3961,7 +4034,9 @@
       <c r="M37" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="N37" s="5"/>
+      <c r="N37" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O37" s="5"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -4004,7 +4079,9 @@
       <c r="M38" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N38" s="5"/>
+      <c r="N38" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O38" s="5"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -4047,7 +4124,9 @@
       <c r="M39" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="N39" s="5"/>
+      <c r="N39" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O39" s="5"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -4090,7 +4169,9 @@
       <c r="M40" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="N40" s="5"/>
+      <c r="N40" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O40" s="5"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -4133,7 +4214,9 @@
       <c r="M41" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="N41" s="5"/>
+      <c r="N41" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O41" s="5"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -4176,7 +4259,9 @@
       <c r="M42" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="N42" s="5"/>
+      <c r="N42" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O42" s="5"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -4219,7 +4304,9 @@
       <c r="M43" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="N43" s="5"/>
+      <c r="N43" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O43" s="5"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -4262,7 +4349,9 @@
       <c r="M44" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="N44" s="5"/>
+      <c r="N44" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O44" s="5"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -4305,7 +4394,9 @@
       <c r="M45" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="N45" s="5"/>
+      <c r="N45" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O45" s="5"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -4348,7 +4439,9 @@
       <c r="M46" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="N46" s="5"/>
+      <c r="N46" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O46" s="5"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -4391,7 +4484,9 @@
       <c r="M47" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="N47" s="5"/>
+      <c r="N47" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O47" s="5"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -4434,7 +4529,9 @@
       <c r="M48" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="N48" s="5"/>
+      <c r="N48" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O48" s="5"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -4477,7 +4574,9 @@
       <c r="M49" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="N49" s="5"/>
+      <c r="N49" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O49" s="5"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -4520,7 +4619,9 @@
       <c r="M50" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="N50" s="5"/>
+      <c r="N50" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O50" s="5"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -4563,7 +4664,9 @@
       <c r="M51" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="N51" s="5"/>
+      <c r="N51" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O51" s="5"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -4606,7 +4709,9 @@
       <c r="M52" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="N52" s="5"/>
+      <c r="N52" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O52" s="5"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -4649,7 +4754,9 @@
       <c r="M53" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="N53" s="5"/>
+      <c r="N53" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O53" s="5"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -4692,7 +4799,9 @@
       <c r="M54" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="N54" s="5"/>
+      <c r="N54" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O54" s="5"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -4735,7 +4844,9 @@
       <c r="M55" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="N55" s="5"/>
+      <c r="N55" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O55" s="5"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4778,7 +4889,9 @@
       <c r="M56" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="N56" s="5"/>
+      <c r="N56" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O56" s="5"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -4821,7 +4934,9 @@
       <c r="M57" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="N57" s="5"/>
+      <c r="N57" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O57" s="5"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
@@ -4864,7 +4979,9 @@
       <c r="M58" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="N58" s="5"/>
+      <c r="N58" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O58" s="5"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -4907,7 +5024,9 @@
       <c r="M59" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="N59" s="5"/>
+      <c r="N59" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O59" s="5"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -4950,7 +5069,9 @@
       <c r="M60" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="N60" s="5"/>
+      <c r="N60" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O60" s="5"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -4993,7 +5114,9 @@
       <c r="M61" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="N61" s="5"/>
+      <c r="N61" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O61" s="5"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -5036,7 +5159,9 @@
       <c r="M62" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="N62" s="5"/>
+      <c r="N62" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O62" s="5"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -5079,7 +5204,9 @@
       <c r="M63" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="N63" s="5"/>
+      <c r="N63" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O63" s="5"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -5122,7 +5249,9 @@
       <c r="M64" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="N64" s="5"/>
+      <c r="N64" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O64" s="5"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -5165,7 +5294,9 @@
       <c r="M65" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="N65" s="5"/>
+      <c r="N65" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O65" s="5"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
@@ -5208,7 +5339,9 @@
       <c r="M66" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="N66" s="5"/>
+      <c r="N66" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O66" s="5"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
@@ -5251,7 +5384,9 @@
       <c r="M67" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="N67" s="5"/>
+      <c r="N67" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O67" s="5"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
@@ -5294,7 +5429,9 @@
       <c r="M68" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="N68" s="5"/>
+      <c r="N68" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O68" s="5"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
@@ -5337,7 +5474,9 @@
       <c r="M69" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="N69" s="5"/>
+      <c r="N69" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O69" s="5"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
@@ -5380,7 +5519,9 @@
       <c r="M70" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="N70" s="5"/>
+      <c r="N70" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O70" s="5"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
@@ -5423,7 +5564,9 @@
       <c r="M71" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="N71" s="5"/>
+      <c r="N71" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O71" s="5"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
@@ -5466,7 +5609,9 @@
       <c r="M72" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="N72" s="5"/>
+      <c r="N72" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O72" s="5"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
@@ -5509,7 +5654,9 @@
       <c r="M73" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="N73" s="5"/>
+      <c r="N73" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O73" s="5"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
@@ -5552,7 +5699,9 @@
       <c r="M74" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="N74" s="5"/>
+      <c r="N74" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O74" s="5"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
@@ -5595,7 +5744,9 @@
       <c r="M75" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="N75" s="5"/>
+      <c r="N75" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O75" s="5"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
@@ -5638,7 +5789,9 @@
       <c r="M76" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="N76" s="5"/>
+      <c r="N76" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O76" s="5"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
@@ -5681,7 +5834,9 @@
       <c r="M77" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="N77" s="5"/>
+      <c r="N77" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O77" s="5"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
@@ -5724,7 +5879,9 @@
       <c r="M78" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="N78" s="5"/>
+      <c r="N78" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O78" s="5"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
@@ -5767,7 +5924,9 @@
       <c r="M79" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="N79" s="5"/>
+      <c r="N79" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O79" s="5"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
@@ -5810,7 +5969,9 @@
       <c r="M80" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="N80" s="5"/>
+      <c r="N80" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O80" s="5"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
@@ -5853,7 +6014,9 @@
       <c r="M81" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="N81" s="5"/>
+      <c r="N81" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O81" s="5"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
@@ -5896,7 +6059,9 @@
       <c r="M82" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="N82" s="5"/>
+      <c r="N82" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O82" s="5"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
@@ -5939,7 +6104,9 @@
       <c r="M83" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="N83" s="5"/>
+      <c r="N83" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O83" s="5"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
@@ -5982,7 +6149,9 @@
       <c r="M84" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="N84" s="5"/>
+      <c r="N84" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O84" s="5"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
@@ -6025,7 +6194,9 @@
       <c r="M85" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="N85" s="5"/>
+      <c r="N85" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O85" s="5"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
@@ -6068,7 +6239,9 @@
       <c r="M86" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="N86" s="5"/>
+      <c r="N86" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O86" s="5"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
@@ -6111,7 +6284,9 @@
       <c r="M87" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="N87" s="5"/>
+      <c r="N87" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O87" s="5"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
@@ -6154,7 +6329,9 @@
       <c r="M88" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="N88" s="5"/>
+      <c r="N88" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O88" s="5"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
@@ -6197,7 +6374,9 @@
       <c r="M89" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="N89" s="5"/>
+      <c r="N89" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O89" s="5"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
@@ -6240,7 +6419,9 @@
       <c r="M90" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="N90" s="5"/>
+      <c r="N90" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O90" s="5"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
@@ -6283,7 +6464,9 @@
       <c r="M91" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="N91" s="5"/>
+      <c r="N91" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O91" s="5"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
@@ -6326,7 +6509,9 @@
       <c r="M92" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="N92" s="5"/>
+      <c r="N92" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O92" s="5"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
@@ -6369,7 +6554,9 @@
       <c r="M93" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="N93" s="5"/>
+      <c r="N93" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O93" s="5"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
@@ -6412,7 +6599,9 @@
       <c r="M94" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="N94" s="5"/>
+      <c r="N94" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O94" s="5"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
@@ -6455,7 +6644,9 @@
       <c r="M95" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="N95" s="5"/>
+      <c r="N95" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O95" s="5"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
@@ -6498,7 +6689,9 @@
       <c r="M96" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="N96" s="5"/>
+      <c r="N96" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O96" s="5"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
@@ -6541,7 +6734,9 @@
       <c r="M97" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="N97" s="5"/>
+      <c r="N97" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O97" s="5"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
@@ -6584,7 +6779,9 @@
       <c r="M98" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="N98" s="5"/>
+      <c r="N98" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O98" s="5"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
@@ -6627,7 +6824,9 @@
       <c r="M99" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="N99" s="5"/>
+      <c r="N99" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O99" s="5"/>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
@@ -6670,7 +6869,9 @@
       <c r="M100" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="N100" s="5"/>
+      <c r="N100" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O100" s="5"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
@@ -6713,7 +6914,9 @@
       <c r="M101" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="N101" s="5"/>
+      <c r="N101" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O101" s="5"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
@@ -6756,7 +6959,9 @@
       <c r="M102" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="N102" s="5"/>
+      <c r="N102" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O102" s="5"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
@@ -6799,7 +7004,9 @@
       <c r="M103" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="N103" s="5"/>
+      <c r="N103" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O103" s="5"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
@@ -6842,7 +7049,9 @@
       <c r="M104" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="N104" s="5"/>
+      <c r="N104" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O104" s="5"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
@@ -6885,7 +7094,9 @@
       <c r="M105" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="N105" s="5"/>
+      <c r="N105" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O105" s="5"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
@@ -6928,7 +7139,9 @@
       <c r="M106" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="N106" s="5"/>
+      <c r="N106" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O106" s="5"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
@@ -6971,7 +7184,9 @@
       <c r="M107" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="N107" s="5"/>
+      <c r="N107" s="5" t="s">
+        <v>643</v>
+      </c>
       <c r="O107" s="5"/>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD9FBC2-E6A0-4E0F-9C87-C56D625C6829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B41B60-546D-41D7-AF47-AE9A361C24CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="642">
   <si>
     <t>Data</t>
   </si>
@@ -1193,12 +1193,6 @@
   </si>
   <si>
     <t>LP-055838</t>
-  </si>
-  <si>
-    <t>4716506412-0161</t>
-  </si>
-  <si>
-    <t>LP-055837</t>
   </si>
   <si>
     <t>4716507709-0052</t>
@@ -2353,7 +2347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O253"/>
+  <dimension ref="A1:O252"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2460,9 +2454,11 @@
         <v>70</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O2" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -2505,9 +2501,11 @@
         <v>73</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O3" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -2550,9 +2548,11 @@
         <v>75</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O4" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -2595,9 +2595,11 @@
         <v>77</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O5" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -2640,9 +2642,11 @@
         <v>79</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O6" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -2685,9 +2689,11 @@
         <v>82</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O7" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -2730,9 +2736,11 @@
         <v>85</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O8" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -2775,9 +2783,11 @@
         <v>88</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O9" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -2820,9 +2830,11 @@
         <v>92</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O10" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -2865,9 +2877,11 @@
         <v>95</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O11" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -2910,9 +2924,11 @@
         <v>97</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O12" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -2955,9 +2971,11 @@
         <v>100</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O13" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -3000,9 +3018,11 @@
         <v>103</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O14" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -3045,9 +3065,11 @@
         <v>105</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O15" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -3090,9 +3112,11 @@
         <v>107</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O16" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -3135,9 +3159,11 @@
         <v>109</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O17" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -3180,9 +3206,11 @@
         <v>113</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O18" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -3225,9 +3253,11 @@
         <v>117</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O19" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -3270,9 +3300,11 @@
         <v>120</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O20" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -3315,9 +3347,11 @@
         <v>122</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O21" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -3360,9 +3394,11 @@
         <v>126</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O22" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -3405,9 +3441,11 @@
         <v>128</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O23" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -3450,9 +3488,11 @@
         <v>130</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O24" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -3495,9 +3535,11 @@
         <v>132</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O25" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -3540,9 +3582,11 @@
         <v>134</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O26" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -3585,9 +3629,11 @@
         <v>136</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O27" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -3630,9 +3676,11 @@
         <v>138</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O28" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -3675,9 +3723,11 @@
         <v>140</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O29" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -3720,9 +3770,11 @@
         <v>143</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O30" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -3765,9 +3817,11 @@
         <v>145</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O31" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -3810,9 +3864,11 @@
         <v>147</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O32" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
@@ -3855,9 +3911,11 @@
         <v>149</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O33" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
@@ -3900,9 +3958,11 @@
         <v>151</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O34" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
@@ -3945,9 +4005,11 @@
         <v>155</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O35" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -3990,9 +4052,11 @@
         <v>158</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O36" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
@@ -4035,9 +4099,11 @@
         <v>161</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O37" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -4080,9 +4146,11 @@
         <v>164</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O38" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
@@ -4125,9 +4193,11 @@
         <v>166</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O39" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
@@ -4170,9 +4240,11 @@
         <v>168</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O40" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
@@ -4215,9 +4287,11 @@
         <v>171</v>
       </c>
       <c r="N41" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O41" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
@@ -4260,9 +4334,11 @@
         <v>173</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O42" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
@@ -4305,9 +4381,11 @@
         <v>175</v>
       </c>
       <c r="N43" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O43" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
@@ -4350,9 +4428,11 @@
         <v>177</v>
       </c>
       <c r="N44" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O44" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
@@ -4395,9 +4475,11 @@
         <v>180</v>
       </c>
       <c r="N45" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O45" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
@@ -4440,9 +4522,11 @@
         <v>182</v>
       </c>
       <c r="N46" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O46" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
@@ -4485,9 +4569,11 @@
         <v>184</v>
       </c>
       <c r="N47" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O47" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
@@ -4530,9 +4616,11 @@
         <v>187</v>
       </c>
       <c r="N48" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O48" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O48" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
@@ -4575,9 +4663,11 @@
         <v>189</v>
       </c>
       <c r="N49" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O49" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
@@ -4620,9 +4710,11 @@
         <v>191</v>
       </c>
       <c r="N50" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O50" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
@@ -4665,9 +4757,11 @@
         <v>194</v>
       </c>
       <c r="N51" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O51" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
@@ -4710,9 +4804,11 @@
         <v>196</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O52" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
@@ -4755,9 +4851,11 @@
         <v>198</v>
       </c>
       <c r="N53" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O53" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
@@ -4800,9 +4898,11 @@
         <v>201</v>
       </c>
       <c r="N54" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O54" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O54" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
@@ -4845,9 +4945,11 @@
         <v>203</v>
       </c>
       <c r="N55" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O55" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O55" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
@@ -4890,9 +4992,11 @@
         <v>206</v>
       </c>
       <c r="N56" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O56" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O56" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -4935,9 +5039,11 @@
         <v>209</v>
       </c>
       <c r="N57" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O57" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O57" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
@@ -4980,9 +5086,11 @@
         <v>211</v>
       </c>
       <c r="N58" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O58" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O58" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
@@ -5025,9 +5133,11 @@
         <v>213</v>
       </c>
       <c r="N59" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O59" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O59" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
@@ -5070,9 +5180,11 @@
         <v>215</v>
       </c>
       <c r="N60" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O60" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O60" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
@@ -5115,9 +5227,11 @@
         <v>217</v>
       </c>
       <c r="N61" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O61" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O61" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
@@ -5160,9 +5274,11 @@
         <v>219</v>
       </c>
       <c r="N62" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O62" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O62" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
@@ -5205,9 +5321,11 @@
         <v>222</v>
       </c>
       <c r="N63" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O63" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O63" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -5250,9 +5368,11 @@
         <v>224</v>
       </c>
       <c r="N64" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O64" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O64" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
@@ -5295,9 +5415,11 @@
         <v>226</v>
       </c>
       <c r="N65" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O65" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O65" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
@@ -5340,9 +5462,11 @@
         <v>229</v>
       </c>
       <c r="N66" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O66" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O66" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
@@ -5385,9 +5509,11 @@
         <v>232</v>
       </c>
       <c r="N67" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O67" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O67" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
@@ -5430,9 +5556,11 @@
         <v>235</v>
       </c>
       <c r="N68" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O68" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O68" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
@@ -5475,9 +5603,11 @@
         <v>237</v>
       </c>
       <c r="N69" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O69" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
@@ -5520,9 +5650,11 @@
         <v>239</v>
       </c>
       <c r="N70" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O70" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O70" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
@@ -5565,9 +5697,11 @@
         <v>241</v>
       </c>
       <c r="N71" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O71" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O71" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
@@ -5610,9 +5744,11 @@
         <v>244</v>
       </c>
       <c r="N72" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O72" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O72" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
@@ -5655,9 +5791,11 @@
         <v>246</v>
       </c>
       <c r="N73" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O73" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O73" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
@@ -5700,9 +5838,11 @@
         <v>247</v>
       </c>
       <c r="N74" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O74" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O74" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
@@ -5745,9 +5885,11 @@
         <v>249</v>
       </c>
       <c r="N75" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O75" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O75" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
@@ -5790,9 +5932,11 @@
         <v>250</v>
       </c>
       <c r="N76" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O76" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O76" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
@@ -5835,9 +5979,11 @@
         <v>253</v>
       </c>
       <c r="N77" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O77" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O77" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
@@ -5880,9 +6026,11 @@
         <v>254</v>
       </c>
       <c r="N78" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O78" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O78" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
@@ -5925,9 +6073,11 @@
         <v>255</v>
       </c>
       <c r="N79" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O79" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O79" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
@@ -5970,9 +6120,11 @@
         <v>256</v>
       </c>
       <c r="N80" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O80" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O80" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
@@ -6015,9 +6167,11 @@
         <v>258</v>
       </c>
       <c r="N81" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O81" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O81" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
@@ -6060,9 +6214,11 @@
         <v>259</v>
       </c>
       <c r="N82" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O82" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O82" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
@@ -6105,9 +6261,11 @@
         <v>261</v>
       </c>
       <c r="N83" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O83" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O83" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
@@ -6150,9 +6308,11 @@
         <v>263</v>
       </c>
       <c r="N84" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O84" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O84" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
@@ -6195,9 +6355,11 @@
         <v>265</v>
       </c>
       <c r="N85" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O85" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O85" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
@@ -6240,9 +6402,11 @@
         <v>267</v>
       </c>
       <c r="N86" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O86" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O86" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
@@ -6285,9 +6449,11 @@
         <v>269</v>
       </c>
       <c r="N87" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O87" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O87" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
@@ -6330,9 +6496,11 @@
         <v>271</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O88" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O88" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
@@ -6375,9 +6543,11 @@
         <v>274</v>
       </c>
       <c r="N89" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O89" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O89" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
@@ -6420,9 +6590,11 @@
         <v>277</v>
       </c>
       <c r="N90" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O90" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O90" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
@@ -6465,9 +6637,11 @@
         <v>280</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O91" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O91" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
@@ -6510,9 +6684,11 @@
         <v>282</v>
       </c>
       <c r="N92" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O92" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O92" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
@@ -6555,9 +6731,11 @@
         <v>284</v>
       </c>
       <c r="N93" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O93" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O93" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
@@ -6600,9 +6778,11 @@
         <v>286</v>
       </c>
       <c r="N94" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O94" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O94" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
@@ -6645,9 +6825,11 @@
         <v>288</v>
       </c>
       <c r="N95" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O95" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O95" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
@@ -6690,9 +6872,11 @@
         <v>290</v>
       </c>
       <c r="N96" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O96" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O96" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
@@ -6735,9 +6919,11 @@
         <v>292</v>
       </c>
       <c r="N97" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O97" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O97" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
@@ -6780,9 +6966,11 @@
         <v>295</v>
       </c>
       <c r="N98" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O98" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O98" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
@@ -6825,9 +7013,11 @@
         <v>298</v>
       </c>
       <c r="N99" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O99" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O99" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
@@ -6870,9 +7060,11 @@
         <v>300</v>
       </c>
       <c r="N100" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O100" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O100" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
@@ -6915,9 +7107,11 @@
         <v>302</v>
       </c>
       <c r="N101" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O101" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O101" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
@@ -6960,9 +7154,11 @@
         <v>304</v>
       </c>
       <c r="N102" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O102" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O102" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
@@ -7005,9 +7201,11 @@
         <v>306</v>
       </c>
       <c r="N103" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O103" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O103" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
@@ -7050,9 +7248,11 @@
         <v>309</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O104" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O104" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
@@ -7095,9 +7295,11 @@
         <v>311</v>
       </c>
       <c r="N105" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O105" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O105" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
@@ -7140,9 +7342,11 @@
         <v>313</v>
       </c>
       <c r="N106" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O106" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O106" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
@@ -7185,9 +7389,11 @@
         <v>316</v>
       </c>
       <c r="N107" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="O107" s="5"/>
+        <v>641</v>
+      </c>
+      <c r="O107" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
@@ -7229,8 +7435,12 @@
       <c r="M108" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="N108" s="5"/>
-      <c r="O108" s="5"/>
+      <c r="N108" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O108" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
@@ -7272,8 +7482,12 @@
       <c r="M109" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="N109" s="5"/>
-      <c r="O109" s="5"/>
+      <c r="N109" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O109" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
@@ -7315,8 +7529,12 @@
       <c r="M110" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="N110" s="5"/>
-      <c r="O110" s="5"/>
+      <c r="N110" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O110" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
@@ -7358,8 +7576,12 @@
       <c r="M111" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="N111" s="5"/>
-      <c r="O111" s="5"/>
+      <c r="N111" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O111" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -7401,8 +7623,12 @@
       <c r="M112" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="N112" s="5"/>
-      <c r="O112" s="5"/>
+      <c r="N112" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O112" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
@@ -7444,8 +7670,12 @@
       <c r="M113" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="N113" s="5"/>
-      <c r="O113" s="5"/>
+      <c r="N113" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O113" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
@@ -7487,8 +7717,12 @@
       <c r="M114" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="N114" s="5"/>
-      <c r="O114" s="5"/>
+      <c r="N114" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O114" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
@@ -7530,8 +7764,12 @@
       <c r="M115" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="N115" s="5"/>
-      <c r="O115" s="5"/>
+      <c r="N115" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O115" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
@@ -7573,8 +7811,12 @@
       <c r="M116" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="N116" s="5"/>
-      <c r="O116" s="5"/>
+      <c r="N116" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O116" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
@@ -7616,8 +7858,12 @@
       <c r="M117" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="N117" s="5"/>
-      <c r="O117" s="5"/>
+      <c r="N117" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O117" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
@@ -7659,8 +7905,12 @@
       <c r="M118" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="N118" s="5"/>
-      <c r="O118" s="5"/>
+      <c r="N118" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O118" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
@@ -7702,8 +7952,12 @@
       <c r="M119" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="N119" s="5"/>
-      <c r="O119" s="5"/>
+      <c r="N119" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O119" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
@@ -7745,8 +7999,12 @@
       <c r="M120" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="N120" s="5"/>
-      <c r="O120" s="5"/>
+      <c r="N120" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O120" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
@@ -7788,8 +8046,12 @@
       <c r="M121" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="N121" s="5"/>
-      <c r="O121" s="5"/>
+      <c r="N121" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O121" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
@@ -7831,8 +8093,12 @@
       <c r="M122" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="N122" s="5"/>
-      <c r="O122" s="5"/>
+      <c r="N122" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O122" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
@@ -7874,8 +8140,12 @@
       <c r="M123" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="N123" s="5"/>
-      <c r="O123" s="5"/>
+      <c r="N123" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O123" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
@@ -7917,8 +8187,12 @@
       <c r="M124" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="N124" s="5"/>
-      <c r="O124" s="5"/>
+      <c r="N124" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O124" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
@@ -7960,8 +8234,12 @@
       <c r="M125" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="N125" s="5"/>
-      <c r="O125" s="5"/>
+      <c r="N125" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O125" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
@@ -8003,8 +8281,12 @@
       <c r="M126" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="N126" s="5"/>
-      <c r="O126" s="5"/>
+      <c r="N126" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O126" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
@@ -8046,8 +8328,12 @@
       <c r="M127" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="N127" s="5"/>
-      <c r="O127" s="5"/>
+      <c r="N127" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O127" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
@@ -8089,8 +8375,12 @@
       <c r="M128" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="N128" s="5"/>
-      <c r="O128" s="5"/>
+      <c r="N128" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O128" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
@@ -8132,8 +8422,12 @@
       <c r="M129" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="N129" s="5"/>
-      <c r="O129" s="5"/>
+      <c r="N129" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O129" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
@@ -8175,8 +8469,12 @@
       <c r="M130" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="N130" s="5"/>
-      <c r="O130" s="5"/>
+      <c r="N130" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O130" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
@@ -8218,8 +8516,12 @@
       <c r="M131" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="N131" s="5"/>
-      <c r="O131" s="5"/>
+      <c r="N131" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O131" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
@@ -8261,8 +8563,12 @@
       <c r="M132" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="N132" s="5"/>
-      <c r="O132" s="5"/>
+      <c r="N132" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O132" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
@@ -8304,8 +8610,12 @@
       <c r="M133" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="N133" s="5"/>
-      <c r="O133" s="5"/>
+      <c r="N133" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O133" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
@@ -8347,8 +8657,12 @@
       <c r="M134" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="N134" s="5"/>
-      <c r="O134" s="5"/>
+      <c r="N134" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O134" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
@@ -8390,8 +8704,12 @@
       <c r="M135" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="N135" s="5"/>
-      <c r="O135" s="5"/>
+      <c r="N135" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O135" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
@@ -8433,8 +8751,12 @@
       <c r="M136" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="N136" s="5"/>
-      <c r="O136" s="5"/>
+      <c r="N136" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O136" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
@@ -8476,8 +8798,12 @@
       <c r="M137" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="N137" s="5"/>
-      <c r="O137" s="5"/>
+      <c r="N137" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O137" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
@@ -8519,8 +8845,12 @@
       <c r="M138" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="N138" s="5"/>
-      <c r="O138" s="5"/>
+      <c r="N138" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O138" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
@@ -8562,8 +8892,12 @@
       <c r="M139" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="N139" s="5"/>
-      <c r="O139" s="5"/>
+      <c r="N139" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O139" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
@@ -8605,8 +8939,12 @@
       <c r="M140" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="N140" s="5"/>
-      <c r="O140" s="5"/>
+      <c r="N140" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O140" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
@@ -8616,13 +8954,13 @@
         <v>90</v>
       </c>
       <c r="C141" s="5">
-        <v>14205095</v>
+        <v>14205114</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E141" s="5">
-        <v>685434</v>
+        <v>685421</v>
       </c>
       <c r="F141" s="5">
         <v>4</v>
@@ -8648,8 +8986,12 @@
       <c r="M141" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="N141" s="5"/>
-      <c r="O141" s="5"/>
+      <c r="N141" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O141" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
@@ -8659,13 +9001,13 @@
         <v>90</v>
       </c>
       <c r="C142" s="5">
-        <v>14205114</v>
+        <v>14205121</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E142" s="5">
-        <v>685421</v>
+        <v>685434</v>
       </c>
       <c r="F142" s="5">
         <v>4</v>
@@ -8691,8 +9033,12 @@
       <c r="M142" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="N142" s="5"/>
-      <c r="O142" s="5"/>
+      <c r="N142" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O142" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
@@ -8702,7 +9048,7 @@
         <v>90</v>
       </c>
       <c r="C143" s="5">
-        <v>14205121</v>
+        <v>14205123</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>65</v>
@@ -8734,8 +9080,12 @@
       <c r="M143" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="N143" s="5"/>
-      <c r="O143" s="5"/>
+      <c r="N143" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O143" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
@@ -8745,7 +9095,7 @@
         <v>90</v>
       </c>
       <c r="C144" s="5">
-        <v>14205123</v>
+        <v>14205133</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>65</v>
@@ -8777,8 +9127,12 @@
       <c r="M144" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="N144" s="5"/>
-      <c r="O144" s="5"/>
+      <c r="N144" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O144" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
@@ -8788,7 +9142,7 @@
         <v>90</v>
       </c>
       <c r="C145" s="5">
-        <v>14205133</v>
+        <v>14205138</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>65</v>
@@ -8820,8 +9174,12 @@
       <c r="M145" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="N145" s="5"/>
-      <c r="O145" s="5"/>
+      <c r="N145" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O145" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
@@ -8831,13 +9189,13 @@
         <v>90</v>
       </c>
       <c r="C146" s="5">
-        <v>14205138</v>
+        <v>14205176</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E146" s="5">
-        <v>685434</v>
+        <v>685546</v>
       </c>
       <c r="F146" s="5">
         <v>4</v>
@@ -8846,41 +9204,45 @@
         <v>1</v>
       </c>
       <c r="H146" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I146" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="I146" s="5" t="s">
-        <v>383</v>
-      </c>
       <c r="J146" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K146" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L146" s="5">
-        <v>400</v>
+      <c r="L146" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="M146" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="N146" s="5"/>
-      <c r="O146" s="5"/>
+      <c r="N146" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O146" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>39</v>
+        <v>403</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="C147" s="5">
-        <v>14205176</v>
+        <v>14205400</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E147" s="5">
-        <v>685546</v>
+        <v>685421</v>
       </c>
       <c r="F147" s="5">
         <v>4</v>
@@ -8888,11 +9250,11 @@
       <c r="G147" s="5">
         <v>1</v>
       </c>
-      <c r="H147" s="5" t="s">
-        <v>153</v>
+      <c r="H147" s="5">
+        <v>4705401045</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J147" s="5" t="s">
         <v>68</v>
@@ -8901,38 +9263,42 @@
         <v>69</v>
       </c>
       <c r="L147" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M147" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="N147" s="5"/>
-      <c r="O147" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="N147" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O147" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="C148" s="5">
-        <v>14205400</v>
+        <v>14205405</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E148" s="5">
-        <v>685421</v>
+        <v>685481</v>
       </c>
       <c r="F148" s="5">
         <v>4</v>
       </c>
       <c r="G148" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H148" s="5">
-        <v>4705401045</v>
+        <v>4716502682</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>406</v>
@@ -8944,41 +9310,45 @@
         <v>69</v>
       </c>
       <c r="L148" s="5" t="s">
-        <v>18</v>
+        <v>407</v>
       </c>
       <c r="M148" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="N148" s="5"/>
-      <c r="O148" s="5"/>
+        <v>408</v>
+      </c>
+      <c r="N148" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O148" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C149" s="5">
-        <v>14205405</v>
+        <v>14205410</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E149" s="5">
-        <v>685481</v>
+        <v>685702</v>
       </c>
       <c r="F149" s="5">
         <v>4</v>
       </c>
       <c r="G149" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H149" s="5">
-        <v>4716502682</v>
+        <v>4716509405</v>
       </c>
       <c r="I149" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J149" s="5" t="s">
         <v>68</v>
@@ -8987,38 +9357,42 @@
         <v>69</v>
       </c>
       <c r="L149" s="5" t="s">
-        <v>409</v>
+        <v>41</v>
       </c>
       <c r="M149" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="N149" s="5"/>
-      <c r="O149" s="5"/>
+      <c r="N149" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O149" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="C150" s="5">
-        <v>14205410</v>
+        <v>14205413</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E150" s="5">
-        <v>685702</v>
+        <v>685557</v>
       </c>
       <c r="F150" s="5">
         <v>4</v>
       </c>
       <c r="G150" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H150" s="5">
-        <v>4716509405</v>
+        <v>4738360639</v>
       </c>
       <c r="I150" s="5" t="s">
         <v>411</v>
@@ -9030,23 +9404,27 @@
         <v>69</v>
       </c>
       <c r="L150" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M150" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="N150" s="5"/>
-      <c r="O150" s="5"/>
+      <c r="N150" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O150" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>321</v>
       </c>
       <c r="C151" s="5">
-        <v>14205413</v>
+        <v>14205414</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>65</v>
@@ -9058,10 +9436,10 @@
         <v>4</v>
       </c>
       <c r="G151" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H151" s="5">
-        <v>4738360639</v>
+        <v>4738360638</v>
       </c>
       <c r="I151" s="5" t="s">
         <v>413</v>
@@ -9078,33 +9456,37 @@
       <c r="M151" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="N151" s="5"/>
-      <c r="O151" s="5"/>
+      <c r="N151" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O151" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="C152" s="5">
-        <v>14205414</v>
+        <v>14205417</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E152" s="5">
-        <v>685557</v>
+        <v>685546</v>
       </c>
       <c r="F152" s="5">
         <v>4</v>
       </c>
       <c r="G152" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H152" s="5">
-        <v>4738360638</v>
+        <v>4714900224</v>
       </c>
       <c r="I152" s="5" t="s">
         <v>415</v>
@@ -9116,29 +9498,33 @@
         <v>69</v>
       </c>
       <c r="L152" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M152" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="N152" s="5"/>
-      <c r="O152" s="5"/>
+      <c r="N152" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O152" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="C153" s="5">
-        <v>14205417</v>
+        <v>14205419</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E153" s="5">
-        <v>685546</v>
+        <v>685434</v>
       </c>
       <c r="F153" s="5">
         <v>4</v>
@@ -9147,7 +9533,7 @@
         <v>2</v>
       </c>
       <c r="H153" s="5">
-        <v>4714900224</v>
+        <v>4705402472</v>
       </c>
       <c r="I153" s="5" t="s">
         <v>417</v>
@@ -9159,41 +9545,45 @@
         <v>69</v>
       </c>
       <c r="L153" s="5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="M153" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="N153" s="5"/>
-      <c r="O153" s="5"/>
+      <c r="N153" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O153" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="C154" s="5">
-        <v>14205419</v>
+        <v>14205422</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E154" s="5">
-        <v>685434</v>
+        <v>685435</v>
       </c>
       <c r="F154" s="5">
         <v>4</v>
       </c>
       <c r="G154" s="5">
-        <v>2</v>
-      </c>
-      <c r="H154" s="5">
-        <v>4705402472</v>
+        <v>1</v>
+      </c>
+      <c r="H154" s="5" t="s">
+        <v>419</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>419</v>
+        <v>67</v>
       </c>
       <c r="J154" s="5" t="s">
         <v>68</v>
@@ -9201,30 +9591,34 @@
       <c r="K154" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L154" s="5" t="s">
-        <v>24</v>
+      <c r="L154" s="5">
+        <v>600</v>
       </c>
       <c r="M154" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="N154" s="5"/>
-      <c r="O154" s="5"/>
+      <c r="N154" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O154" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C155" s="5">
-        <v>14205422</v>
+        <v>14205426</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E155" s="5">
-        <v>685435</v>
+        <v>685705</v>
       </c>
       <c r="F155" s="5">
         <v>4</v>
@@ -9245,29 +9639,33 @@
         <v>69</v>
       </c>
       <c r="L155" s="5">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M155" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="N155" s="5"/>
-      <c r="O155" s="5"/>
+      <c r="N155" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O155" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C156" s="5">
-        <v>14205426</v>
+        <v>14205427</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E156" s="5">
-        <v>685705</v>
+        <v>685434</v>
       </c>
       <c r="F156" s="5">
         <v>4</v>
@@ -9279,7 +9677,7 @@
         <v>423</v>
       </c>
       <c r="I156" s="5" t="s">
-        <v>67</v>
+        <v>383</v>
       </c>
       <c r="J156" s="5" t="s">
         <v>68</v>
@@ -9288,29 +9686,33 @@
         <v>69</v>
       </c>
       <c r="L156" s="5">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M156" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="N156" s="5"/>
-      <c r="O156" s="5"/>
+      <c r="N156" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O156" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C157" s="5">
-        <v>14205427</v>
+        <v>14205428</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E157" s="5">
-        <v>685434</v>
+        <v>685433</v>
       </c>
       <c r="F157" s="5">
         <v>4</v>
@@ -9322,7 +9724,7 @@
         <v>425</v>
       </c>
       <c r="I157" s="5" t="s">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="J157" s="5" t="s">
         <v>68</v>
@@ -9330,30 +9732,34 @@
       <c r="K157" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L157" s="5">
-        <v>400</v>
+      <c r="L157" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="M157" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="N157" s="5"/>
-      <c r="O157" s="5"/>
+        <v>427</v>
+      </c>
+      <c r="N157" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O157" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C158" s="5">
-        <v>14205428</v>
+        <v>14205431</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E158" s="5">
-        <v>685433</v>
+        <v>685541</v>
       </c>
       <c r="F158" s="5">
         <v>4</v>
@@ -9362,10 +9768,10 @@
         <v>1</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>428</v>
+        <v>119</v>
       </c>
       <c r="J158" s="5" t="s">
         <v>68</v>
@@ -9373,24 +9779,28 @@
       <c r="K158" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L158" s="5" t="s">
-        <v>13</v>
+      <c r="L158" s="5">
+        <v>800</v>
       </c>
       <c r="M158" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="N158" s="5"/>
-      <c r="O158" s="5"/>
+      <c r="N158" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O158" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C159" s="5">
-        <v>14205431</v>
+        <v>14205433</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>65</v>
@@ -9422,24 +9832,28 @@
       <c r="M159" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="N159" s="5"/>
-      <c r="O159" s="5"/>
+      <c r="N159" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O159" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C160" s="5">
-        <v>14205433</v>
+        <v>14205438</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E160" s="5">
-        <v>685541</v>
+        <v>685485</v>
       </c>
       <c r="F160" s="5">
         <v>4</v>
@@ -9451,7 +9865,7 @@
         <v>432</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>119</v>
+        <v>433</v>
       </c>
       <c r="J160" s="5" t="s">
         <v>68</v>
@@ -9459,30 +9873,34 @@
       <c r="K160" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L160" s="5">
-        <v>800</v>
+      <c r="L160" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="M160" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="N160" s="5"/>
-      <c r="O160" s="5"/>
+        <v>434</v>
+      </c>
+      <c r="N160" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O160" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C161" s="5">
-        <v>14205438</v>
+        <v>14205440</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E161" s="5">
-        <v>685485</v>
+        <v>685554</v>
       </c>
       <c r="F161" s="5">
         <v>4</v>
@@ -9491,10 +9909,10 @@
         <v>1</v>
       </c>
       <c r="H161" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I161" s="5" t="s">
-        <v>435</v>
+        <v>84</v>
       </c>
       <c r="J161" s="5" t="s">
         <v>68</v>
@@ -9502,30 +9920,34 @@
       <c r="K161" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L161" s="5" t="s">
-        <v>34</v>
+      <c r="L161" s="5">
+        <v>600</v>
       </c>
       <c r="M161" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="N161" s="5"/>
-      <c r="O161" s="5"/>
+      <c r="N161" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O161" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C162" s="5">
-        <v>14205440</v>
+        <v>14205442</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E162" s="5">
-        <v>685554</v>
+        <v>685867</v>
       </c>
       <c r="F162" s="5">
         <v>4</v>
@@ -9537,7 +9959,7 @@
         <v>437</v>
       </c>
       <c r="I162" s="5" t="s">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="J162" s="5" t="s">
         <v>68</v>
@@ -9546,29 +9968,33 @@
         <v>69</v>
       </c>
       <c r="L162" s="5">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="M162" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="N162" s="5"/>
-      <c r="O162" s="5"/>
+        <v>439</v>
+      </c>
+      <c r="N162" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O162" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C163" s="5">
-        <v>14205442</v>
+        <v>14205443</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E163" s="5">
-        <v>685867</v>
+        <v>685551</v>
       </c>
       <c r="F163" s="5">
         <v>4</v>
@@ -9577,10 +10003,10 @@
         <v>1</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I163" s="5" t="s">
-        <v>440</v>
+        <v>112</v>
       </c>
       <c r="J163" s="5" t="s">
         <v>68</v>
@@ -9589,29 +10015,33 @@
         <v>69</v>
       </c>
       <c r="L163" s="5">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="M163" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="N163" s="5"/>
-      <c r="O163" s="5"/>
+      <c r="N163" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="O163" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C164" s="5">
-        <v>14205443</v>
+        <v>14205449</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E164" s="5">
-        <v>685551</v>
+        <v>685421</v>
       </c>
       <c r="F164" s="5">
         <v>4</v>
@@ -9623,7 +10053,7 @@
         <v>442</v>
       </c>
       <c r="I164" s="5" t="s">
-        <v>112</v>
+        <v>383</v>
       </c>
       <c r="J164" s="5" t="s">
         <v>68</v>
@@ -9632,29 +10062,31 @@
         <v>69</v>
       </c>
       <c r="L164" s="5">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="M164" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="N164" s="5"/>
+      <c r="N164" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O164" s="5"/>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C165" s="5">
-        <v>14205449</v>
+        <v>14205450</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E165" s="5">
-        <v>685421</v>
+        <v>685434</v>
       </c>
       <c r="F165" s="5">
         <v>4</v>
@@ -9680,24 +10112,26 @@
       <c r="M165" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="N165" s="5"/>
+      <c r="N165" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O165" s="5"/>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>405</v>
+        <v>40</v>
       </c>
       <c r="B166" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C166" s="5">
-        <v>14205450</v>
+        <v>14205807</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E166" s="5">
-        <v>685434</v>
+        <v>685411</v>
       </c>
       <c r="F166" s="5">
         <v>4</v>
@@ -9709,7 +10143,7 @@
         <v>446</v>
       </c>
       <c r="I166" s="5" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="J166" s="5" t="s">
         <v>68</v>
@@ -9717,13 +10151,15 @@
       <c r="K166" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L166" s="5">
-        <v>400</v>
+      <c r="L166" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="M166" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="N166" s="5"/>
+        <v>448</v>
+      </c>
+      <c r="N166" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O166" s="5"/>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
@@ -9734,7 +10170,7 @@
         <v>90</v>
       </c>
       <c r="C167" s="5">
-        <v>14205807</v>
+        <v>14205811</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>65</v>
@@ -9749,10 +10185,10 @@
         <v>1</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I167" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J167" s="5" t="s">
         <v>68</v>
@@ -9766,7 +10202,9 @@
       <c r="M167" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="N167" s="5"/>
+      <c r="N167" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O167" s="5"/>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
@@ -9777,13 +10215,13 @@
         <v>90</v>
       </c>
       <c r="C168" s="5">
-        <v>14205811</v>
+        <v>14205817</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E168" s="5">
-        <v>685411</v>
+        <v>685434</v>
       </c>
       <c r="F168" s="5">
         <v>4</v>
@@ -9795,7 +10233,7 @@
         <v>451</v>
       </c>
       <c r="I168" s="5" t="s">
-        <v>449</v>
+        <v>112</v>
       </c>
       <c r="J168" s="5" t="s">
         <v>68</v>
@@ -9803,13 +10241,15 @@
       <c r="K168" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L168" s="5" t="s">
-        <v>13</v>
+      <c r="L168" s="5">
+        <v>400</v>
       </c>
       <c r="M168" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="N168" s="5"/>
+      <c r="N168" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O168" s="5"/>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
@@ -9820,7 +10260,7 @@
         <v>90</v>
       </c>
       <c r="C169" s="5">
-        <v>14205817</v>
+        <v>14205819</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>65</v>
@@ -9852,7 +10292,9 @@
       <c r="M169" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="N169" s="5"/>
+      <c r="N169" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O169" s="5"/>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
@@ -9863,7 +10305,7 @@
         <v>90</v>
       </c>
       <c r="C170" s="5">
-        <v>14205819</v>
+        <v>14205822</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>65</v>
@@ -9895,24 +10337,26 @@
       <c r="M170" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="N170" s="5"/>
+      <c r="N170" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O170" s="5"/>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>90</v>
+        <v>214</v>
       </c>
       <c r="C171" s="5">
-        <v>14205822</v>
+        <v>14207983</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E171" s="5">
-        <v>685434</v>
+        <v>685914</v>
       </c>
       <c r="F171" s="5">
         <v>4</v>
@@ -9920,42 +10364,44 @@
       <c r="G171" s="5">
         <v>1</v>
       </c>
-      <c r="H171" s="5" t="s">
+      <c r="H171" s="5">
+        <v>4738361081</v>
+      </c>
+      <c r="I171" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="I171" s="5" t="s">
-        <v>112</v>
-      </c>
       <c r="J171" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K171" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L171" s="5">
-        <v>400</v>
+      <c r="L171" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="M171" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="N171" s="5"/>
+      <c r="N171" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O171" s="5"/>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>214</v>
+        <v>90</v>
       </c>
       <c r="C172" s="5">
-        <v>14207983</v>
+        <v>14208889</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E172" s="5">
-        <v>685914</v>
+        <v>685556</v>
       </c>
       <c r="F172" s="5">
         <v>4</v>
@@ -9963,11 +10409,11 @@
       <c r="G172" s="5">
         <v>1</v>
       </c>
-      <c r="H172" s="5">
-        <v>4738361081</v>
+      <c r="H172" s="5" t="s">
+        <v>459</v>
       </c>
       <c r="I172" s="5" t="s">
-        <v>459</v>
+        <v>112</v>
       </c>
       <c r="J172" s="5" t="s">
         <v>68</v>
@@ -9975,13 +10421,15 @@
       <c r="K172" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L172" s="5" t="s">
-        <v>24</v>
+      <c r="L172" s="5">
+        <v>800</v>
       </c>
       <c r="M172" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="N172" s="5"/>
+      <c r="N172" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O172" s="5"/>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
@@ -9992,13 +10440,13 @@
         <v>90</v>
       </c>
       <c r="C173" s="5">
-        <v>14208889</v>
+        <v>14208892</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E173" s="5">
-        <v>685556</v>
+        <v>685485</v>
       </c>
       <c r="F173" s="5">
         <v>4</v>
@@ -10019,12 +10467,14 @@
         <v>69</v>
       </c>
       <c r="L173" s="5">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="M173" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="N173" s="5"/>
+      <c r="N173" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O173" s="5"/>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
@@ -10035,13 +10485,13 @@
         <v>90</v>
       </c>
       <c r="C174" s="5">
-        <v>14208892</v>
+        <v>14208897</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E174" s="5">
-        <v>685485</v>
+        <v>685401</v>
       </c>
       <c r="F174" s="5">
         <v>4</v>
@@ -10053,7 +10503,7 @@
         <v>463</v>
       </c>
       <c r="I174" s="5" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="J174" s="5" t="s">
         <v>68</v>
@@ -10067,7 +10517,9 @@
       <c r="M174" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="N174" s="5"/>
+      <c r="N174" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O174" s="5"/>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
@@ -10078,13 +10530,13 @@
         <v>90</v>
       </c>
       <c r="C175" s="5">
-        <v>14208897</v>
+        <v>14209030</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E175" s="5">
-        <v>685401</v>
+        <v>685484</v>
       </c>
       <c r="F175" s="5">
         <v>4</v>
@@ -10096,7 +10548,7 @@
         <v>465</v>
       </c>
       <c r="I175" s="5" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="J175" s="5" t="s">
         <v>68</v>
@@ -10110,7 +10562,9 @@
       <c r="M175" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="N175" s="5"/>
+      <c r="N175" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O175" s="5"/>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
@@ -10121,7 +10575,7 @@
         <v>90</v>
       </c>
       <c r="C176" s="5">
-        <v>14209030</v>
+        <v>14209038</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>65</v>
@@ -10153,50 +10607,54 @@
       <c r="M176" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="N176" s="5"/>
+      <c r="N176" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O176" s="5"/>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="C177" s="5">
-        <v>14209038</v>
+        <v>14210061</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E177" s="5">
-        <v>685484</v>
+        <v>685702</v>
       </c>
       <c r="F177" s="5">
         <v>4</v>
       </c>
       <c r="G177" s="5">
-        <v>1</v>
-      </c>
-      <c r="H177" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H177" s="5">
+        <v>4738360873</v>
+      </c>
+      <c r="I177" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="I177" s="5" t="s">
-        <v>112</v>
-      </c>
       <c r="J177" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K177" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L177" s="5">
-        <v>400</v>
+      <c r="L177" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="M177" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="N177" s="5"/>
+      <c r="N177" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O177" s="5"/>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
@@ -10204,28 +10662,28 @@
         <v>49</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="C178" s="5">
-        <v>14210061</v>
+        <v>14210142</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E178" s="5">
-        <v>685702</v>
+        <v>685401</v>
       </c>
       <c r="F178" s="5">
         <v>4</v>
       </c>
       <c r="G178" s="5">
-        <v>2</v>
-      </c>
-      <c r="H178" s="5">
-        <v>4738360873</v>
+        <v>1</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>471</v>
       </c>
       <c r="I178" s="5" t="s">
-        <v>471</v>
+        <v>67</v>
       </c>
       <c r="J178" s="5" t="s">
         <v>68</v>
@@ -10234,12 +10692,14 @@
         <v>69</v>
       </c>
       <c r="L178" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="M178" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="N178" s="5"/>
+      <c r="N178" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O178" s="5"/>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
@@ -10247,16 +10707,16 @@
         <v>49</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="C179" s="5">
-        <v>14210142</v>
+        <v>14210206</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E179" s="5">
-        <v>685401</v>
+        <v>685485</v>
       </c>
       <c r="F179" s="5">
         <v>4</v>
@@ -10268,7 +10728,7 @@
         <v>473</v>
       </c>
       <c r="I179" s="5" t="s">
-        <v>67</v>
+        <v>474</v>
       </c>
       <c r="J179" s="5" t="s">
         <v>68</v>
@@ -10277,12 +10737,14 @@
         <v>69</v>
       </c>
       <c r="L179" s="5" t="s">
-        <v>20</v>
+        <v>475</v>
       </c>
       <c r="M179" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="N179" s="5"/>
+        <v>476</v>
+      </c>
+      <c r="N179" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O179" s="5"/>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
@@ -10290,10 +10752,10 @@
         <v>49</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>321</v>
+        <v>477</v>
       </c>
       <c r="C180" s="5">
-        <v>14210206</v>
+        <v>14210212</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>65</v>
@@ -10307,11 +10769,11 @@
       <c r="G180" s="5">
         <v>1</v>
       </c>
-      <c r="H180" s="5" t="s">
-        <v>475</v>
+      <c r="H180" s="5">
+        <v>4738360871</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J180" s="5" t="s">
         <v>68</v>
@@ -10320,29 +10782,31 @@
         <v>69</v>
       </c>
       <c r="L180" s="5" t="s">
-        <v>477</v>
+        <v>18</v>
       </c>
       <c r="M180" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="N180" s="5"/>
+        <v>479</v>
+      </c>
+      <c r="N180" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O180" s="5"/>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>479</v>
+        <v>90</v>
       </c>
       <c r="C181" s="5">
-        <v>14210212</v>
+        <v>14210798</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E181" s="5">
-        <v>685485</v>
+        <v>685606</v>
       </c>
       <c r="F181" s="5">
         <v>4</v>
@@ -10350,11 +10814,11 @@
       <c r="G181" s="5">
         <v>1</v>
       </c>
-      <c r="H181" s="5">
-        <v>4738360871</v>
+      <c r="H181" s="5" t="s">
+        <v>480</v>
       </c>
       <c r="I181" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J181" s="5" t="s">
         <v>68</v>
@@ -10362,13 +10826,15 @@
       <c r="K181" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L181" s="5" t="s">
-        <v>18</v>
+      <c r="L181" s="5">
+        <v>400</v>
       </c>
       <c r="M181" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="N181" s="5"/>
+        <v>482</v>
+      </c>
+      <c r="N181" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O181" s="5"/>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.25">
@@ -10379,13 +10845,13 @@
         <v>90</v>
       </c>
       <c r="C182" s="5">
-        <v>14210798</v>
+        <v>14210800</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E182" s="5">
-        <v>685606</v>
+        <v>685605</v>
       </c>
       <c r="F182" s="5">
         <v>4</v>
@@ -10394,10 +10860,10 @@
         <v>1</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I182" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J182" s="5" t="s">
         <v>68</v>
@@ -10411,7 +10877,9 @@
       <c r="M182" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="N182" s="5"/>
+      <c r="N182" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O182" s="5"/>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
@@ -10422,13 +10890,13 @@
         <v>90</v>
       </c>
       <c r="C183" s="5">
-        <v>14210800</v>
+        <v>14210802</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E183" s="5">
-        <v>685605</v>
+        <v>685616</v>
       </c>
       <c r="F183" s="5">
         <v>4</v>
@@ -10440,7 +10908,7 @@
         <v>485</v>
       </c>
       <c r="I183" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J183" s="5" t="s">
         <v>68</v>
@@ -10454,7 +10922,9 @@
       <c r="M183" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="N183" s="5"/>
+      <c r="N183" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O183" s="5"/>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
@@ -10465,13 +10935,13 @@
         <v>90</v>
       </c>
       <c r="C184" s="5">
-        <v>14210802</v>
+        <v>14210811</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E184" s="5">
-        <v>685616</v>
+        <v>685114</v>
       </c>
       <c r="F184" s="5">
         <v>4</v>
@@ -10483,7 +10953,7 @@
         <v>487</v>
       </c>
       <c r="I184" s="5" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="J184" s="5" t="s">
         <v>68</v>
@@ -10495,9 +10965,11 @@
         <v>400</v>
       </c>
       <c r="M184" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="N184" s="5"/>
+        <v>489</v>
+      </c>
+      <c r="N184" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O184" s="5"/>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
@@ -10508,13 +10980,13 @@
         <v>90</v>
       </c>
       <c r="C185" s="5">
-        <v>14210811</v>
+        <v>14210814</v>
       </c>
       <c r="D185" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E185" s="5">
-        <v>685114</v>
+        <v>685433</v>
       </c>
       <c r="F185" s="5">
         <v>4</v>
@@ -10523,10 +10995,10 @@
         <v>1</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I185" s="5" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="J185" s="5" t="s">
         <v>68</v>
@@ -10540,7 +11012,9 @@
       <c r="M185" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="N185" s="5"/>
+      <c r="N185" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O185" s="5"/>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
@@ -10551,13 +11025,13 @@
         <v>90</v>
       </c>
       <c r="C186" s="5">
-        <v>14210814</v>
+        <v>14210827</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E186" s="5">
-        <v>685433</v>
+        <v>685431</v>
       </c>
       <c r="F186" s="5">
         <v>4</v>
@@ -10569,7 +11043,7 @@
         <v>492</v>
       </c>
       <c r="I186" s="5" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="J186" s="5" t="s">
         <v>68</v>
@@ -10581,9 +11055,11 @@
         <v>400</v>
       </c>
       <c r="M186" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="N186" s="5"/>
+        <v>494</v>
+      </c>
+      <c r="N186" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O186" s="5"/>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
@@ -10594,7 +11070,7 @@
         <v>90</v>
       </c>
       <c r="C187" s="5">
-        <v>14210827</v>
+        <v>14210832</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>65</v>
@@ -10609,10 +11085,10 @@
         <v>1</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I187" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J187" s="5" t="s">
         <v>68</v>
@@ -10621,12 +11097,14 @@
         <v>69</v>
       </c>
       <c r="L187" s="5">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M187" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="N187" s="5"/>
+      <c r="N187" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O187" s="5"/>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
@@ -10634,16 +11112,16 @@
         <v>51</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="C188" s="5">
-        <v>14210832</v>
+        <v>14210851</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E188" s="5">
-        <v>685431</v>
+        <v>685434</v>
       </c>
       <c r="F188" s="5">
         <v>4</v>
@@ -10655,7 +11133,7 @@
         <v>497</v>
       </c>
       <c r="I188" s="5" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J188" s="5" t="s">
         <v>68</v>
@@ -10664,12 +11142,14 @@
         <v>69</v>
       </c>
       <c r="L188" s="5">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="M188" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="N188" s="5"/>
+        <v>499</v>
+      </c>
+      <c r="N188" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O188" s="5"/>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
@@ -10677,10 +11157,10 @@
         <v>51</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="C189" s="5">
-        <v>14210851</v>
+        <v>14210853</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>65</v>
@@ -10695,10 +11175,10 @@
         <v>1</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I189" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J189" s="5" t="s">
         <v>68</v>
@@ -10712,7 +11192,9 @@
       <c r="M189" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="N189" s="5"/>
+      <c r="N189" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O189" s="5"/>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
@@ -10720,10 +11202,10 @@
         <v>51</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="C190" s="5">
-        <v>14210853</v>
+        <v>14210868</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>65</v>
@@ -10741,7 +11223,7 @@
         <v>502</v>
       </c>
       <c r="I190" s="5" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="J190" s="5" t="s">
         <v>68</v>
@@ -10753,26 +11235,28 @@
         <v>400</v>
       </c>
       <c r="M190" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="N190" s="5"/>
+        <v>504</v>
+      </c>
+      <c r="N190" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O190" s="5"/>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>321</v>
       </c>
       <c r="C191" s="5">
-        <v>14210868</v>
+        <v>14211233</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E191" s="5">
-        <v>685434</v>
+        <v>685433</v>
       </c>
       <c r="F191" s="5">
         <v>4</v>
@@ -10781,10 +11265,10 @@
         <v>1</v>
       </c>
       <c r="H191" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I191" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J191" s="5" t="s">
         <v>68</v>
@@ -10792,13 +11276,15 @@
       <c r="K191" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L191" s="5">
-        <v>400</v>
+      <c r="L191" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="M191" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="N191" s="5"/>
+        <v>507</v>
+      </c>
+      <c r="N191" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O191" s="5"/>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
@@ -10809,7 +11295,7 @@
         <v>321</v>
       </c>
       <c r="C192" s="5">
-        <v>14211233</v>
+        <v>14211240</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>65</v>
@@ -10824,10 +11310,10 @@
         <v>1</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I192" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J192" s="5" t="s">
         <v>68</v>
@@ -10841,7 +11327,9 @@
       <c r="M192" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="N192" s="5"/>
+      <c r="N192" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O192" s="5"/>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.25">
@@ -10852,7 +11340,7 @@
         <v>321</v>
       </c>
       <c r="C193" s="5">
-        <v>14211240</v>
+        <v>14211245</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>65</v>
@@ -10870,7 +11358,7 @@
         <v>510</v>
       </c>
       <c r="I193" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J193" s="5" t="s">
         <v>68</v>
@@ -10884,7 +11372,9 @@
       <c r="M193" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="N193" s="5"/>
+      <c r="N193" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O193" s="5"/>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.25">
@@ -10895,7 +11385,7 @@
         <v>321</v>
       </c>
       <c r="C194" s="5">
-        <v>14211245</v>
+        <v>14211249</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>65</v>
@@ -10913,7 +11403,7 @@
         <v>512</v>
       </c>
       <c r="I194" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J194" s="5" t="s">
         <v>68</v>
@@ -10927,7 +11417,9 @@
       <c r="M194" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="N194" s="5"/>
+      <c r="N194" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O194" s="5"/>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.25">
@@ -10938,7 +11430,7 @@
         <v>321</v>
       </c>
       <c r="C195" s="5">
-        <v>14211249</v>
+        <v>14211261</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>65</v>
@@ -10956,7 +11448,7 @@
         <v>514</v>
       </c>
       <c r="I195" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>68</v>
@@ -10970,7 +11462,9 @@
       <c r="M195" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="N195" s="5"/>
+      <c r="N195" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O195" s="5"/>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.25">
@@ -10981,7 +11475,7 @@
         <v>321</v>
       </c>
       <c r="C196" s="5">
-        <v>14211261</v>
+        <v>14211265</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>65</v>
@@ -10999,7 +11493,7 @@
         <v>516</v>
       </c>
       <c r="I196" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J196" s="5" t="s">
         <v>68</v>
@@ -11013,7 +11507,9 @@
       <c r="M196" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="N196" s="5"/>
+      <c r="N196" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O196" s="5"/>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.25">
@@ -11024,13 +11520,13 @@
         <v>321</v>
       </c>
       <c r="C197" s="5">
-        <v>14211265</v>
+        <v>14211276</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E197" s="5">
-        <v>685433</v>
+        <v>685701</v>
       </c>
       <c r="F197" s="5">
         <v>4</v>
@@ -11042,7 +11538,7 @@
         <v>518</v>
       </c>
       <c r="I197" s="5" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="J197" s="5" t="s">
         <v>68</v>
@@ -11050,13 +11546,15 @@
       <c r="K197" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L197" s="5" t="s">
-        <v>13</v>
+      <c r="L197" s="5">
+        <v>600</v>
       </c>
       <c r="M197" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="N197" s="5"/>
+        <v>520</v>
+      </c>
+      <c r="N197" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O197" s="5"/>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.25">
@@ -11067,13 +11565,13 @@
         <v>321</v>
       </c>
       <c r="C198" s="5">
-        <v>14211276</v>
+        <v>14211338</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E198" s="5">
-        <v>685701</v>
+        <v>685541</v>
       </c>
       <c r="F198" s="5">
         <v>4</v>
@@ -11082,10 +11580,10 @@
         <v>1</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I198" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="J198" s="5" t="s">
         <v>68</v>
@@ -11094,12 +11592,14 @@
         <v>69</v>
       </c>
       <c r="L198" s="5">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="M198" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="N198" s="5"/>
+      <c r="N198" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O198" s="5"/>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.25">
@@ -11110,13 +11610,13 @@
         <v>321</v>
       </c>
       <c r="C199" s="5">
-        <v>14211338</v>
+        <v>14211342</v>
       </c>
       <c r="D199" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E199" s="5">
-        <v>685541</v>
+        <v>685700</v>
       </c>
       <c r="F199" s="5">
         <v>4</v>
@@ -11128,7 +11628,7 @@
         <v>523</v>
       </c>
       <c r="I199" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="J199" s="5" t="s">
         <v>68</v>
@@ -11137,12 +11637,14 @@
         <v>69</v>
       </c>
       <c r="L199" s="5">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="M199" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="N199" s="5"/>
+      <c r="N199" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O199" s="5"/>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.25">
@@ -11153,7 +11655,7 @@
         <v>321</v>
       </c>
       <c r="C200" s="5">
-        <v>14211342</v>
+        <v>14211367</v>
       </c>
       <c r="D200" s="5" t="s">
         <v>65</v>
@@ -11171,7 +11673,7 @@
         <v>525</v>
       </c>
       <c r="I200" s="5" t="s">
-        <v>521</v>
+        <v>67</v>
       </c>
       <c r="J200" s="5" t="s">
         <v>68</v>
@@ -11185,24 +11687,26 @@
       <c r="M200" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="N200" s="5"/>
+      <c r="N200" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O200" s="5"/>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>321</v>
       </c>
       <c r="C201" s="5">
-        <v>14211367</v>
+        <v>14211925</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E201" s="5">
-        <v>685700</v>
+        <v>685551</v>
       </c>
       <c r="F201" s="5">
         <v>4</v>
@@ -11214,7 +11718,7 @@
         <v>527</v>
       </c>
       <c r="I201" s="5" t="s">
-        <v>67</v>
+        <v>493</v>
       </c>
       <c r="J201" s="5" t="s">
         <v>68</v>
@@ -11222,13 +11726,15 @@
       <c r="K201" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L201" s="5">
-        <v>500</v>
+      <c r="L201" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="M201" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="N201" s="5"/>
+      <c r="N201" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O201" s="5"/>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.25">
@@ -11239,13 +11745,13 @@
         <v>321</v>
       </c>
       <c r="C202" s="5">
-        <v>14211925</v>
+        <v>14211935</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E202" s="5">
-        <v>685551</v>
+        <v>685485</v>
       </c>
       <c r="F202" s="5">
         <v>4</v>
@@ -11257,7 +11763,7 @@
         <v>529</v>
       </c>
       <c r="I202" s="5" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="J202" s="5" t="s">
         <v>68</v>
@@ -11265,13 +11771,15 @@
       <c r="K202" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L202" s="5" t="s">
-        <v>34</v>
+      <c r="L202" s="5">
+        <v>500</v>
       </c>
       <c r="M202" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="N202" s="5"/>
+      <c r="N202" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O202" s="5"/>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.25">
@@ -11282,13 +11790,13 @@
         <v>321</v>
       </c>
       <c r="C203" s="5">
-        <v>14211935</v>
+        <v>14211941</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E203" s="5">
-        <v>685485</v>
+        <v>685484</v>
       </c>
       <c r="F203" s="5">
         <v>4</v>
@@ -11300,7 +11808,7 @@
         <v>531</v>
       </c>
       <c r="I203" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J203" s="5" t="s">
         <v>68</v>
@@ -11314,7 +11822,9 @@
       <c r="M203" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="N203" s="5"/>
+      <c r="N203" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O203" s="5"/>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.25">
@@ -11325,13 +11835,13 @@
         <v>321</v>
       </c>
       <c r="C204" s="5">
-        <v>14211941</v>
+        <v>14211945</v>
       </c>
       <c r="D204" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E204" s="5">
-        <v>685484</v>
+        <v>685552</v>
       </c>
       <c r="F204" s="5">
         <v>4</v>
@@ -11343,7 +11853,7 @@
         <v>533</v>
       </c>
       <c r="I204" s="5" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="J204" s="5" t="s">
         <v>68</v>
@@ -11352,12 +11862,14 @@
         <v>69</v>
       </c>
       <c r="L204" s="5">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="M204" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="N204" s="5"/>
+      <c r="N204" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O204" s="5"/>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.25">
@@ -11368,13 +11880,13 @@
         <v>321</v>
       </c>
       <c r="C205" s="5">
-        <v>14211945</v>
+        <v>14211947</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E205" s="5">
-        <v>685552</v>
+        <v>685401</v>
       </c>
       <c r="F205" s="5">
         <v>4</v>
@@ -11386,7 +11898,7 @@
         <v>535</v>
       </c>
       <c r="I205" s="5" t="s">
-        <v>521</v>
+        <v>493</v>
       </c>
       <c r="J205" s="5" t="s">
         <v>68</v>
@@ -11395,12 +11907,14 @@
         <v>69</v>
       </c>
       <c r="L205" s="5">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="M205" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="N205" s="5"/>
+      <c r="N205" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O205" s="5"/>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.25">
@@ -11411,13 +11925,13 @@
         <v>321</v>
       </c>
       <c r="C206" s="5">
-        <v>14211947</v>
+        <v>14211950</v>
       </c>
       <c r="D206" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E206" s="5">
-        <v>685401</v>
+        <v>685703</v>
       </c>
       <c r="F206" s="5">
         <v>4</v>
@@ -11429,7 +11943,7 @@
         <v>537</v>
       </c>
       <c r="I206" s="5" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="J206" s="5" t="s">
         <v>68</v>
@@ -11438,12 +11952,14 @@
         <v>69</v>
       </c>
       <c r="L206" s="5">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="M206" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="N206" s="5"/>
+      <c r="N206" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O206" s="5"/>
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.25">
@@ -11454,7 +11970,7 @@
         <v>321</v>
       </c>
       <c r="C207" s="5">
-        <v>14211950</v>
+        <v>14211952</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>65</v>
@@ -11472,7 +11988,7 @@
         <v>539</v>
       </c>
       <c r="I207" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="J207" s="5" t="s">
         <v>68</v>
@@ -11486,7 +12002,9 @@
       <c r="M207" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="N207" s="5"/>
+      <c r="N207" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O207" s="5"/>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.25">
@@ -11497,13 +12015,13 @@
         <v>321</v>
       </c>
       <c r="C208" s="5">
-        <v>14211952</v>
+        <v>14211955</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E208" s="5">
-        <v>685703</v>
+        <v>685482</v>
       </c>
       <c r="F208" s="5">
         <v>4</v>
@@ -11515,7 +12033,7 @@
         <v>541</v>
       </c>
       <c r="I208" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="J208" s="5" t="s">
         <v>68</v>
@@ -11524,12 +12042,14 @@
         <v>69</v>
       </c>
       <c r="L208" s="5">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="M208" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="N208" s="5"/>
+      <c r="N208" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O208" s="5"/>
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.25">
@@ -11537,16 +12057,16 @@
         <v>53</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="C209" s="5">
-        <v>14211955</v>
+        <v>14212241</v>
       </c>
       <c r="D209" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E209" s="5">
-        <v>685482</v>
+        <v>685411</v>
       </c>
       <c r="F209" s="5">
         <v>4</v>
@@ -11558,7 +12078,7 @@
         <v>543</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>521</v>
+        <v>67</v>
       </c>
       <c r="J209" s="5" t="s">
         <v>68</v>
@@ -11567,29 +12087,31 @@
         <v>69</v>
       </c>
       <c r="L209" s="5">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="M209" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="N209" s="5"/>
+      <c r="N209" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O209" s="5"/>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="C210" s="5">
-        <v>14212241</v>
+        <v>14214064</v>
       </c>
       <c r="D210" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E210" s="5">
-        <v>685411</v>
+        <v>685434</v>
       </c>
       <c r="F210" s="5">
         <v>4</v>
@@ -11601,7 +12123,7 @@
         <v>545</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>67</v>
+        <v>546</v>
       </c>
       <c r="J210" s="5" t="s">
         <v>68</v>
@@ -11613,9 +12135,11 @@
         <v>400</v>
       </c>
       <c r="M210" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="N210" s="5"/>
+        <v>547</v>
+      </c>
+      <c r="N210" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O210" s="5"/>
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.25">
@@ -11626,7 +12150,7 @@
         <v>321</v>
       </c>
       <c r="C211" s="5">
-        <v>14214064</v>
+        <v>14214072</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>65</v>
@@ -11641,10 +12165,10 @@
         <v>1</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I211" s="5" t="s">
-        <v>548</v>
+        <v>383</v>
       </c>
       <c r="J211" s="5" t="s">
         <v>68</v>
@@ -11658,7 +12182,9 @@
       <c r="M211" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="N211" s="5"/>
+      <c r="N211" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O211" s="5"/>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.25">
@@ -11669,13 +12195,13 @@
         <v>321</v>
       </c>
       <c r="C212" s="5">
-        <v>14214072</v>
+        <v>14214092</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E212" s="5">
-        <v>685434</v>
+        <v>685705</v>
       </c>
       <c r="F212" s="5">
         <v>4</v>
@@ -11687,7 +12213,7 @@
         <v>550</v>
       </c>
       <c r="I212" s="5" t="s">
-        <v>383</v>
+        <v>112</v>
       </c>
       <c r="J212" s="5" t="s">
         <v>68</v>
@@ -11696,12 +12222,14 @@
         <v>69</v>
       </c>
       <c r="L212" s="5">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M212" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="N212" s="5"/>
+      <c r="N212" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O212" s="5"/>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.25">
@@ -11712,7 +12240,7 @@
         <v>321</v>
       </c>
       <c r="C213" s="5">
-        <v>14214092</v>
+        <v>14214097</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>65</v>
@@ -11730,7 +12258,7 @@
         <v>552</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>112</v>
+        <v>553</v>
       </c>
       <c r="J213" s="5" t="s">
         <v>68</v>
@@ -11739,12 +12267,14 @@
         <v>69</v>
       </c>
       <c r="L213" s="5">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M213" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="N213" s="5"/>
+        <v>554</v>
+      </c>
+      <c r="N213" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O213" s="5"/>
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.25">
@@ -11755,13 +12285,13 @@
         <v>321</v>
       </c>
       <c r="C214" s="5">
-        <v>14214097</v>
+        <v>14214101</v>
       </c>
       <c r="D214" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E214" s="5">
-        <v>685705</v>
+        <v>685421</v>
       </c>
       <c r="F214" s="5">
         <v>4</v>
@@ -11770,10 +12300,10 @@
         <v>1</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I214" s="5" t="s">
-        <v>555</v>
+        <v>67</v>
       </c>
       <c r="J214" s="5" t="s">
         <v>68</v>
@@ -11782,12 +12312,14 @@
         <v>69</v>
       </c>
       <c r="L214" s="5">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="M214" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="N214" s="5"/>
+      <c r="N214" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O214" s="5"/>
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.25">
@@ -11798,13 +12330,13 @@
         <v>321</v>
       </c>
       <c r="C215" s="5">
-        <v>14214101</v>
+        <v>14214108</v>
       </c>
       <c r="D215" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E215" s="5">
-        <v>685421</v>
+        <v>685554</v>
       </c>
       <c r="F215" s="5">
         <v>4</v>
@@ -11816,7 +12348,7 @@
         <v>557</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>67</v>
+        <v>558</v>
       </c>
       <c r="J215" s="5" t="s">
         <v>68</v>
@@ -11825,29 +12357,31 @@
         <v>69</v>
       </c>
       <c r="L215" s="5">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="M215" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="N215" s="5"/>
+        <v>559</v>
+      </c>
+      <c r="N215" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O215" s="5"/>
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B216" s="4" t="s">
         <v>321</v>
       </c>
       <c r="C216" s="5">
-        <v>14214108</v>
+        <v>14214855</v>
       </c>
       <c r="D216" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E216" s="5">
-        <v>685554</v>
+        <v>685553</v>
       </c>
       <c r="F216" s="5">
         <v>4</v>
@@ -11855,8 +12389,8 @@
       <c r="G216" s="5">
         <v>1</v>
       </c>
-      <c r="H216" s="5" t="s">
-        <v>559</v>
+      <c r="H216" s="5">
+        <v>4716506269</v>
       </c>
       <c r="I216" s="5" t="s">
         <v>560</v>
@@ -11867,13 +12401,15 @@
       <c r="K216" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L216" s="5">
-        <v>400</v>
+      <c r="L216" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="M216" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="N216" s="5"/>
+      <c r="N216" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O216" s="5"/>
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.25">
@@ -11884,22 +12420,22 @@
         <v>321</v>
       </c>
       <c r="C217" s="5">
-        <v>14214855</v>
+        <v>14214897</v>
       </c>
       <c r="D217" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E217" s="5">
-        <v>685553</v>
+        <v>685703</v>
       </c>
       <c r="F217" s="5">
         <v>4</v>
       </c>
       <c r="G217" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H217" s="5">
-        <v>4716506269</v>
+        <v>4716511526</v>
       </c>
       <c r="I217" s="5" t="s">
         <v>562</v>
@@ -11910,13 +12446,15 @@
       <c r="K217" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L217" s="5" t="s">
-        <v>193</v>
+      <c r="L217" s="5">
+        <v>400</v>
       </c>
       <c r="M217" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="N217" s="5"/>
+      <c r="N217" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O217" s="5"/>
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.25">
@@ -11927,7 +12465,7 @@
         <v>321</v>
       </c>
       <c r="C218" s="5">
-        <v>14214897</v>
+        <v>14214907</v>
       </c>
       <c r="D218" s="5" t="s">
         <v>65</v>
@@ -11942,7 +12480,7 @@
         <v>4</v>
       </c>
       <c r="H218" s="5">
-        <v>4716511526</v>
+        <v>4716511525</v>
       </c>
       <c r="I218" s="5" t="s">
         <v>564</v>
@@ -11953,13 +12491,15 @@
       <c r="K218" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L218" s="5">
-        <v>400</v>
+      <c r="L218" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="M218" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="N218" s="5"/>
+      <c r="N218" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O218" s="5"/>
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.25">
@@ -11970,22 +12510,22 @@
         <v>321</v>
       </c>
       <c r="C219" s="5">
-        <v>14214907</v>
+        <v>14214919</v>
       </c>
       <c r="D219" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E219" s="5">
-        <v>685703</v>
+        <v>685541</v>
       </c>
       <c r="F219" s="5">
         <v>4</v>
       </c>
       <c r="G219" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H219" s="5">
-        <v>4716511525</v>
+        <v>4513411086</v>
       </c>
       <c r="I219" s="5" t="s">
         <v>566</v>
@@ -11997,12 +12537,14 @@
         <v>69</v>
       </c>
       <c r="L219" s="5" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M219" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="N219" s="5"/>
+      <c r="N219" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O219" s="5"/>
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.25">
@@ -12013,13 +12555,13 @@
         <v>321</v>
       </c>
       <c r="C220" s="5">
-        <v>14214919</v>
+        <v>14214924</v>
       </c>
       <c r="D220" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E220" s="5">
-        <v>685541</v>
+        <v>685554</v>
       </c>
       <c r="F220" s="5">
         <v>4</v>
@@ -12028,7 +12570,7 @@
         <v>2</v>
       </c>
       <c r="H220" s="5">
-        <v>4513411086</v>
+        <v>4713400047</v>
       </c>
       <c r="I220" s="5" t="s">
         <v>568</v>
@@ -12040,41 +12582,43 @@
         <v>69</v>
       </c>
       <c r="L220" s="5" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="M220" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="N220" s="5"/>
+      <c r="N220" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O220" s="5"/>
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>321</v>
       </c>
       <c r="C221" s="5">
-        <v>14214924</v>
+        <v>14215649</v>
       </c>
       <c r="D221" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E221" s="5">
-        <v>685554</v>
+        <v>685433</v>
       </c>
       <c r="F221" s="5">
         <v>4</v>
       </c>
       <c r="G221" s="5">
-        <v>2</v>
-      </c>
-      <c r="H221" s="5">
-        <v>4713400047</v>
+        <v>1</v>
+      </c>
+      <c r="H221" s="5" t="s">
+        <v>570</v>
       </c>
       <c r="I221" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J221" s="5" t="s">
         <v>68</v>
@@ -12083,12 +12627,14 @@
         <v>69</v>
       </c>
       <c r="L221" s="5" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="M221" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="N221" s="5"/>
+        <v>572</v>
+      </c>
+      <c r="N221" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O221" s="5"/>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.25">
@@ -12099,13 +12645,13 @@
         <v>321</v>
       </c>
       <c r="C222" s="5">
-        <v>14215649</v>
+        <v>14215657</v>
       </c>
       <c r="D222" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E222" s="5">
-        <v>685433</v>
+        <v>685554</v>
       </c>
       <c r="F222" s="5">
         <v>4</v>
@@ -12114,10 +12660,10 @@
         <v>1</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I222" s="5" t="s">
-        <v>573</v>
+        <v>112</v>
       </c>
       <c r="J222" s="5" t="s">
         <v>68</v>
@@ -12125,13 +12671,15 @@
       <c r="K222" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L222" s="5" t="s">
-        <v>13</v>
+      <c r="L222" s="5">
+        <v>800</v>
       </c>
       <c r="M222" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="N222" s="5"/>
+      <c r="N222" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O222" s="5"/>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.25">
@@ -12142,13 +12690,13 @@
         <v>321</v>
       </c>
       <c r="C223" s="5">
-        <v>14215657</v>
+        <v>14215715</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E223" s="5">
-        <v>685554</v>
+        <v>685484</v>
       </c>
       <c r="F223" s="5">
         <v>4</v>
@@ -12157,7 +12705,7 @@
         <v>1</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>575</v>
+        <v>268</v>
       </c>
       <c r="I223" s="5" t="s">
         <v>112</v>
@@ -12169,12 +12717,14 @@
         <v>69</v>
       </c>
       <c r="L223" s="5">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="M223" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="N223" s="5"/>
+        <v>575</v>
+      </c>
+      <c r="N223" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O223" s="5"/>
     </row>
     <row r="224" spans="1:15" x14ac:dyDescent="0.25">
@@ -12185,7 +12735,7 @@
         <v>321</v>
       </c>
       <c r="C224" s="5">
-        <v>14215715</v>
+        <v>14215721</v>
       </c>
       <c r="D224" s="5" t="s">
         <v>65</v>
@@ -12200,7 +12750,7 @@
         <v>1</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>268</v>
+        <v>576</v>
       </c>
       <c r="I224" s="5" t="s">
         <v>112</v>
@@ -12212,12 +12762,14 @@
         <v>69</v>
       </c>
       <c r="L224" s="5">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M224" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="N224" s="5"/>
+      <c r="N224" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O224" s="5"/>
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.25">
@@ -12228,13 +12780,13 @@
         <v>321</v>
       </c>
       <c r="C225" s="5">
-        <v>14215721</v>
+        <v>14215726</v>
       </c>
       <c r="D225" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E225" s="5">
-        <v>685484</v>
+        <v>685485</v>
       </c>
       <c r="F225" s="5">
         <v>4</v>
@@ -12255,12 +12807,14 @@
         <v>69</v>
       </c>
       <c r="L225" s="5">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="M225" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="N225" s="5"/>
+      <c r="N225" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O225" s="5"/>
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.25">
@@ -12271,13 +12825,13 @@
         <v>321</v>
       </c>
       <c r="C226" s="5">
-        <v>14215726</v>
+        <v>14215732</v>
       </c>
       <c r="D226" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E226" s="5">
-        <v>685485</v>
+        <v>685484</v>
       </c>
       <c r="F226" s="5">
         <v>4</v>
@@ -12289,7 +12843,7 @@
         <v>580</v>
       </c>
       <c r="I226" s="5" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="J226" s="5" t="s">
         <v>68</v>
@@ -12298,12 +12852,14 @@
         <v>69</v>
       </c>
       <c r="L226" s="5">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="M226" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="N226" s="5"/>
+      <c r="N226" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O226" s="5"/>
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.25">
@@ -12314,13 +12870,13 @@
         <v>321</v>
       </c>
       <c r="C227" s="5">
-        <v>14215732</v>
+        <v>14215735</v>
       </c>
       <c r="D227" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E227" s="5">
-        <v>685484</v>
+        <v>685700</v>
       </c>
       <c r="F227" s="5">
         <v>4</v>
@@ -12341,29 +12897,31 @@
         <v>69</v>
       </c>
       <c r="L227" s="5">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="M227" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="N227" s="5"/>
+      <c r="N227" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O227" s="5"/>
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>321</v>
+        <v>214</v>
       </c>
       <c r="C228" s="5">
-        <v>14215735</v>
+        <v>14216257</v>
       </c>
       <c r="D228" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E228" s="5">
-        <v>685700</v>
+        <v>685864</v>
       </c>
       <c r="F228" s="5">
         <v>4</v>
@@ -12375,7 +12933,7 @@
         <v>584</v>
       </c>
       <c r="I228" s="5" t="s">
-        <v>67</v>
+        <v>585</v>
       </c>
       <c r="J228" s="5" t="s">
         <v>68</v>
@@ -12383,13 +12941,15 @@
       <c r="K228" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L228" s="5">
-        <v>600</v>
+      <c r="L228" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="M228" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="N228" s="5"/>
+        <v>586</v>
+      </c>
+      <c r="N228" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O228" s="5"/>
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.25">
@@ -12397,16 +12957,16 @@
         <v>59</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>214</v>
+        <v>477</v>
       </c>
       <c r="C229" s="5">
-        <v>14216257</v>
+        <v>14216291</v>
       </c>
       <c r="D229" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E229" s="5">
-        <v>685864</v>
+        <v>685545</v>
       </c>
       <c r="F229" s="5">
         <v>4</v>
@@ -12415,10 +12975,10 @@
         <v>1</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I229" s="5" t="s">
-        <v>587</v>
+        <v>67</v>
       </c>
       <c r="J229" s="5" t="s">
         <v>68</v>
@@ -12426,13 +12986,15 @@
       <c r="K229" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L229" s="5" t="s">
-        <v>32</v>
+      <c r="L229" s="5">
+        <v>600</v>
       </c>
       <c r="M229" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="N229" s="5"/>
+      <c r="N229" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O229" s="5"/>
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.25">
@@ -12440,16 +13002,16 @@
         <v>59</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C230" s="5">
-        <v>14216291</v>
+        <v>14216297</v>
       </c>
       <c r="D230" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E230" s="5">
-        <v>685545</v>
+        <v>685485</v>
       </c>
       <c r="F230" s="5">
         <v>4</v>
@@ -12461,7 +13023,7 @@
         <v>589</v>
       </c>
       <c r="I230" s="5" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="J230" s="5" t="s">
         <v>68</v>
@@ -12469,13 +13031,15 @@
       <c r="K230" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L230" s="5">
-        <v>600</v>
+      <c r="L230" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="M230" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="N230" s="5"/>
+      <c r="N230" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O230" s="5"/>
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.25">
@@ -12483,16 +13047,16 @@
         <v>59</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C231" s="5">
-        <v>14216297</v>
+        <v>14216305</v>
       </c>
       <c r="D231" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E231" s="5">
-        <v>685485</v>
+        <v>685554</v>
       </c>
       <c r="F231" s="5">
         <v>4</v>
@@ -12504,7 +13068,7 @@
         <v>591</v>
       </c>
       <c r="I231" s="5" t="s">
-        <v>112</v>
+        <v>592</v>
       </c>
       <c r="J231" s="5" t="s">
         <v>68</v>
@@ -12512,30 +13076,32 @@
       <c r="K231" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L231" s="5" t="s">
-        <v>34</v>
+      <c r="L231" s="5">
+        <v>400</v>
       </c>
       <c r="M231" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="N231" s="5"/>
+        <v>593</v>
+      </c>
+      <c r="N231" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O231" s="5"/>
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>479</v>
+        <v>214</v>
       </c>
       <c r="C232" s="5">
-        <v>14216305</v>
+        <v>14216838</v>
       </c>
       <c r="D232" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E232" s="5">
-        <v>685554</v>
+        <v>685700</v>
       </c>
       <c r="F232" s="5">
         <v>4</v>
@@ -12543,8 +13109,8 @@
       <c r="G232" s="5">
         <v>1</v>
       </c>
-      <c r="H232" s="5" t="s">
-        <v>593</v>
+      <c r="H232" s="5">
+        <v>4716509719</v>
       </c>
       <c r="I232" s="5" t="s">
         <v>594</v>
@@ -12556,12 +13122,14 @@
         <v>69</v>
       </c>
       <c r="L232" s="5">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M232" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="N232" s="5"/>
+      <c r="N232" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O232" s="5"/>
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.25">
@@ -12572,13 +13140,13 @@
         <v>214</v>
       </c>
       <c r="C233" s="5">
-        <v>14216838</v>
+        <v>14216860</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E233" s="5">
-        <v>685700</v>
+        <v>685606</v>
       </c>
       <c r="F233" s="5">
         <v>4</v>
@@ -12586,11 +13154,11 @@
       <c r="G233" s="5">
         <v>1</v>
       </c>
-      <c r="H233" s="5">
-        <v>4716509719</v>
+      <c r="H233" s="5" t="s">
+        <v>596</v>
       </c>
       <c r="I233" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J233" s="5" t="s">
         <v>68</v>
@@ -12599,12 +13167,14 @@
         <v>69</v>
       </c>
       <c r="L233" s="5">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M233" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="N233" s="5"/>
+        <v>598</v>
+      </c>
+      <c r="N233" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O233" s="5"/>
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.25">
@@ -12615,13 +13185,13 @@
         <v>214</v>
       </c>
       <c r="C234" s="5">
-        <v>14216860</v>
+        <v>14216957</v>
       </c>
       <c r="D234" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E234" s="5">
-        <v>685606</v>
+        <v>685705</v>
       </c>
       <c r="F234" s="5">
         <v>4</v>
@@ -12629,8 +13199,8 @@
       <c r="G234" s="5">
         <v>1</v>
       </c>
-      <c r="H234" s="5" t="s">
-        <v>598</v>
+      <c r="H234" s="5">
+        <v>4716405375</v>
       </c>
       <c r="I234" s="5" t="s">
         <v>599</v>
@@ -12642,12 +13212,14 @@
         <v>69</v>
       </c>
       <c r="L234" s="5">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M234" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="N234" s="5"/>
+      <c r="N234" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O234" s="5"/>
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
@@ -12658,13 +13230,13 @@
         <v>214</v>
       </c>
       <c r="C235" s="5">
-        <v>14216957</v>
+        <v>14216980</v>
       </c>
       <c r="D235" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E235" s="5">
-        <v>685705</v>
+        <v>685546</v>
       </c>
       <c r="F235" s="5">
         <v>4</v>
@@ -12672,11 +13244,11 @@
       <c r="G235" s="5">
         <v>1</v>
       </c>
-      <c r="H235" s="5">
-        <v>4716405375</v>
+      <c r="H235" s="5" t="s">
+        <v>601</v>
       </c>
       <c r="I235" s="5" t="s">
-        <v>601</v>
+        <v>67</v>
       </c>
       <c r="J235" s="5" t="s">
         <v>68</v>
@@ -12690,7 +13262,9 @@
       <c r="M235" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="N235" s="5"/>
+      <c r="N235" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O235" s="5"/>
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
@@ -12701,7 +13275,7 @@
         <v>214</v>
       </c>
       <c r="C236" s="5">
-        <v>14216980</v>
+        <v>14216983</v>
       </c>
       <c r="D236" s="5" t="s">
         <v>65</v>
@@ -12733,7 +13307,9 @@
       <c r="M236" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="N236" s="5"/>
+      <c r="N236" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O236" s="5"/>
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
@@ -12744,13 +13320,13 @@
         <v>214</v>
       </c>
       <c r="C237" s="5">
-        <v>14216983</v>
+        <v>14216987</v>
       </c>
       <c r="D237" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E237" s="5">
-        <v>685546</v>
+        <v>685487</v>
       </c>
       <c r="F237" s="5">
         <v>4</v>
@@ -12758,25 +13334,27 @@
       <c r="G237" s="5">
         <v>1</v>
       </c>
-      <c r="H237" s="5" t="s">
+      <c r="H237" s="5">
+        <v>4715400083</v>
+      </c>
+      <c r="I237" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="I237" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="J237" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K237" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L237" s="5">
-        <v>600</v>
+      <c r="L237" s="5" t="s">
+        <v>606</v>
       </c>
       <c r="M237" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="N237" s="5"/>
+        <v>607</v>
+      </c>
+      <c r="N237" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O237" s="5"/>
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
@@ -12787,13 +13365,13 @@
         <v>214</v>
       </c>
       <c r="C238" s="5">
-        <v>14216987</v>
+        <v>14216993</v>
       </c>
       <c r="D238" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E238" s="5">
-        <v>685487</v>
+        <v>685546</v>
       </c>
       <c r="F238" s="5">
         <v>4</v>
@@ -12802,10 +13380,10 @@
         <v>1</v>
       </c>
       <c r="H238" s="5">
-        <v>4715400083</v>
+        <v>4313400049</v>
       </c>
       <c r="I238" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J238" s="5" t="s">
         <v>68</v>
@@ -12814,12 +13392,14 @@
         <v>69</v>
       </c>
       <c r="L238" s="5" t="s">
-        <v>608</v>
+        <v>163</v>
       </c>
       <c r="M238" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="N238" s="5"/>
+      <c r="N238" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O238" s="5"/>
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
@@ -12830,13 +13410,13 @@
         <v>214</v>
       </c>
       <c r="C239" s="5">
-        <v>14216993</v>
+        <v>14217018</v>
       </c>
       <c r="D239" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E239" s="5">
-        <v>685546</v>
+        <v>685491</v>
       </c>
       <c r="F239" s="5">
         <v>4</v>
@@ -12845,7 +13425,7 @@
         <v>1</v>
       </c>
       <c r="H239" s="5">
-        <v>4313400049</v>
+        <v>4716511227</v>
       </c>
       <c r="I239" s="5" t="s">
         <v>610</v>
@@ -12857,12 +13437,14 @@
         <v>69</v>
       </c>
       <c r="L239" s="5" t="s">
-        <v>163</v>
+        <v>32</v>
       </c>
       <c r="M239" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="N239" s="5"/>
+      <c r="N239" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O239" s="5"/>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
@@ -12873,7 +13455,7 @@
         <v>214</v>
       </c>
       <c r="C240" s="5">
-        <v>14217018</v>
+        <v>14217049</v>
       </c>
       <c r="D240" s="5" t="s">
         <v>65</v>
@@ -12888,7 +13470,7 @@
         <v>1</v>
       </c>
       <c r="H240" s="5">
-        <v>4716511227</v>
+        <v>4716512216</v>
       </c>
       <c r="I240" s="5" t="s">
         <v>612</v>
@@ -12900,12 +13482,14 @@
         <v>69</v>
       </c>
       <c r="L240" s="5" t="s">
-        <v>32</v>
+        <v>613</v>
       </c>
       <c r="M240" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="N240" s="5"/>
+        <v>614</v>
+      </c>
+      <c r="N240" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O240" s="5"/>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
@@ -12916,7 +13500,7 @@
         <v>214</v>
       </c>
       <c r="C241" s="5">
-        <v>14217049</v>
+        <v>14217059</v>
       </c>
       <c r="D241" s="5" t="s">
         <v>65</v>
@@ -12931,10 +13515,10 @@
         <v>1</v>
       </c>
       <c r="H241" s="5">
-        <v>4716512216</v>
+        <v>4716512217</v>
       </c>
       <c r="I241" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="J241" s="5" t="s">
         <v>68</v>
@@ -12943,12 +13527,14 @@
         <v>69</v>
       </c>
       <c r="L241" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="M241" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="M241" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="N241" s="5"/>
+      <c r="N241" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O241" s="5"/>
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
@@ -12959,7 +13545,7 @@
         <v>214</v>
       </c>
       <c r="C242" s="5">
-        <v>14217059</v>
+        <v>14217062</v>
       </c>
       <c r="D242" s="5" t="s">
         <v>65</v>
@@ -12974,10 +13560,10 @@
         <v>1</v>
       </c>
       <c r="H242" s="5">
-        <v>4716512217</v>
+        <v>4738361124</v>
       </c>
       <c r="I242" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="J242" s="5" t="s">
         <v>68</v>
@@ -12986,29 +13572,31 @@
         <v>69</v>
       </c>
       <c r="L242" s="5" t="s">
-        <v>615</v>
+        <v>18</v>
       </c>
       <c r="M242" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="N242" s="5"/>
+        <v>616</v>
+      </c>
+      <c r="N242" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O242" s="5"/>
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B243" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C243" s="5">
-        <v>14217062</v>
+        <v>14217681</v>
       </c>
       <c r="D243" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E243" s="5">
-        <v>685491</v>
+        <v>685541</v>
       </c>
       <c r="F243" s="5">
         <v>4</v>
@@ -13017,10 +13605,10 @@
         <v>1</v>
       </c>
       <c r="H243" s="5">
-        <v>4738361124</v>
+        <v>4714200425</v>
       </c>
       <c r="I243" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="J243" s="5" t="s">
         <v>68</v>
@@ -13034,7 +13622,9 @@
       <c r="M243" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="N243" s="5"/>
+      <c r="N243" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O243" s="5"/>
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
@@ -13045,13 +13635,13 @@
         <v>214</v>
       </c>
       <c r="C244" s="5">
-        <v>14217681</v>
+        <v>14218356</v>
       </c>
       <c r="D244" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E244" s="5">
-        <v>685541</v>
+        <v>685551</v>
       </c>
       <c r="F244" s="5">
         <v>4</v>
@@ -13060,7 +13650,7 @@
         <v>1</v>
       </c>
       <c r="H244" s="5">
-        <v>4714200425</v>
+        <v>4715900482</v>
       </c>
       <c r="I244" s="5" t="s">
         <v>619</v>
@@ -13072,72 +13662,76 @@
         <v>69</v>
       </c>
       <c r="L244" s="5" t="s">
-        <v>18</v>
+        <v>620</v>
       </c>
       <c r="M244" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="N244" s="5"/>
+        <v>621</v>
+      </c>
+      <c r="N244" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O244" s="5"/>
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>61</v>
+        <v>622</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C245" s="5">
-        <v>14218356</v>
+        <v>14218856</v>
       </c>
       <c r="D245" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E245" s="5">
-        <v>685551</v>
+        <v>685701</v>
       </c>
       <c r="F245" s="5">
         <v>4</v>
       </c>
       <c r="G245" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H245" s="5">
-        <v>4715900482</v>
+        <v>4716406123</v>
       </c>
       <c r="I245" s="5" t="s">
-        <v>621</v>
+        <v>317</v>
       </c>
       <c r="J245" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K245" s="5" t="s">
-        <v>69</v>
+        <v>623</v>
       </c>
       <c r="L245" s="5" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="M245" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="N245" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="N245" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O245" s="5"/>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C246" s="5">
-        <v>14218856</v>
+        <v>14218861</v>
       </c>
       <c r="D246" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E246" s="5">
-        <v>685701</v>
+        <v>685541</v>
       </c>
       <c r="F246" s="5">
         <v>4</v>
@@ -13146,35 +13740,37 @@
         <v>2</v>
       </c>
       <c r="H246" s="5">
-        <v>4716406123</v>
+        <v>4716403034</v>
       </c>
       <c r="I246" s="5" t="s">
-        <v>317</v>
+        <v>625</v>
       </c>
       <c r="J246" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K246" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="L246" s="5" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="M246" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="N246" s="5"/>
+        <v>627</v>
+      </c>
+      <c r="N246" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O246" s="5"/>
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C247" s="5">
-        <v>14218861</v>
+        <v>14218903</v>
       </c>
       <c r="D247" s="5" t="s">
         <v>65</v>
@@ -13186,44 +13782,46 @@
         <v>4</v>
       </c>
       <c r="G247" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H247" s="5">
-        <v>4716403034</v>
+        <v>4314010126</v>
       </c>
       <c r="I247" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J247" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K247" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="L247" s="5" t="s">
-        <v>628</v>
+        <v>15</v>
       </c>
       <c r="M247" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="N247" s="5"/>
+      <c r="N247" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O247" s="5"/>
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C248" s="5">
-        <v>14218903</v>
+        <v>14219019</v>
       </c>
       <c r="D248" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E248" s="5">
-        <v>685541</v>
+        <v>685433</v>
       </c>
       <c r="F248" s="5">
         <v>4</v>
@@ -13231,42 +13829,44 @@
       <c r="G248" s="5">
         <v>1</v>
       </c>
-      <c r="H248" s="5">
-        <v>4314010126</v>
+      <c r="H248" s="5" t="s">
+        <v>630</v>
       </c>
       <c r="I248" s="5" t="s">
-        <v>630</v>
+        <v>112</v>
       </c>
       <c r="J248" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K248" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="L248" s="5" t="s">
-        <v>15</v>
+        <v>623</v>
+      </c>
+      <c r="L248" s="5">
+        <v>400</v>
       </c>
       <c r="M248" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="N248" s="5"/>
+      <c r="N248" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O248" s="5"/>
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B249" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C249" s="5">
-        <v>14219019</v>
+        <v>14219028</v>
       </c>
       <c r="D249" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E249" s="5">
-        <v>685433</v>
+        <v>685703</v>
       </c>
       <c r="F249" s="5">
         <v>4</v>
@@ -13274,42 +13874,44 @@
       <c r="G249" s="5">
         <v>1</v>
       </c>
-      <c r="H249" s="5" t="s">
+      <c r="H249" s="5">
+        <v>4716406239</v>
+      </c>
+      <c r="I249" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="J249" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K249" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="L249" s="5" t="s">
         <v>632</v>
-      </c>
-      <c r="I249" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="J249" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="K249" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="L249" s="5">
-        <v>400</v>
       </c>
       <c r="M249" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="N249" s="5"/>
+      <c r="N249" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O249" s="5"/>
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C250" s="5">
-        <v>14219028</v>
+        <v>14219033</v>
       </c>
       <c r="D250" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E250" s="5">
-        <v>685703</v>
+        <v>685491</v>
       </c>
       <c r="F250" s="5">
         <v>4</v>
@@ -13317,155 +13919,118 @@
       <c r="G250" s="5">
         <v>1</v>
       </c>
-      <c r="H250" s="5">
-        <v>4716406239</v>
+      <c r="H250" s="5" t="s">
+        <v>634</v>
       </c>
       <c r="I250" s="5" t="s">
-        <v>612</v>
+        <v>72</v>
       </c>
       <c r="J250" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K250" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="L250" s="5" t="s">
-        <v>634</v>
+        <v>623</v>
+      </c>
+      <c r="L250" s="5">
+        <v>800</v>
       </c>
       <c r="M250" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="N250" s="5"/>
+      <c r="N250" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O250" s="5"/>
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B251" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C251" s="5">
-        <v>14219033</v>
+        <v>14219053</v>
       </c>
       <c r="D251" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E251" s="5">
-        <v>685491</v>
+        <v>685914</v>
       </c>
       <c r="F251" s="5">
         <v>4</v>
       </c>
       <c r="G251" s="5">
-        <v>1</v>
-      </c>
-      <c r="H251" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H251" s="5">
+        <v>4716511948</v>
+      </c>
+      <c r="I251" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="I251" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="J251" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K251" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="L251" s="5">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="M251" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="N251" s="5"/>
+      <c r="N251" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O251" s="5"/>
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>624</v>
+        <v>638</v>
       </c>
       <c r="B252" s="4" t="s">
         <v>214</v>
       </c>
       <c r="C252" s="5">
-        <v>14219053</v>
+        <v>14219835</v>
       </c>
       <c r="D252" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E252" s="5">
-        <v>685914</v>
+        <v>685482</v>
       </c>
       <c r="F252" s="5">
         <v>4</v>
       </c>
       <c r="G252" s="5">
-        <v>2</v>
-      </c>
-      <c r="H252" s="5">
-        <v>4716511948</v>
+        <v>1</v>
+      </c>
+      <c r="H252" s="5" t="s">
+        <v>639</v>
       </c>
       <c r="I252" s="5" t="s">
-        <v>638</v>
+        <v>67</v>
       </c>
       <c r="J252" s="5" t="s">
         <v>68</v>
       </c>
       <c r="K252" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="L252" s="5">
-        <v>600</v>
+        <v>623</v>
+      </c>
+      <c r="L252" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="M252" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="N252" s="5"/>
+        <v>640</v>
+      </c>
+      <c r="N252" s="5" t="s">
+        <v>641</v>
+      </c>
       <c r="O252" s="5"/>
-    </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A253" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="B253" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C253" s="5">
-        <v>14219835</v>
-      </c>
-      <c r="D253" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E253" s="5">
-        <v>685482</v>
-      </c>
-      <c r="F253" s="5">
-        <v>4</v>
-      </c>
-      <c r="G253" s="5">
-        <v>1</v>
-      </c>
-      <c r="H253" s="5" t="s">
-        <v>641</v>
-      </c>
-      <c r="I253" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J253" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="K253" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="L253" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="M253" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="N253" s="5"/>
-      <c r="O253" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B41B60-546D-41D7-AF47-AE9A361C24CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA69A9E-A4B8-4C2A-9E59-9979E7512E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="642">
   <si>
     <t>Data</t>
   </si>
@@ -10070,7 +10070,9 @@
       <c r="N164" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O164" s="5"/>
+      <c r="O164" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
@@ -10115,7 +10117,9 @@
       <c r="N165" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O165" s="5"/>
+      <c r="O165" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
@@ -10160,7 +10164,9 @@
       <c r="N166" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O166" s="5"/>
+      <c r="O166" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
@@ -10205,7 +10211,9 @@
       <c r="N167" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O167" s="5"/>
+      <c r="O167" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
@@ -10250,7 +10258,9 @@
       <c r="N168" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O168" s="5"/>
+      <c r="O168" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
@@ -10295,7 +10305,9 @@
       <c r="N169" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O169" s="5"/>
+      <c r="O169" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
@@ -10340,7 +10352,9 @@
       <c r="N170" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O170" s="5"/>
+      <c r="O170" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
@@ -10385,7 +10399,9 @@
       <c r="N171" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O171" s="5"/>
+      <c r="O171" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
@@ -10430,7 +10446,9 @@
       <c r="N172" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O172" s="5"/>
+      <c r="O172" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
@@ -10475,7 +10493,9 @@
       <c r="N173" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O173" s="5"/>
+      <c r="O173" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
@@ -10520,7 +10540,9 @@
       <c r="N174" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O174" s="5"/>
+      <c r="O174" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
@@ -10565,7 +10587,9 @@
       <c r="N175" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O175" s="5"/>
+      <c r="O175" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
@@ -10610,7 +10634,9 @@
       <c r="N176" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O176" s="5"/>
+      <c r="O176" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
@@ -10655,7 +10681,9 @@
       <c r="N177" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O177" s="5"/>
+      <c r="O177" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
@@ -10700,7 +10728,9 @@
       <c r="N178" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O178" s="5"/>
+      <c r="O178" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
@@ -10745,7 +10775,9 @@
       <c r="N179" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O179" s="5"/>
+      <c r="O179" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
@@ -10790,7 +10822,9 @@
       <c r="N180" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O180" s="5"/>
+      <c r="O180" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
@@ -10835,7 +10869,9 @@
       <c r="N181" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O181" s="5"/>
+      <c r="O181" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
@@ -10880,7 +10916,9 @@
       <c r="N182" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O182" s="5"/>
+      <c r="O182" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
@@ -10925,7 +10963,9 @@
       <c r="N183" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O183" s="5"/>
+      <c r="O183" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
@@ -10970,7 +11010,9 @@
       <c r="N184" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O184" s="5"/>
+      <c r="O184" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
@@ -11015,7 +11057,9 @@
       <c r="N185" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O185" s="5"/>
+      <c r="O185" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
@@ -11060,7 +11104,9 @@
       <c r="N186" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O186" s="5"/>
+      <c r="O186" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
@@ -11105,7 +11151,9 @@
       <c r="N187" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O187" s="5"/>
+      <c r="O187" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
@@ -11150,7 +11198,9 @@
       <c r="N188" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O188" s="5"/>
+      <c r="O188" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
@@ -11195,7 +11245,9 @@
       <c r="N189" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O189" s="5"/>
+      <c r="O189" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
@@ -11240,7 +11292,9 @@
       <c r="N190" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O190" s="5"/>
+      <c r="O190" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
@@ -11285,7 +11339,9 @@
       <c r="N191" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O191" s="5"/>
+      <c r="O191" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
@@ -11330,7 +11386,9 @@
       <c r="N192" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O192" s="5"/>
+      <c r="O192" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
@@ -11375,7 +11433,9 @@
       <c r="N193" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O193" s="5"/>
+      <c r="O193" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
@@ -11420,7 +11480,9 @@
       <c r="N194" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O194" s="5"/>
+      <c r="O194" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
@@ -11465,7 +11527,9 @@
       <c r="N195" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O195" s="5"/>
+      <c r="O195" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
@@ -11510,7 +11574,9 @@
       <c r="N196" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O196" s="5"/>
+      <c r="O196" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
@@ -11555,7 +11621,9 @@
       <c r="N197" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O197" s="5"/>
+      <c r="O197" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
@@ -11600,7 +11668,9 @@
       <c r="N198" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O198" s="5"/>
+      <c r="O198" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
@@ -11645,7 +11715,9 @@
       <c r="N199" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O199" s="5"/>
+      <c r="O199" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
@@ -11690,7 +11762,9 @@
       <c r="N200" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O200" s="5"/>
+      <c r="O200" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
@@ -11735,7 +11809,9 @@
       <c r="N201" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O201" s="5"/>
+      <c r="O201" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
@@ -11780,7 +11856,9 @@
       <c r="N202" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O202" s="5"/>
+      <c r="O202" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
@@ -11825,7 +11903,9 @@
       <c r="N203" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O203" s="5"/>
+      <c r="O203" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
@@ -11870,7 +11950,9 @@
       <c r="N204" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O204" s="5"/>
+      <c r="O204" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
@@ -11915,7 +11997,9 @@
       <c r="N205" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O205" s="5"/>
+      <c r="O205" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
@@ -11960,7 +12044,9 @@
       <c r="N206" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O206" s="5"/>
+      <c r="O206" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
@@ -12005,7 +12091,9 @@
       <c r="N207" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O207" s="5"/>
+      <c r="O207" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
@@ -12050,7 +12138,9 @@
       <c r="N208" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O208" s="5"/>
+      <c r="O208" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
@@ -12095,7 +12185,9 @@
       <c r="N209" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O209" s="5"/>
+      <c r="O209" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
@@ -12140,7 +12232,9 @@
       <c r="N210" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O210" s="5"/>
+      <c r="O210" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
@@ -12185,7 +12279,9 @@
       <c r="N211" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O211" s="5"/>
+      <c r="O211" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
@@ -12230,7 +12326,9 @@
       <c r="N212" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O212" s="5"/>
+      <c r="O212" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
@@ -12275,7 +12373,9 @@
       <c r="N213" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O213" s="5"/>
+      <c r="O213" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
@@ -12320,7 +12420,9 @@
       <c r="N214" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O214" s="5"/>
+      <c r="O214" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
@@ -12365,7 +12467,9 @@
       <c r="N215" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O215" s="5"/>
+      <c r="O215" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
@@ -12410,7 +12514,9 @@
       <c r="N216" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O216" s="5"/>
+      <c r="O216" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
@@ -12455,7 +12561,9 @@
       <c r="N217" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O217" s="5"/>
+      <c r="O217" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
@@ -12500,7 +12608,9 @@
       <c r="N218" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O218" s="5"/>
+      <c r="O218" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
@@ -12545,7 +12655,9 @@
       <c r="N219" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O219" s="5"/>
+      <c r="O219" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
@@ -12590,7 +12702,9 @@
       <c r="N220" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O220" s="5"/>
+      <c r="O220" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
@@ -12635,7 +12749,9 @@
       <c r="N221" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O221" s="5"/>
+      <c r="O221" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
@@ -12680,7 +12796,9 @@
       <c r="N222" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O222" s="5"/>
+      <c r="O222" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
@@ -12725,7 +12843,9 @@
       <c r="N223" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O223" s="5"/>
+      <c r="O223" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
@@ -12770,7 +12890,9 @@
       <c r="N224" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O224" s="5"/>
+      <c r="O224" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
@@ -12815,7 +12937,9 @@
       <c r="N225" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O225" s="5"/>
+      <c r="O225" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
@@ -12860,7 +12984,9 @@
       <c r="N226" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O226" s="5"/>
+      <c r="O226" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
@@ -12905,7 +13031,9 @@
       <c r="N227" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O227" s="5"/>
+      <c r="O227" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
@@ -12950,7 +13078,9 @@
       <c r="N228" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O228" s="5"/>
+      <c r="O228" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
@@ -12995,7 +13125,9 @@
       <c r="N229" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O229" s="5"/>
+      <c r="O229" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
@@ -13040,7 +13172,9 @@
       <c r="N230" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O230" s="5"/>
+      <c r="O230" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
@@ -13085,7 +13219,9 @@
       <c r="N231" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O231" s="5"/>
+      <c r="O231" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
@@ -13130,7 +13266,9 @@
       <c r="N232" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O232" s="5"/>
+      <c r="O232" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
@@ -13175,7 +13313,9 @@
       <c r="N233" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O233" s="5"/>
+      <c r="O233" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
@@ -13220,7 +13360,9 @@
       <c r="N234" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O234" s="5"/>
+      <c r="O234" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
@@ -13265,7 +13407,9 @@
       <c r="N235" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O235" s="5"/>
+      <c r="O235" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
@@ -13310,7 +13454,9 @@
       <c r="N236" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O236" s="5"/>
+      <c r="O236" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
@@ -13355,7 +13501,9 @@
       <c r="N237" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O237" s="5"/>
+      <c r="O237" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
@@ -13400,7 +13548,9 @@
       <c r="N238" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O238" s="5"/>
+      <c r="O238" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
@@ -13445,7 +13595,9 @@
       <c r="N239" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O239" s="5"/>
+      <c r="O239" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
@@ -13490,7 +13642,9 @@
       <c r="N240" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O240" s="5"/>
+      <c r="O240" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
@@ -13535,7 +13689,9 @@
       <c r="N241" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O241" s="5"/>
+      <c r="O241" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
@@ -13580,7 +13736,9 @@
       <c r="N242" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O242" s="5"/>
+      <c r="O242" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
@@ -13625,7 +13783,9 @@
       <c r="N243" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O243" s="5"/>
+      <c r="O243" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
@@ -13670,7 +13830,9 @@
       <c r="N244" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O244" s="5"/>
+      <c r="O244" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
@@ -13715,7 +13877,9 @@
       <c r="N245" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O245" s="5"/>
+      <c r="O245" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
@@ -13760,7 +13924,9 @@
       <c r="N246" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O246" s="5"/>
+      <c r="O246" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
@@ -13805,7 +13971,9 @@
       <c r="N247" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O247" s="5"/>
+      <c r="O247" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
@@ -13850,7 +14018,9 @@
       <c r="N248" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O248" s="5"/>
+      <c r="O248" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
@@ -13895,7 +14065,9 @@
       <c r="N249" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O249" s="5"/>
+      <c r="O249" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
@@ -13940,7 +14112,9 @@
       <c r="N250" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O250" s="5"/>
+      <c r="O250" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
@@ -13985,7 +14159,9 @@
       <c r="N251" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O251" s="5"/>
+      <c r="O251" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
@@ -14030,7 +14206,9 @@
       <c r="N252" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="O252" s="5"/>
+      <c r="O252" s="5" t="s">
+        <v>641</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/98 - Excels/Cadastro-LPs.xlsx
+++ b/98 - Excels/Cadastro-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32C0F4A-DD82-4B8B-8095-3AF23712E3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F29AB4E-E4BF-4ADD-888D-359262AC42BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="140">
   <si>
     <t>Data</t>
   </si>
@@ -437,6 +437,9 @@
   </si>
   <si>
     <t>LP-056145</t>
+  </si>
+  <si>
+    <t>CADASTRADA</t>
   </si>
 </sst>
 </file>
@@ -854,7 +857,8 @@
     <col min="11" max="11" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -944,7 +948,9 @@
       <c r="M2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="5"/>
+      <c r="N2" s="5" t="s">
+        <v>139</v>
+      </c>
       <c r="O2" s="5"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -987,7 +993,9 @@
       <c r="M3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="5"/>
+      <c r="N3" s="5" t="s">
+        <v>139</v>
+      </c>
       <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
